--- a/site/demo/demo_network.xlsx
+++ b/site/demo/demo_network.xlsx
@@ -479,7 +479,7 @@
         <v>https://example.com/in/jordan-lee</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23d3f5e6%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23b35c00%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23d9a07a%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23d9a07a%22%2F%3E%3Cpath%20d%3D%22M20%2050c0-22%2012-34%2028-34s28%2012%2028%2034v26h-9V46c-5-6-12-9-19-9s-14%203-19%209v30h-9z%22%20fill%3D%22%236b4226%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cg%20fill%3D%22none%22%20stroke%3D%22%231f2937%22%20stroke-width%3D%222%22%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%226%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%226%22%2F%3E%3Cpath%20d%3D%22M46%2047h4%22%2F%3E%3C%2Fg%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H2" t="str">
         <v/>
@@ -517,7 +517,7 @@
         <v>https://example.com/in/priya-shah</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff1c2%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%235c7cfa%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%235f3b26%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%235f3b26%22%2F%3E%3Cpath%20d%3D%22M22%2044c0-18%2012-28%2026-28s26%2010%2026%2028c-6-8-16-12-26-12s-20%204-26%2012z%22%20fill%3D%22%23a0612b%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cg%20fill%3D%22none%22%20stroke%3D%22%231f2937%22%20stroke-width%3D%222%22%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%226%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%226%22%2F%3E%3Cpath%20d%3D%22M46%2047h4%22%2F%3E%3C%2Fg%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -555,7 +555,7 @@
         <v>https://example.com/in/sofia-alvarez</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23ffe3d3%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23b35c00%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23b97a56%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23b97a56%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H4" t="str">
         <v/>
@@ -593,7 +593,7 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23dbe7ff%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23c2255c%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23d9a07a%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23d9a07a%22%2F%3E%3Cpath%20d%3D%22M20%2046c-4-16%208-30%2028-30s32%2014%2028%2030c-4-3-6-8-6-8s-4%206-11%206-7-6-11-6-4%206-11%206-7-6-7-6-2%205-10%208z%22%20fill%3D%22%23a0612b%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -631,7 +631,7 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23e3e8ef%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%237048e8%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23b97a56%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23b97a56%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -669,7 +669,7 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23ece3ff%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%232e6fd8%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%238d5a3b%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%238d5a3b%22%2F%3E%3Cpath%20d%3D%22M20%2050c0-22%2012-34%2028-34s28%2012%2028%2034v26h-9V46c-5-6-12-9-19-9s-14%203-19%209v30h-9z%22%20fill%3D%22%23d9a441%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -707,7 +707,7 @@
         <v/>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23ffe3d3%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%230891b2%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23b97a56%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23b97a56%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2214%22%20r%3D%2210%22%20fill%3D%22%238a8a8a%22%2F%3E%3Cpath%20d%3D%22M22%2044c0-17%2012-27%2026-27s26%2010%2026%2027c-6-7-16-11-26-11s-20%204-26%2011z%22%20fill%3D%22%238a8a8a%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H8" t="str">
         <v/>
@@ -745,7 +745,7 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23d5f1f8%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%230891b2%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23b97a56%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23b97a56%22%2F%3E%3Cpath%20d%3D%22M22%2044c0-18%2012-28%2026-28s26%2010%2026%2028c-6-8-16-12-26-12s-20%204-26%2012z%22%20fill%3D%22%23d9a441%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -783,7 +783,7 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23e3e8ef%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23b35c00%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23f6d7c3%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23f6d7c3%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2214%22%20r%3D%2210%22%20fill%3D%22%23b5452b%22%2F%3E%3Cpath%20d%3D%22M22%2044c0-17%2012-27%2026-27s26%2010%2026%2027c-6-7-16-11-26-11s-20%204-26%2011z%22%20fill%3D%22%23b5452b%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -821,7 +821,7 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23d3f5e6%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%231971c2%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%235f3b26%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%235f3b26%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2214%22%20r%3D%2210%22%20fill%3D%22%23a0612b%22%2F%3E%3Cpath%20d%3D%22M22%2044c0-17%2012-27%2026-27s26%2010%2026%2027c-6-7-16-11-26-11s-20%204-26%2011z%22%20fill%3D%22%23a0612b%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -859,7 +859,7 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23ffe3d3%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%237048e8%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23b97a56%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23b97a56%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2214%22%20r%3D%2210%22%20fill%3D%22%234a2f1d%22%2F%3E%3Cpath%20d%3D%22M22%2044c0-17%2012-27%2026-27s26%2010%2026%2027c-6-7-16-11-26-11s-20%204-26%2011z%22%20fill%3D%22%234a2f1d%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H12" t="str">
         <v/>
@@ -897,7 +897,7 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff1c2%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23e8590c%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%238d5a3b%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%238d5a3b%22%2F%3E%3Cpath%20d%3D%22M20%2050c0-22%2012-34%2028-34s28%2012%2028%2034v26h-9V46c-5-6-12-9-19-9s-14%203-19%209v30h-9z%22%20fill%3D%22%23d9a441%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H13" t="str">
         <v/>
@@ -935,7 +935,7 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff1c2%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%237048e8%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23d9a07a%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23d9a07a%22%2F%3E%3Cpath%20d%3D%22M22%2044c0-18%2012-28%2026-28s26%2010%2026%2028c-6-8-16-12-26-12s-20%204-26%2012z%22%20fill%3D%22%23a0612b%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -973,7 +973,7 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23ffe3d3%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23c2255c%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23f6d7c3%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23f6d7c3%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H15" t="str">
         <v/>
@@ -1011,7 +1011,7 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23e3e8ef%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%231971c2%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23f6d7c3%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23f6d7c3%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2214%22%20r%3D%2210%22%20fill%3D%22%231f1f1f%22%2F%3E%3Cpath%20d%3D%22M22%2044c0-17%2012-27%2026-27s26%2010%2026%2027c-6-7-16-11-26-11s-20%204-26%2011z%22%20fill%3D%22%231f1f1f%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H16" t="str">
         <v>Jordan Lee</v>
@@ -1049,7 +1049,7 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23ffdbe7%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%232f9e44%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%238d5a3b%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%238d5a3b%22%2F%3E%3Cpath%20d%3D%22M20%2046c-4-16%208-30%2028-30s32%2014%2028%2030c-4-3-6-8-6-8s-4%206-11%206-7-6-11-6-4%206-11%206-7-6-7-6-2%205-10%208z%22%20fill%3D%22%236b4226%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H17" t="str">
         <v>Sofia Alvarez</v>
@@ -1087,7 +1087,7 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff1c2%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23e8590c%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%235f3b26%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%235f3b26%22%2F%3E%3Cpath%20d%3D%22M20%2046c-4-16%208-30%2028-30s32%2014%2028%2030c-4-3-6-8-6-8s-4%206-11%206-7-6-11-6-4%206-11%206-7-6-7-6-2%205-10%208z%22%20fill%3D%22%238a8a8a%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H18" t="str">
         <v>Sofia Alvarez</v>
@@ -1125,7 +1125,7 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23ffdbe7%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23e8590c%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23eec1a0%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23eec1a0%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cg%20fill%3D%22none%22%20stroke%3D%22%231f2937%22%20stroke-width%3D%222%22%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%226%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%226%22%2F%3E%3Cpath%20d%3D%22M46%2047h4%22%2F%3E%3C%2Fg%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H19" t="str">
         <v>Noah Carter</v>
@@ -1163,7 +1163,7 @@
         <v/>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23d3f5e6%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23b35c00%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23b97a56%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23b97a56%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2214%22%20r%3D%2210%22%20fill%3D%22%23a0612b%22%2F%3E%3Cpath%20d%3D%22M22%2044c0-17%2012-27%2026-27s26%2010%2026%2027c-6-7-16-11-26-11s-20%204-26%2011z%22%20fill%3D%22%23a0612b%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H20" t="str">
         <v>Mia Chen</v>
@@ -1201,7 +1201,7 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23d5f1f8%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23d6336c%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23d9a07a%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23d9a07a%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2214%22%20r%3D%2210%22%20fill%3D%22%236b4226%22%2F%3E%3Cpath%20d%3D%22M22%2044c0-17%2012-27%2026-27s26%2010%2026%2027c-6-7-16-11-26-11s-20%204-26%2011z%22%20fill%3D%22%236b4226%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H21" t="str">
         <v>Daniel Ortiz</v>
@@ -1239,7 +1239,7 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23e3e8ef%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23c2255c%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23d9a07a%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23d9a07a%22%2F%3E%3Cpath%20d%3D%22M20%2050c0-22%2012-34%2028-34s28%2012%2028%2034v26h-9V46c-5-6-12-9-19-9s-14%203-19%209v30h-9z%22%20fill%3D%22%232b1d14%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H22" t="str">
         <v>Liam Walsh</v>
@@ -1277,7 +1277,7 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v/>
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23ffdbe7%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23c2255c%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23f6d7c3%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23f6d7c3%22%2F%3E%3Cpath%20d%3D%22M20%2046c-4-16%208-30%2028-30s32%2014%2028%2030c-4-3-6-8-6-8s-4%206-11%206-7-6-11-6-4%206-11%206-7-6-7-6-2%205-10%208z%22%20fill%3D%22%23a0612b%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cg%20fill%3D%22none%22%20stroke%3D%22%231f2937%22%20stroke-width%3D%222%22%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%226%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%226%22%2F%3E%3Cpath%20d%3D%22M46%2047h4%22%2F%3E%3C%2Fg%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
       </c>
       <c r="H23" t="str">
         <v>Zoe Adams</v>
@@ -1419,10 +1419,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="28.83203125"/>
     <col min="2" max="2" customWidth="1" width="30.83203125"/>
+    <col min="3" max="3" customWidth="1" width="30.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1432,10 +1433,178 @@
       <c r="B1" t="str">
         <v>Website</v>
       </c>
+      <c r="C1" t="str">
+        <v>Logo</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Brightline Bank</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2248%22%20r%3D%2238%22%20fill%3D%22%232e6fd8%22%2F%3E%3Cg%20style%3D%22color%3A%232e6fd8%22%3E%3Cpath%20d%3D%22M48%2022l28%2013v5H20v-5z%20M26%2044h7v22h-7z%20M44.5%2044h7v22h-7z%20M63%2044h7v22h-7z%20M20%2070h56v6H20z%22%20fill%3D%22%23fff%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Contoso Games</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Cpath%20d%3D%22M48%208l35%2020v40L48%2088%2013%2068V28z%22%20fill%3D%22%232e6fd8%22%2F%3E%3Cg%20style%3D%22color%3A%232e6fd8%22%3E%3Crect%20x%3D%2220%22%20y%3D%2236%22%20width%3D%2256%22%20height%3D%2228%22%20rx%3D%2214%22%20fill%3D%22%23fff%22%2F%3E%3Cpath%20d%3D%22M32%2045v10M27%2050h10%22%20stroke%3D%22currentColor%22%20stroke-width%3D%224%22%20stroke-linecap%3D%22round%22%2F%3E%3Ccircle%20cx%3D%2260%22%20cy%3D%2247%22%20r%3D%223.5%22%20fill%3D%22currentColor%22%2F%3E%3Ccircle%20cx%3D%2267%22%20cy%3D%2254%22%20r%3D%223.5%22%20fill%3D%22currentColor%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Fieldstone Capital</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Crect%20x%3D%2210%22%20y%3D%2210%22%20width%3D%2276%22%20height%3D%2276%22%20rx%3D%226%22%20fill%3D%22%23c2255c%22%2F%3E%3Cg%20style%3D%22color%3A%23c2255c%22%3E%3Cpath%20d%3D%22M48%2022l28%2013v5H20v-5z%20M26%2044h7v22h-7z%20M44.5%2044h7v22h-7z%20M63%2044h7v22h-7z%20M20%2070h56v6H20z%22%20fill%3D%22%23fff%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Granite Peak Partners</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2248%22%20r%3D%2238%22%20fill%3D%22%230891b2%22%2F%3E%3Cg%20style%3D%22color%3A%230891b2%22%3E%3Cpath%20d%3D%22M48%2022l28%2013v5H20v-5z%20M26%2044h7v22h-7z%20M44.5%2044h7v22h-7z%20M63%2044h7v22h-7z%20M20%2070h56v6H20z%22%20fill%3D%22%23fff%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Harbor Tech Institute</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2248%22%20r%3D%2238%22%20fill%3D%22%23c2255c%22%2F%3E%3Cg%20style%3D%22color%3A%23c2255c%22%3E%3Cpath%20d%3D%22M48%2024l32%2014-32%2014-32-14z%20M28%2046v14c0%206%209%2012%2020%2012s20-6%2020-12V46l-20%209z%20M76%2040v18%22%20fill%3D%22%23fff%22%20stroke%3D%22%23fff%22%20stroke-width%3D%222%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Harbor Ventures</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Cpath%20d%3D%22M48%208l35%2020v40L48%2088%2013%2068V28z%22%20fill%3D%22%238b5cf6%22%2F%3E%3Cg%20style%3D%22color%3A%238b5cf6%22%3E%3Cpath%20d%3D%22M48%2018c10%208%2014%2020%2012%2034l-6%208H42l-6-8c-2-14%202-26%2012-34z%20M36%2056l-8%2012%2010-2z%20M60%2056l8%2012-10-2z%22%20fill%3D%22%23fff%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2238%22%20r%3D%225%22%20fill%3D%22currentColor%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Harborview Media</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Crect%20x%3D%2210%22%20y%3D%2210%22%20width%3D%2276%22%20height%3D%2276%22%20rx%3D%2220%22%20fill%3D%22%23b35c00%22%2F%3E%3Cg%20style%3D%22color%3A%23b35c00%22%3E%3Cpath%20d%3D%22M38%2028l32%2020-32%2020z%22%20fill%3D%22%23fff%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Independent</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Crect%20x%3D%2210%22%20y%3D%2210%22%20width%3D%2276%22%20height%3D%2276%22%20rx%3D%226%22%20fill%3D%22%231971c2%22%2F%3E%3Ctext%20x%3D%2248%22%20y%3D%2261%22%20font-size%3D%2234%22%20fill%3D%22%23fff%22%20font-family%3D%22system-ui%2C-apple-system%2CSegoe%20UI%2Csans-serif%22%20font-weight%3D%22700%22%20text-anchor%3D%22middle%22%3EIN%3C%2Ftext%3E%3C%2Fsvg%3E</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Keystone Health</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Crect%20x%3D%2210%22%20y%3D%2210%22%20width%3D%2276%22%20height%3D%2276%22%20rx%3D%226%22%20fill%3D%22%238b5cf6%22%2F%3E%3Cg%20style%3D%22color%3A%238b5cf6%22%3E%3Cpath%20d%3D%22M40%2022h16v18h18v16H56v18H40V56H22V40h18z%22%20fill%3D%22%23fff%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Lakeview State University</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Cpath%20d%3D%22M48%208l35%2020v40L48%2088%2013%2068V28z%22%20fill%3D%22%231f9d6b%22%2F%3E%3Cg%20style%3D%22color%3A%231f9d6b%22%3E%3Cpath%20d%3D%22M48%2024l32%2014-32%2014-32-14z%20M28%2046v14c0%206%209%2012%2020%2012s20-6%2020-12V46l-20%209z%20M76%2040v18%22%20fill%3D%22%23fff%22%20stroke%3D%22%23fff%22%20stroke-width%3D%222%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Northwind Consulting</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2248%22%20r%3D%2238%22%20fill%3D%22%23b35c00%22%2F%3E%3Cg%20style%3D%22color%3A%23b35c00%22%3E%3Cpath%20d%3D%22M24%2070V52h10v18z%20M43%2070V38h10v32z%20M62%2070V26h10v44z%22%20fill%3D%22%23fff%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Northwind Consulting, Inc.</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Cpath%20d%3D%22M48%208l35%2020v40L48%2088%2013%2068V28z%22%20fill%3D%22%231f9d6b%22%2F%3E%3Cg%20style%3D%22color%3A%231f9d6b%22%3E%3Cpath%20d%3D%22M24%2070V52h10v18z%20M43%2070V38h10v32z%20M62%2070V26h10v44z%22%20fill%3D%22%23fff%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Pinecrest Labs</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2248%22%20r%3D%2238%22%20fill%3D%22%23e8590c%22%2F%3E%3Cg%20style%3D%22color%3A%23e8590c%22%3E%3Cpath%20d%3D%22M40%2022h16v6h-3v14l17%2026c2%204-1%208-5%208H31c-4%200-7-4-5-8l17-26V28h-3z%22%20fill%3D%22%23fff%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Riverbend University</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Crect%20x%3D%2210%22%20y%3D%2210%22%20width%3D%2276%22%20height%3D%2276%22%20rx%3D%226%22%20fill%3D%22%23e8590c%22%2F%3E%3Cg%20style%3D%22color%3A%23e8590c%22%3E%3Cpath%20d%3D%22M48%2024l32%2014-32%2014-32-14z%20M28%2046v14c0%206%209%2012%2020%2012s20-6%2020-12V46l-20%209z%20M76%2040v18%22%20fill%3D%22%23fff%22%20stroke%3D%22%23fff%22%20stroke-width%3D%222%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Summit Airlines</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2248%22%20r%3D%2238%22%20fill%3D%22%238b5cf6%22%2F%3E%3Cg%20style%3D%22color%3A%238b5cf6%22%3E%3Cpath%20d%3D%22M48%2022l6%2020%2020%208v6l-20-4-2%2016%207%205v5l-11-3-11%203v-5l7-5-2-16-20%204v-6l20-8z%22%20fill%3D%22%23fff%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1763,7 +1932,7 @@
         <v xml:space="preserve">  Photo</v>
       </c>
       <c r="B7" t="str">
-        <v>An image link, or leave it to the app (it stores a small picture here when you add one).</v>
+        <v>An image link, or use 'Add photo' in the app (it stores a small picture here). LinkedIn exports don't include photos.</v>
       </c>
     </row>
     <row r="8">
@@ -1803,7 +1972,7 @@
         <v>Targets</v>
       </c>
       <c r="B12" t="str">
-        <v>Companies you want to work at. Priority (1 = highest) and Stage (Researching / Networking / Applied / Interviewing / Offer / Closed) are optional.</v>
+        <v>Companies you want to work at. Priority (1 = highest) and Stage (Researching / Networking / Applied / Interviewing / Offer) are optional.</v>
       </c>
     </row>
     <row r="13">
@@ -1811,7 +1980,7 @@
         <v>Companies</v>
       </c>
       <c r="B13" t="str">
-        <v>Optional. Set a company's Website (e.g. byu.edu) if its logo comes out wrong.</v>
+        <v>Optional. Set a company's Website (e.g. byu.edu) if its logo comes out wrong, or put an image link in Logo.</v>
       </c>
     </row>
     <row r="14">

--- a/site/demo/demo_network.xlsx
+++ b/site/demo/demo_network.xlsx
@@ -464,10 +464,10 @@
         <v>Jordan Lee</v>
       </c>
       <c r="B2" t="str">
-        <v>Northwind Consulting</v>
+        <v>Deloitte</v>
       </c>
       <c r="C2" t="str">
-        <v>Riverbend University</v>
+        <v>BYU</v>
       </c>
       <c r="D2" t="str">
         <v>Senior Consultant</v>
@@ -479,7 +479,7 @@
         <v>https://example.com/in/jordan-lee</v>
       </c>
       <c r="G2" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23d3f5e6%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23b35c00%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23d9a07a%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23d9a07a%22%2F%3E%3Cpath%20d%3D%22M20%2050c0-22%2012-34%2028-34s28%2012%2028%2034v26h-9V46c-5-6-12-9-19-9s-14%203-19%209v30h-9z%22%20fill%3D%22%236b4226%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cg%20fill%3D%22none%22%20stroke%3D%22%231f2937%22%20stroke-width%3D%222%22%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%226%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%226%22%2F%3E%3Cpath%20d%3D%22M46%2047h4%22%2F%3E%3C%2Fg%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H2" t="str">
         <v/>
@@ -502,10 +502,10 @@
         <v>Priya Shah</v>
       </c>
       <c r="B3" t="str">
-        <v>Northwind Consulting</v>
+        <v>Deloitte</v>
       </c>
       <c r="C3" t="str">
-        <v>Lakeview State University</v>
+        <v>University of Utah</v>
       </c>
       <c r="D3" t="str">
         <v>Manager</v>
@@ -517,7 +517,7 @@
         <v>https://example.com/in/priya-shah</v>
       </c>
       <c r="G3" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff1c2%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%235c7cfa%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%235f3b26%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%235f3b26%22%2F%3E%3Cpath%20d%3D%22M22%2044c0-18%2012-28%2026-28s26%2010%2026%2028c-6-8-16-12-26-12s-20%204-26%2012z%22%20fill%3D%22%23a0612b%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cg%20fill%3D%22none%22%20stroke%3D%22%231f2937%22%20stroke-width%3D%222%22%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%226%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%226%22%2F%3E%3Cpath%20d%3D%22M46%2047h4%22%2F%3E%3C%2Fg%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -540,10 +540,10 @@
         <v>Sofia Alvarez</v>
       </c>
       <c r="B4" t="str">
-        <v>Contoso Games</v>
+        <v>Microsoft</v>
       </c>
       <c r="C4" t="str">
-        <v>Riverbend University</v>
+        <v>BYU</v>
       </c>
       <c r="D4" t="str">
         <v>Product Manager</v>
@@ -555,7 +555,7 @@
         <v>https://example.com/in/sofia-alvarez</v>
       </c>
       <c r="G4" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23ffe3d3%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23b35c00%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23b97a56%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23b97a56%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H4" t="str">
         <v/>
@@ -567,7 +567,7 @@
         <v>Met</v>
       </c>
       <c r="K4" t="str">
-        <v>Gaming</v>
+        <v>Product</v>
       </c>
       <c r="L4" t="str">
         <v>Owns the marketplace roadmap</v>
@@ -578,10 +578,10 @@
         <v>Marcus Bell</v>
       </c>
       <c r="B5" t="str">
-        <v>Northwind Consulting</v>
+        <v>Deloitte</v>
       </c>
       <c r="C5" t="str">
-        <v>Riverbend University</v>
+        <v>Brigham Young University</v>
       </c>
       <c r="D5" t="str">
         <v>Analyst</v>
@@ -593,7 +593,7 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23dbe7ff%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23c2255c%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23d9a07a%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23d9a07a%22%2F%3E%3Cpath%20d%3D%22M20%2046c-4-16%208-30%2028-30s32%2014%2028%2030c-4-3-6-8-6-8s-4%206-11%206-7-6-11-6-4%206-11%206-7-6-7-6-2%205-10%208z%22%20fill%3D%22%23a0612b%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -616,7 +616,7 @@
         <v>Hana Kim</v>
       </c>
       <c r="B6" t="str">
-        <v>Northwind Consulting, Inc.</v>
+        <v>Deloitte LLP</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -631,7 +631,7 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23e3e8ef%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%237048e8%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23b97a56%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23b97a56%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -654,7 +654,7 @@
         <v>Ethan Brooks</v>
       </c>
       <c r="B7" t="str">
-        <v>Contoso Games</v>
+        <v>Microsoft</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -669,7 +669,7 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23ece3ff%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%232e6fd8%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%238d5a3b%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%238d5a3b%22%2F%3E%3Cpath%20d%3D%22M20%2050c0-22%2012-34%2028-34s28%2012%2028%2034v26h-9V46c-5-6-12-9-19-9s-14%203-19%209v30h-9z%22%20fill%3D%22%23d9a441%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -681,7 +681,7 @@
         <v>Follow Up</v>
       </c>
       <c r="K7" t="str">
-        <v>Gaming</v>
+        <v>Product</v>
       </c>
       <c r="L7" t="str">
         <v/>
@@ -692,13 +692,13 @@
         <v>Lena Novak</v>
       </c>
       <c r="B8" t="str">
-        <v>Contoso Games</v>
+        <v>Microsoft</v>
       </c>
       <c r="C8" t="str">
-        <v>Harbor Tech Institute</v>
+        <v>University of Utah</v>
       </c>
       <c r="D8" t="str">
-        <v>Producer</v>
+        <v>Program Manager</v>
       </c>
       <c r="E8" t="str">
         <v>lena.novak@example.com</v>
@@ -707,7 +707,7 @@
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23ffe3d3%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%230891b2%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23b97a56%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23b97a56%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2214%22%20r%3D%2210%22%20fill%3D%22%238a8a8a%22%2F%3E%3Cpath%20d%3D%22M22%2044c0-17%2012-27%2026-27s26%2010%2026%2027c-6-7-16-11-26-11s-20%204-26%2011z%22%20fill%3D%22%238a8a8a%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H8" t="str">
         <v/>
@@ -719,7 +719,7 @@
         <v>To Reach Out</v>
       </c>
       <c r="K8" t="str">
-        <v>Gaming</v>
+        <v>Product</v>
       </c>
       <c r="L8" t="str">
         <v/>
@@ -730,10 +730,10 @@
         <v>Noah Carter</v>
       </c>
       <c r="B9" t="str">
-        <v>Summit Airlines</v>
+        <v>Delta Air Lines</v>
       </c>
       <c r="C9" t="str">
-        <v>Riverbend University</v>
+        <v>BYU</v>
       </c>
       <c r="D9" t="str">
         <v>Commercial Strategy Analyst</v>
@@ -745,7 +745,7 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23d5f1f8%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%230891b2%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23b97a56%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23b97a56%22%2F%3E%3Cpath%20d%3D%22M22%2044c0-18%2012-28%2026-28s26%2010%2026%2028c-6-8-16-12-26-12s-20%204-26%2012z%22%20fill%3D%22%23d9a441%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -768,7 +768,7 @@
         <v>Grace Owens</v>
       </c>
       <c r="B10" t="str">
-        <v>Summit Airlines</v>
+        <v>Delta Air Lines</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -783,7 +783,7 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23e3e8ef%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23b35c00%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23f6d7c3%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23f6d7c3%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2214%22%20r%3D%2210%22%20fill%3D%22%23b5452b%22%2F%3E%3Cpath%20d%3D%22M22%2044c0-17%2012-27%2026-27s26%2010%2026%2027c-6-7-16-11-26-11s-20%204-26%2011z%22%20fill%3D%22%23b5452b%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -806,10 +806,10 @@
         <v>Daniel Ortiz</v>
       </c>
       <c r="B11" t="str">
-        <v>Brightline Bank</v>
+        <v>Goldman Sachs</v>
       </c>
       <c r="C11" t="str">
-        <v>Riverbend University</v>
+        <v>BYU</v>
       </c>
       <c r="D11" t="str">
         <v>Strategy Associate</v>
@@ -821,7 +821,7 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23d3f5e6%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%231971c2%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%235f3b26%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%235f3b26%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2214%22%20r%3D%2210%22%20fill%3D%22%23a0612b%22%2F%3E%3Cpath%20d%3D%22M22%2044c0-17%2012-27%2026-27s26%2010%2026%2027c-6-7-16-11-26-11s-20%204-26%2011z%22%20fill%3D%22%23a0612b%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -844,13 +844,13 @@
         <v>Mia Chen</v>
       </c>
       <c r="B12" t="str">
-        <v>Fieldstone Capital</v>
+        <v>Google</v>
       </c>
       <c r="C12" t="str">
-        <v>Lakeview State University</v>
+        <v>University of Utah</v>
       </c>
       <c r="D12" t="str">
-        <v>Partner</v>
+        <v>Product Lead</v>
       </c>
       <c r="E12" t="str">
         <v>mia.chen@example.com</v>
@@ -859,7 +859,7 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23ffe3d3%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%237048e8%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23b97a56%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23b97a56%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2214%22%20r%3D%2210%22%20fill%3D%22%234a2f1d%22%2F%3E%3Cpath%20d%3D%22M22%2044c0-17%2012-27%2026-27s26%2010%2026%2027c-6-7-16-11-26-11s-20%204-26%2011z%22%20fill%3D%22%234a2f1d%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H12" t="str">
         <v/>
@@ -882,13 +882,13 @@
         <v>Owen Price</v>
       </c>
       <c r="B13" t="str">
-        <v>Fieldstone Capital</v>
+        <v>Google</v>
       </c>
       <c r="C13" t="str">
-        <v>Lakeview State University</v>
+        <v>University of Utah</v>
       </c>
       <c r="D13" t="str">
-        <v>Associate</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="E13" t="str">
         <v>owen.price@example.com</v>
@@ -897,7 +897,7 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff1c2%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23e8590c%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%238d5a3b%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%238d5a3b%22%2F%3E%3Cpath%20d%3D%22M20%2050c0-22%2012-34%2028-34s28%2012%2028%2034v26h-9V46c-5-6-12-9-19-9s-14%203-19%209v30h-9z%22%20fill%3D%22%23d9a441%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H13" t="str">
         <v/>
@@ -920,10 +920,10 @@
         <v>Ava Thompson</v>
       </c>
       <c r="B14" t="str">
-        <v>Keystone Health</v>
+        <v>Adobe</v>
       </c>
       <c r="C14" t="str">
-        <v>Lakeview State University</v>
+        <v>University of Utah</v>
       </c>
       <c r="D14" t="str">
         <v>Operations Lead</v>
@@ -935,7 +935,7 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff1c2%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%237048e8%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23d9a07a%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23d9a07a%22%2F%3E%3Cpath%20d%3D%22M22%2044c0-18%2012-28%2026-28s26%2010%2026%2028c-6-8-16-12-26-12s-20%204-26%2012z%22%20fill%3D%22%23a0612b%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -973,7 +973,7 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23ffe3d3%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23c2255c%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23f6d7c3%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23f6d7c3%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H15" t="str">
         <v/>
@@ -996,7 +996,7 @@
         <v>Rachel Green</v>
       </c>
       <c r="B16" t="str">
-        <v>Northwind Consulting</v>
+        <v>Deloitte</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -1011,7 +1011,7 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23e3e8ef%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%231971c2%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23f6d7c3%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23f6d7c3%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2214%22%20r%3D%2210%22%20fill%3D%22%231f1f1f%22%2F%3E%3Cpath%20d%3D%22M22%2044c0-17%2012-27%2026-27s26%2010%2026%2027c-6-7-16-11-26-11s-20%204-26%2011z%22%20fill%3D%22%231f1f1f%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H16" t="str">
         <v>Jordan Lee</v>
@@ -1034,7 +1034,7 @@
         <v>Tom Nguyen</v>
       </c>
       <c r="B17" t="str">
-        <v>Contoso Games</v>
+        <v>Microsoft</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -1049,7 +1049,7 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23ffdbe7%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%232f9e44%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%238d5a3b%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%238d5a3b%22%2F%3E%3Cpath%20d%3D%22M20%2046c-4-16%208-30%2028-30s32%2014%2028%2030c-4-3-6-8-6-8s-4%206-11%206-7-6-11-6-4%206-11%206-7-6-7-6-2%205-10%208z%22%20fill%3D%22%236b4226%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H17" t="str">
         <v>Sofia Alvarez</v>
@@ -1061,7 +1061,7 @@
         <v>To Reach Out</v>
       </c>
       <c r="K17" t="str">
-        <v>Gaming</v>
+        <v>Product</v>
       </c>
       <c r="L17" t="str">
         <v/>
@@ -1072,7 +1072,7 @@
         <v>Isla Moore</v>
       </c>
       <c r="B18" t="str">
-        <v>Contoso Games</v>
+        <v>Microsoft</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -1087,7 +1087,7 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff1c2%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23e8590c%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%235f3b26%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%235f3b26%22%2F%3E%3Cpath%20d%3D%22M20%2046c-4-16%208-30%2028-30s32%2014%2028%2030c-4-3-6-8-6-8s-4%206-11%206-7-6-11-6-4%206-11%206-7-6-7-6-2%205-10%208z%22%20fill%3D%22%238a8a8a%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H18" t="str">
         <v>Sofia Alvarez</v>
@@ -1099,7 +1099,7 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>Gaming</v>
+        <v>Product</v>
       </c>
       <c r="L18" t="str">
         <v/>
@@ -1110,7 +1110,7 @@
         <v>Victor Hale</v>
       </c>
       <c r="B19" t="str">
-        <v>Summit Airlines</v>
+        <v>Delta Air Lines</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -1125,7 +1125,7 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23ffdbe7%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23e8590c%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23eec1a0%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23eec1a0%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cg%20fill%3D%22none%22%20stroke%3D%22%231f2937%22%20stroke-width%3D%222%22%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%226%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%226%22%2F%3E%3Cpath%20d%3D%22M46%2047h4%22%2F%3E%3C%2Fg%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H19" t="str">
         <v>Noah Carter</v>
@@ -1148,13 +1148,13 @@
         <v>Chloe Park</v>
       </c>
       <c r="B20" t="str">
-        <v>Harbor Ventures</v>
+        <v>Adobe</v>
       </c>
       <c r="C20" t="str">
         <v/>
       </c>
       <c r="D20" t="str">
-        <v>Investor</v>
+        <v>Design Manager</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1163,7 +1163,7 @@
         <v/>
       </c>
       <c r="G20" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23d3f5e6%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23b35c00%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23b97a56%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23b97a56%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2214%22%20r%3D%2210%22%20fill%3D%22%23a0612b%22%2F%3E%3Cpath%20d%3D%22M22%2044c0-17%2012-27%2026-27s26%2010%2026%2027c-6-7-16-11-26-11s-20%204-26%2011z%22%20fill%3D%22%23a0612b%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H20" t="str">
         <v>Mia Chen</v>
@@ -1186,7 +1186,7 @@
         <v>Ben Foster</v>
       </c>
       <c r="B21" t="str">
-        <v>Riverbend University</v>
+        <v>BYU</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -1201,7 +1201,7 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23d5f1f8%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23d6336c%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23d9a07a%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23d9a07a%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2214%22%20r%3D%2210%22%20fill%3D%22%236b4226%22%2F%3E%3Cpath%20d%3D%22M22%2044c0-17%2012-27%2026-27s26%2010%2026%2027c-6-7-16-11-26-11s-20%204-26%2011z%22%20fill%3D%22%236b4226%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H21" t="str">
         <v>Daniel Ortiz</v>
@@ -1224,13 +1224,13 @@
         <v>Zoe Adams</v>
       </c>
       <c r="B22" t="str">
-        <v>Pinecrest Labs</v>
+        <v>Qualtrics</v>
       </c>
       <c r="C22" t="str">
         <v/>
       </c>
       <c r="D22" t="str">
-        <v>CEO</v>
+        <v>Director of Strategy</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1239,7 +1239,7 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23e3e8ef%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23c2255c%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23d9a07a%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23d9a07a%22%2F%3E%3Cpath%20d%3D%22M20%2050c0-22%2012-34%2028-34s28%2012%2028%2034v26h-9V46c-5-6-12-9-19-9s-14%203-19%209v30h-9z%22%20fill%3D%22%232b1d14%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H22" t="str">
         <v>Liam Walsh</v>
@@ -1262,7 +1262,7 @@
         <v>Sam Rivera</v>
       </c>
       <c r="B23" t="str">
-        <v>Pinecrest Labs</v>
+        <v>Qualtrics</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -1277,7 +1277,7 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23ffdbe7%22%2F%3E%3Cpath%20d%3D%22M16%2096c2-16%2015-24%2032-24s30%208%2032%2024z%22%20fill%3D%22%23c2255c%22%2F%3E%3Crect%20x%3D%2242%22%20y%3D%2260%22%20width%3D%2212%22%20height%3D%2214%22%20rx%3D%225%22%20fill%3D%22%23f6d7c3%22%2F%3E%3Cellipse%20cx%3D%2248%22%20cy%3D%2246%22%20rx%3D%2221%22%20ry%3D%2224%22%20fill%3D%22%23f6d7c3%22%2F%3E%3Cpath%20d%3D%22M20%2046c-4-16%208-30%2028-30s32%2014%2028%2030c-4-3-6-8-6-8s-4%206-11%206-7-6-11-6-4%206-11%206-7-6-7-6-2%205-10%208z%22%20fill%3D%22%23a0612b%22%2F%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%222.6%22%20fill%3D%22%231f2937%22%2F%3E%3Cg%20fill%3D%22none%22%20stroke%3D%22%231f2937%22%20stroke-width%3D%222%22%3E%3Ccircle%20cx%3D%2240%22%20cy%3D%2247%22%20r%3D%226%22%2F%3E%3Ccircle%20cx%3D%2256%22%20cy%3D%2247%22%20r%3D%226%22%2F%3E%3Cpath%20d%3D%22M46%2047h4%22%2F%3E%3C%2Fg%3E%3Cpath%20d%3D%22M41%2057c4%204%2010%204%2014%200%22%20fill%3D%22none%22%20stroke%3D%22%237a3b2e%22%20stroke-width%3D%222.4%22%20stroke-linecap%3D%22round%22%2F%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
       <c r="H23" t="str">
         <v>Zoe Adams</v>
@@ -1328,7 +1328,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Northwind Consulting</v>
+        <v>Deloitte</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Summit Airlines</v>
+        <v>Delta Air Lines</v>
       </c>
       <c r="B3" t="str">
         <v>1</v>
@@ -1356,7 +1356,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Brightline Bank</v>
+        <v>Goldman Sachs</v>
       </c>
       <c r="B4" t="str">
         <v>2</v>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Pinecrest Labs</v>
+        <v>Qualtrics</v>
       </c>
       <c r="B5" t="str">
         <v>2</v>
@@ -1384,7 +1384,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Granite Peak Partners</v>
+        <v>Apple</v>
       </c>
       <c r="B6" t="str">
         <v>3</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Harborview Media</v>
+        <v>Nike</v>
       </c>
       <c r="B7" t="str">
         <v>3</v>
@@ -1419,7 +1419,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C12"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="28.83203125"/>
     <col min="2" max="2" customWidth="1" width="30.83203125"/>
@@ -1439,172 +1439,128 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Brightline Bank</v>
+        <v>Deloitte</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>deloitte.com</v>
       </c>
       <c r="C2" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2248%22%20r%3D%2238%22%20fill%3D%22%232e6fd8%22%2F%3E%3Cg%20style%3D%22color%3A%232e6fd8%22%3E%3Cpath%20d%3D%22M48%2022l28%2013v5H20v-5z%20M26%2044h7v22h-7z%20M44.5%2044h7v22h-7z%20M63%2044h7v22h-7z%20M20%2070h56v6H20z%22%20fill%3D%22%23fff%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Contoso Games</v>
+        <v>Delta Air Lines</v>
       </c>
       <c r="B3" t="str">
-        <v/>
+        <v>delta.com</v>
       </c>
       <c r="C3" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Cpath%20d%3D%22M48%208l35%2020v40L48%2088%2013%2068V28z%22%20fill%3D%22%232e6fd8%22%2F%3E%3Cg%20style%3D%22color%3A%232e6fd8%22%3E%3Crect%20x%3D%2220%22%20y%3D%2236%22%20width%3D%2256%22%20height%3D%2228%22%20rx%3D%2214%22%20fill%3D%22%23fff%22%2F%3E%3Cpath%20d%3D%22M32%2045v10M27%2050h10%22%20stroke%3D%22currentColor%22%20stroke-width%3D%224%22%20stroke-linecap%3D%22round%22%2F%3E%3Ccircle%20cx%3D%2260%22%20cy%3D%2247%22%20r%3D%223.5%22%20fill%3D%22currentColor%22%2F%3E%3Ccircle%20cx%3D%2267%22%20cy%3D%2254%22%20r%3D%223.5%22%20fill%3D%22currentColor%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Fieldstone Capital</v>
+        <v>Goldman Sachs</v>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>goldmansachs.com</v>
       </c>
       <c r="C4" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Crect%20x%3D%2210%22%20y%3D%2210%22%20width%3D%2276%22%20height%3D%2276%22%20rx%3D%226%22%20fill%3D%22%23c2255c%22%2F%3E%3Cg%20style%3D%22color%3A%23c2255c%22%3E%3Cpath%20d%3D%22M48%2022l28%2013v5H20v-5z%20M26%2044h7v22h-7z%20M44.5%2044h7v22h-7z%20M63%2044h7v22h-7z%20M20%2070h56v6H20z%22%20fill%3D%22%23fff%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Granite Peak Partners</v>
+        <v>Qualtrics</v>
       </c>
       <c r="B5" t="str">
-        <v/>
+        <v>qualtrics.com</v>
       </c>
       <c r="C5" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2248%22%20r%3D%2238%22%20fill%3D%22%230891b2%22%2F%3E%3Cg%20style%3D%22color%3A%230891b2%22%3E%3Cpath%20d%3D%22M48%2022l28%2013v5H20v-5z%20M26%2044h7v22h-7z%20M44.5%2044h7v22h-7z%20M63%2044h7v22h-7z%20M20%2070h56v6H20z%22%20fill%3D%22%23fff%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Harbor Tech Institute</v>
+        <v>Microsoft</v>
       </c>
       <c r="B6" t="str">
-        <v/>
+        <v>microsoft.com</v>
       </c>
       <c r="C6" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2248%22%20r%3D%2238%22%20fill%3D%22%23c2255c%22%2F%3E%3Cg%20style%3D%22color%3A%23c2255c%22%3E%3Cpath%20d%3D%22M48%2024l32%2014-32%2014-32-14z%20M28%2046v14c0%206%209%2012%2020%2012s20-6%2020-12V46l-20%209z%20M76%2040v18%22%20fill%3D%22%23fff%22%20stroke%3D%22%23fff%22%20stroke-width%3D%222%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Harbor Ventures</v>
+        <v>Google</v>
       </c>
       <c r="B7" t="str">
-        <v/>
+        <v>google.com</v>
       </c>
       <c r="C7" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Cpath%20d%3D%22M48%208l35%2020v40L48%2088%2013%2068V28z%22%20fill%3D%22%238b5cf6%22%2F%3E%3Cg%20style%3D%22color%3A%238b5cf6%22%3E%3Cpath%20d%3D%22M48%2018c10%208%2014%2020%2012%2034l-6%208H42l-6-8c-2-14%202-26%2012-34z%20M36%2056l-8%2012%2010-2z%20M60%2056l8%2012-10-2z%22%20fill%3D%22%23fff%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2238%22%20r%3D%225%22%20fill%3D%22currentColor%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Harborview Media</v>
+        <v>Adobe</v>
       </c>
       <c r="B8" t="str">
-        <v/>
+        <v>adobe.com</v>
       </c>
       <c r="C8" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Crect%20x%3D%2210%22%20y%3D%2210%22%20width%3D%2276%22%20height%3D%2276%22%20rx%3D%2220%22%20fill%3D%22%23b35c00%22%2F%3E%3Cg%20style%3D%22color%3A%23b35c00%22%3E%3Cpath%20d%3D%22M38%2028l32%2020-32%2020z%22%20fill%3D%22%23fff%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Independent</v>
+        <v>Apple</v>
       </c>
       <c r="B9" t="str">
-        <v/>
+        <v>apple.com</v>
       </c>
       <c r="C9" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Crect%20x%3D%2210%22%20y%3D%2210%22%20width%3D%2276%22%20height%3D%2276%22%20rx%3D%226%22%20fill%3D%22%231971c2%22%2F%3E%3Ctext%20x%3D%2248%22%20y%3D%2261%22%20font-size%3D%2234%22%20fill%3D%22%23fff%22%20font-family%3D%22system-ui%2C-apple-system%2CSegoe%20UI%2Csans-serif%22%20font-weight%3D%22700%22%20text-anchor%3D%22middle%22%3EIN%3C%2Ftext%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Keystone Health</v>
+        <v>Nike</v>
       </c>
       <c r="B10" t="str">
-        <v/>
+        <v>nike.com</v>
       </c>
       <c r="C10" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Crect%20x%3D%2210%22%20y%3D%2210%22%20width%3D%2276%22%20height%3D%2276%22%20rx%3D%226%22%20fill%3D%22%238b5cf6%22%2F%3E%3Cg%20style%3D%22color%3A%238b5cf6%22%3E%3Cpath%20d%3D%22M40%2022h16v18h18v16H56v18H40V56H22V40h18z%22%20fill%3D%22%23fff%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Lakeview State University</v>
+        <v>BYU</v>
       </c>
       <c r="B11" t="str">
-        <v/>
+        <v>byu.edu</v>
       </c>
       <c r="C11" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Cpath%20d%3D%22M48%208l35%2020v40L48%2088%2013%2068V28z%22%20fill%3D%22%231f9d6b%22%2F%3E%3Cg%20style%3D%22color%3A%231f9d6b%22%3E%3Cpath%20d%3D%22M48%2024l32%2014-32%2014-32-14z%20M28%2046v14c0%206%209%2012%2020%2012s20-6%2020-12V46l-20%209z%20M76%2040v18%22%20fill%3D%22%23fff%22%20stroke%3D%22%23fff%22%20stroke-width%3D%222%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Northwind Consulting</v>
+        <v>University of Utah</v>
       </c>
       <c r="B12" t="str">
-        <v/>
+        <v>admissions.utah.edu</v>
       </c>
       <c r="C12" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2248%22%20r%3D%2238%22%20fill%3D%22%23b35c00%22%2F%3E%3Cg%20style%3D%22color%3A%23b35c00%22%3E%3Cpath%20d%3D%22M24%2070V52h10v18z%20M43%2070V38h10v32z%20M62%2070V26h10v44z%22%20fill%3D%22%23fff%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Northwind Consulting, Inc.</v>
-      </c>
-      <c r="B13" t="str">
-        <v/>
-      </c>
-      <c r="C13" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Cpath%20d%3D%22M48%208l35%2020v40L48%2088%2013%2068V28z%22%20fill%3D%22%231f9d6b%22%2F%3E%3Cg%20style%3D%22color%3A%231f9d6b%22%3E%3Cpath%20d%3D%22M24%2070V52h10v18z%20M43%2070V38h10v32z%20M62%2070V26h10v44z%22%20fill%3D%22%23fff%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Pinecrest Labs</v>
-      </c>
-      <c r="B14" t="str">
-        <v/>
-      </c>
-      <c r="C14" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2248%22%20r%3D%2238%22%20fill%3D%22%23e8590c%22%2F%3E%3Cg%20style%3D%22color%3A%23e8590c%22%3E%3Cpath%20d%3D%22M40%2022h16v6h-3v14l17%2026c2%204-1%208-5%208H31c-4%200-7-4-5-8l17-26V28h-3z%22%20fill%3D%22%23fff%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Riverbend University</v>
-      </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Crect%20x%3D%2210%22%20y%3D%2210%22%20width%3D%2276%22%20height%3D%2276%22%20rx%3D%226%22%20fill%3D%22%23e8590c%22%2F%3E%3Cg%20style%3D%22color%3A%23e8590c%22%3E%3Cpath%20d%3D%22M48%2024l32%2014-32%2014-32-14z%20M28%2046v14c0%206%209%2012%2020%2012s20-6%2020-12V46l-20%209z%20M76%2040v18%22%20fill%3D%22%23fff%22%20stroke%3D%22%23fff%22%20stroke-width%3D%222%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Summit Airlines</v>
-      </c>
-      <c r="B16" t="str">
-        <v/>
-      </c>
-      <c r="C16" t="str">
-        <v>data:image/svg+xml;charset=utf-8,%3Csvg%20xmlns%3D%22http%3A%2F%2Fwww.w3.org%2F2000%2Fsvg%22%20width%3D%2296%22%20height%3D%2296%22%20viewBox%3D%220%200%2096%2096%22%3E%3Crect%20width%3D%2296%22%20height%3D%2296%22%20fill%3D%22%23fff%22%2F%3E%3Ccircle%20cx%3D%2248%22%20cy%3D%2248%22%20r%3D%2238%22%20fill%3D%22%238b5cf6%22%2F%3E%3Cg%20style%3D%22color%3A%238b5cf6%22%3E%3Cpath%20d%3D%22M48%2022l6%2020%2020%208v6l-20-4-2%2016%207%205v5l-11-3-11%203v-5l7-5-2-16-20%204v-6l20-8z%22%20fill%3D%22%23fff%22%2F%3E%3C%2Fg%3E%3C%2Fsvg%3E</v>
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1659,7 +1615,7 @@
         <v/>
       </c>
       <c r="E2" t="str">
-        <v>Northwind Consulting</v>
+        <v>Deloitte</v>
       </c>
       <c r="F2" t="str">
         <v>Senior Consultant</v>
@@ -1682,7 +1638,7 @@
         <v/>
       </c>
       <c r="E3" t="str">
-        <v>Northwind Consulting</v>
+        <v>Deloitte</v>
       </c>
       <c r="F3" t="str">
         <v>Manager</v>
@@ -1705,7 +1661,7 @@
         <v/>
       </c>
       <c r="E4" t="str">
-        <v>Contoso Games</v>
+        <v>Microsoft</v>
       </c>
       <c r="F4" t="str">
         <v>Product Manager</v>
@@ -1728,7 +1684,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Brightline Bank</v>
+        <v>Goldman Sachs</v>
       </c>
       <c r="F5" t="str">
         <v>Analyst</v>
@@ -1751,7 +1707,7 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>Brightline Bank</v>
+        <v>Goldman Sachs</v>
       </c>
       <c r="F6" t="str">
         <v>Risk Associate</v>
@@ -1774,7 +1730,7 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Brightline Bank</v>
+        <v>Goldman Sachs</v>
       </c>
       <c r="F7" t="str">
         <v>Product Owner</v>
@@ -1797,7 +1753,7 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Keystone Health</v>
+        <v>Adobe</v>
       </c>
       <c r="F8" t="str">
         <v>Strategy Manager</v>
@@ -1815,7 +1771,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="16.83203125"/>
     <col min="2" max="2" customWidth="1" width="30.83203125"/>
@@ -1837,9 +1793,17 @@
         <v>Alex Rivera</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Avatar style</v>
+      </c>
+      <c r="B3" t="str">
+        <v>notionists</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1873,7 +1837,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="110.83203125" customWidth="1"/>
@@ -1993,23 +1957,31 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Layout / Settings</v>
+        <v>Settings</v>
       </c>
       <c r="B15" t="str">
-        <v>Managed by the app (saved node positions, your name).</v>
+        <v>Your name, and Avatar style: initials, or notionists for illustrated avatars drawn in your browser.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
+        <v>Layout</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Managed by the app (saved node positions).</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
         <v>Privacy</v>
       </c>
-      <c r="B16" t="str">
+      <c r="B17" t="str">
         <v>Network Map runs entirely in your browser. This file is never uploaded anywhere.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/site/demo/demo_network.xlsx
+++ b/site/demo/demo_network.xlsx
@@ -467,7 +467,7 @@
         <v>Deloitte</v>
       </c>
       <c r="C2" t="str">
-        <v>BYU</v>
+        <v>Stanford University</v>
       </c>
       <c r="D2" t="str">
         <v>Senior Consultant</v>
@@ -479,7 +479,7 @@
         <v>https://example.com/in/jordan-lee</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>demo/photos/jordan-lee.jpg</v>
       </c>
       <c r="H2" t="str">
         <v/>
@@ -517,7 +517,7 @@
         <v>https://example.com/in/priya-shah</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>demo/photos/priya-shah.jpg</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -543,7 +543,7 @@
         <v>Microsoft</v>
       </c>
       <c r="C4" t="str">
-        <v>BYU</v>
+        <v>Stanford University</v>
       </c>
       <c r="D4" t="str">
         <v>Product Manager</v>
@@ -555,7 +555,7 @@
         <v>https://example.com/in/sofia-alvarez</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>demo/photos/sofia-alvarez.jpg</v>
       </c>
       <c r="H4" t="str">
         <v/>
@@ -581,7 +581,7 @@
         <v>Deloitte</v>
       </c>
       <c r="C5" t="str">
-        <v>Brigham Young University</v>
+        <v>Stanford</v>
       </c>
       <c r="D5" t="str">
         <v>Analyst</v>
@@ -593,7 +593,7 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>demo/photos/marcus-bell.jpg</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -631,7 +631,7 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>demo/photos/hana-kim.jpg</v>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -669,7 +669,7 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>demo/photos/ethan-brooks.jpg</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -707,7 +707,7 @@
         <v/>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>demo/photos/lena-novak.jpg</v>
       </c>
       <c r="H8" t="str">
         <v/>
@@ -733,7 +733,7 @@
         <v>Delta Air Lines</v>
       </c>
       <c r="C9" t="str">
-        <v>BYU</v>
+        <v>Stanford University</v>
       </c>
       <c r="D9" t="str">
         <v>Commercial Strategy Analyst</v>
@@ -745,7 +745,7 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>demo/photos/noah-carter.jpg</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -783,7 +783,7 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>demo/photos/grace-owens.jpg</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -809,7 +809,7 @@
         <v>Goldman Sachs</v>
       </c>
       <c r="C11" t="str">
-        <v>BYU</v>
+        <v>Stanford University</v>
       </c>
       <c r="D11" t="str">
         <v>Strategy Associate</v>
@@ -821,7 +821,7 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>demo/photos/daniel-ortiz.jpg</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -859,7 +859,7 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>demo/photos/mia-chen.jpg</v>
       </c>
       <c r="H12" t="str">
         <v/>
@@ -897,7 +897,7 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>demo/photos/owen-price.jpg</v>
       </c>
       <c r="H13" t="str">
         <v/>
@@ -935,7 +935,7 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>demo/photos/ava-thompson.jpg</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -973,7 +973,7 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>demo/photos/liam-walsh.jpg</v>
       </c>
       <c r="H15" t="str">
         <v/>
@@ -1011,7 +1011,7 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>demo/photos/rachel-green.jpg</v>
       </c>
       <c r="H16" t="str">
         <v>Jordan Lee</v>
@@ -1049,7 +1049,7 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>demo/photos/tom-nguyen.jpg</v>
       </c>
       <c r="H17" t="str">
         <v>Sofia Alvarez</v>
@@ -1087,7 +1087,7 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>demo/photos/isla-moore.jpg</v>
       </c>
       <c r="H18" t="str">
         <v>Sofia Alvarez</v>
@@ -1125,7 +1125,7 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>demo/photos/victor-hale.jpg</v>
       </c>
       <c r="H19" t="str">
         <v>Noah Carter</v>
@@ -1163,7 +1163,7 @@
         <v/>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>demo/photos/chloe-park.jpg</v>
       </c>
       <c r="H20" t="str">
         <v>Mia Chen</v>
@@ -1186,7 +1186,7 @@
         <v>Ben Foster</v>
       </c>
       <c r="B21" t="str">
-        <v>BYU</v>
+        <v>Stanford University</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -1201,7 +1201,7 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>demo/photos/ben-foster.jpg</v>
       </c>
       <c r="H21" t="str">
         <v>Daniel Ortiz</v>
@@ -1239,7 +1239,7 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>demo/photos/zoe-adams.jpg</v>
       </c>
       <c r="H22" t="str">
         <v>Liam Walsh</v>
@@ -1277,7 +1277,7 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v/>
+        <v>demo/photos/sam-rivera.jpg</v>
       </c>
       <c r="H23" t="str">
         <v>Zoe Adams</v>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>BYU</v>
+        <v>Stanford University</v>
       </c>
       <c r="B11" t="str">
-        <v>byu.edu</v>
+        <v>stanford.edu</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -1872,7 +1872,7 @@
         <v xml:space="preserve">  Company / School</v>
       </c>
       <c r="B4" t="str">
-        <v>3+ direct connections at one company or school become a group bubble. 'BYU' and 'Brigham Young University' count as the same.</v>
+        <v>3+ direct connections at one company or school become a group bubble. 'Stanford' and 'Stanford University' count as the same.</v>
       </c>
     </row>
     <row r="5">

--- a/site/demo/demo_network.xlsx
+++ b/site/demo/demo_network.xlsx
@@ -7,9 +7,11 @@
     <sheet name="Targets" sheetId="2" r:id="rId2"/>
     <sheet name="Companies" sheetId="3" r:id="rId3"/>
     <sheet name="LinkedIn Pool" sheetId="4" r:id="rId4"/>
-    <sheet name="Settings" sheetId="5" r:id="rId5"/>
-    <sheet name="Layout" sheetId="6" r:id="rId6" state="hidden"/>
-    <sheet name="How to use" sheetId="7" r:id="rId7"/>
+    <sheet name="Meetings" sheetId="5" r:id="rId5"/>
+    <sheet name="Tasks" sheetId="6" r:id="rId6"/>
+    <sheet name="Settings" sheetId="7" r:id="rId7"/>
+    <sheet name="Layout" sheetId="8" r:id="rId8" state="hidden"/>
+    <sheet name="How to use" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -526,7 +528,7 @@
         <v>46055</v>
       </c>
       <c r="J3" t="str">
-        <v>Contacted</v>
+        <v>Scheduled</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -678,7 +680,7 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>Follow Up</v>
+        <v>Scheduled</v>
       </c>
       <c r="K7" t="str">
         <v>Product</v>
@@ -792,7 +794,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>Contacted</v>
+        <v>Scheduled</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -1771,10 +1773,665 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:K10"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="16.83203125"/>
-    <col min="2" max="2" customWidth="1" width="30.83203125"/>
+    <col min="1" max="1" customWidth="1" width="22.83203125"/>
+    <col min="2" max="2" customWidth="1" width="12.83203125"/>
+    <col min="3" max="3" customWidth="1" width="8.83203125"/>
+    <col min="4" max="4" customWidth="1" width="8.83203125"/>
+    <col min="5" max="5" customWidth="1" width="16.83203125"/>
+    <col min="6" max="6" customWidth="1" width="12.83203125"/>
+    <col min="7" max="7" customWidth="1" width="40.83203125"/>
+    <col min="8" max="8" customWidth="1" width="30.83203125"/>
+    <col min="9" max="9" customWidth="1" width="22.83203125"/>
+    <col min="10" max="10" customWidth="1" width="30.83203125"/>
+    <col min="11" max="11" customWidth="1" width="16.83203125"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Person</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Date</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Start</v>
+      </c>
+      <c r="D1" t="str">
+        <v>End</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Method</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Next Step</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Calendar Event ID</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Link</v>
+      </c>
+      <c r="K1" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Liam Walsh</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46263</v>
+      </c>
+      <c r="C2" t="str">
+        <v>18:00</v>
+      </c>
+      <c r="D2" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Coffee Chat</v>
+      </c>
+      <c r="F2" t="str">
+        <v>In Person</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Caught up; he offered to introduce me to Zoe at Qualtrics.</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Ask Liam for the Zoe intro</v>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v>demo-m1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Sofia Alvarez</v>
+      </c>
+      <c r="B3" s="1">
+        <v>46273</v>
+      </c>
+      <c r="C3" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="D3" t="str">
+        <v>12:30</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Coffee Chat</v>
+      </c>
+      <c r="F3" t="str">
+        <v>In Person</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Marketplace roadmap, how PMs at Microsoft pick problems.</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Send thank-you</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>demo-m2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Jordan Lee</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46281</v>
+      </c>
+      <c r="C4" t="str">
+        <v>16:30</v>
+      </c>
+      <c r="D4" t="str">
+        <v>17:00</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Informational</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Zoom</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Walked through case interview prep and the strategy practice.</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Send resume for review</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v>https://zoom.us/j/0000000000</v>
+      </c>
+      <c r="K4" t="str">
+        <v>demo-m3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Noah Carter</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46288</v>
+      </c>
+      <c r="C5" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="D5" t="str">
+        <v>09:30</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Informational</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Phone</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Delta's commercial strategy team; APM-style rotation.</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Apply to the fall rotation</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v>demo-m4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Daniel Ortiz</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46291</v>
+      </c>
+      <c r="C6" t="str">
+        <v>15:00</v>
+      </c>
+      <c r="D6" t="str">
+        <v>15:30</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Coffee Chat</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Zoom</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Goldman strategy group; offered to connect me with Ben.</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Send thank-you</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v>https://zoom.us/j/0000000000</v>
+      </c>
+      <c r="K6" t="str">
+        <v>demo-m5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Priya Shah</v>
+      </c>
+      <c r="B7" s="1">
+        <v>46295</v>
+      </c>
+      <c r="C7" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="D7" t="str">
+        <v>10:30</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Coffee Chat</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Zoom</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v>https://zoom.us/j/0000000000</v>
+      </c>
+      <c r="K7" t="str">
+        <v>demo-m6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Grace Owens</v>
+      </c>
+      <c r="B8" s="1">
+        <v>46299</v>
+      </c>
+      <c r="C8" t="str">
+        <v>13:30</v>
+      </c>
+      <c r="D8" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Interview</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Teams</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Recruiter screen for the Delta internship.</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v>demo-m7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Mia Chen</v>
+      </c>
+      <c r="B9" s="1">
+        <v>46305</v>
+      </c>
+      <c r="C9" t="str">
+        <v>11:00</v>
+      </c>
+      <c r="D9" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Coffee Chat</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Google Meet</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v>https://meet.google.com/abc-defg-hij</v>
+      </c>
+      <c r="K9" t="str">
+        <v>demo-m8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Ethan Brooks</v>
+      </c>
+      <c r="B10" s="1">
+        <v>46318</v>
+      </c>
+      <c r="C10" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="D10" t="str">
+        <v>14:30</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Informational</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Zoom</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v>https://zoom.us/j/0000000000</v>
+      </c>
+      <c r="K10" t="str">
+        <v>demo-m9</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H10"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="40.83203125"/>
+    <col min="2" max="2" customWidth="1" width="22.83203125"/>
+    <col min="3" max="3" customWidth="1" width="20.83203125"/>
+    <col min="4" max="4" customWidth="1" width="12.83203125"/>
+    <col min="5" max="5" customWidth="1" width="8.83203125"/>
+    <col min="6" max="6" customWidth="1" width="12.83203125"/>
+    <col min="7" max="7" customWidth="1" width="20.83203125"/>
+    <col min="8" max="8" customWidth="1" width="16.83203125"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Task</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Person</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Company</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Due</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Done</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Created</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Source</v>
+      </c>
+      <c r="H1" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Send thank-you to Daniel Ortiz within 24 hrs</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Daniel Ortiz</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Goldman Sachs</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46292</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" s="1">
+        <v>46289</v>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v>demo-t1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Follow up with Hana Kim about the strategy practice</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Hana Kim</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="D3" s="1">
+        <v>46290</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" s="1">
+        <v>46287</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>demo-t2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Send resume to Jordan for review</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Jordan Lee</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="D4" s="1">
+        <v>46293</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" s="1">
+        <v>46290</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>demo-t3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Prepare questions for coffee chat with Priya</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Priya Shah</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="D5" s="1">
+        <v>46294</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" s="1">
+        <v>46290</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v>demo-t4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Ask Liam for the intro to Zoe Adams</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Liam Walsh</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Qualtrics</v>
+      </c>
+      <c r="D6" s="1">
+        <v>46296</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" s="1">
+        <v>46290</v>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v>demo-t5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Research Apple strategy &amp; operations roles</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v>Apple</v>
+      </c>
+      <c r="D7" s="1">
+        <v>46302</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" s="1">
+        <v>46290</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>demo-t6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Update resume with fall projects</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" s="1">
+        <v>46307</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" s="1">
+        <v>46290</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>demo-t7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Send thank-you to Noah Carter within 24 hrs</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Noah Carter</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Delta Air Lines</v>
+      </c>
+      <c r="D9" s="1">
+        <v>46289</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F9" s="1">
+        <v>46286</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v>demo-t8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Send thank-you to Sofia Alvarez within 24 hrs</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Sofia Alvarez</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Microsoft</v>
+      </c>
+      <c r="D10" s="1">
+        <v>46274</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F10" s="1">
+        <v>46271</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v>demo-t9</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B9"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="26.83203125"/>
+    <col min="2" max="2" customWidth="1" width="60.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1801,14 +2458,62 @@
         <v>notionists</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Your email</v>
+      </c>
+      <c r="B4" t="str">
+        <v>alex.rivera@example.com</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Meeting length (minutes)</v>
+      </c>
+      <c r="B5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Zoom link</v>
+      </c>
+      <c r="B6" t="str">
+        <v>https://zoom.us/j/0000000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Check-in every (days)</v>
+      </c>
+      <c r="B7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Invite message</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Hi {first name}, looking forward to our chat on {date} at {time}. {link}</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Demo base date</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-09-28</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C1"/>
   <cols>
@@ -1835,9 +2540,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="110.83203125" customWidth="1"/>
@@ -1957,31 +2662,47 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Settings</v>
+        <v>Meetings</v>
       </c>
       <c r="B15" t="str">
-        <v>Your name, and Avatar style: initials, or notionists for illustrated avatars drawn in your browser.</v>
+        <v>One row per meeting: Person, Date, Start, End, Type, Method, Notes, Next Step. The app fills this when you schedule or log a meeting.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Layout</v>
+        <v>Tasks</v>
       </c>
       <c r="B16" t="str">
-        <v>Managed by the app (saved node positions).</v>
+        <v>Your to-dos: Task, Person, Company, Due, Done. Scheduling a meeting adds a 'Send thank-you' task automatically.</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Your name and email, default meeting length, your Zoom link (used in invites), the invite message, and Avatar style (initials or notionists).</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Layout</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Managed by the app (saved node positions).</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
         <v>Privacy</v>
       </c>
-      <c r="B17" t="str">
+      <c r="B19" t="str">
         <v>Network Map runs entirely in your browser. This file is never uploaded anywhere.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B19"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/site/demo/demo_network.xlsx
+++ b/site/demo/demo_network.xlsx
@@ -407,11 +407,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:M23"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="22.83203125"/>
     <col min="2" max="2" customWidth="1" width="24.83203125"/>
-    <col min="3" max="3" customWidth="1" width="24.83203125"/>
+    <col min="3" max="3" customWidth="1" width="30.83203125"/>
     <col min="4" max="4" customWidth="1" width="24.83203125"/>
     <col min="5" max="5" customWidth="1" width="28.83203125"/>
     <col min="6" max="6" customWidth="1" width="36.83203125"/>
@@ -421,6 +421,7 @@
     <col min="10" max="10" customWidth="1" width="14.83203125"/>
     <col min="11" max="11" customWidth="1" width="20.83203125"/>
     <col min="12" max="12" customWidth="1" width="40.83203125"/>
+    <col min="13" max="13" customWidth="1" width="36.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -431,7 +432,7 @@
         <v>Company</v>
       </c>
       <c r="C1" t="str">
-        <v>School</v>
+        <v>Schools</v>
       </c>
       <c r="D1" t="str">
         <v>Role</v>
@@ -459,6 +460,9 @@
       </c>
       <c r="L1" t="str">
         <v>Notes</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Past Companies</v>
       </c>
     </row>
     <row r="2">
@@ -478,7 +482,7 @@
         <v>jordan.lee@example.com</v>
       </c>
       <c r="F2" t="str">
-        <v>https://example.com/in/jordan-lee</v>
+        <v>https://www.linkedin.com/in/jordan-lee-3f9a21</v>
       </c>
       <c r="G2" t="str">
         <v>demo/photos/jordan-lee.jpg</v>
@@ -497,6 +501,9 @@
       </c>
       <c r="L2" t="str">
         <v>Case interview tips</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -516,7 +523,7 @@
         <v>priya.shah@example.com</v>
       </c>
       <c r="F3" t="str">
-        <v>https://example.com/in/priya-shah</v>
+        <v>https://www.linkedin.com/in/priya-shah-77b0c4</v>
       </c>
       <c r="G3" t="str">
         <v>demo/photos/priya-shah.jpg</v>
@@ -534,6 +541,9 @@
         <v/>
       </c>
       <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v/>
       </c>
     </row>
@@ -554,7 +564,7 @@
         <v>sofia.alvarez@example.com</v>
       </c>
       <c r="F4" t="str">
-        <v>https://example.com/in/sofia-alvarez</v>
+        <v>https://www.linkedin.com/in/sofia-alvarez-5d2e18</v>
       </c>
       <c r="G4" t="str">
         <v>demo/photos/sofia-alvarez.jpg</v>
@@ -574,104 +584,113 @@
       <c r="L4" t="str">
         <v>Owns the marketplace roadmap</v>
       </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Marcus Bell</v>
+        <v>Noah Carter</v>
       </c>
       <c r="B5" t="str">
-        <v>Deloitte</v>
+        <v>Delta Air Lines</v>
       </c>
       <c r="C5" t="str">
-        <v>Stanford</v>
+        <v>Stanford University</v>
       </c>
       <c r="D5" t="str">
-        <v>Analyst</v>
+        <v>Commercial Strategy Analyst</v>
       </c>
       <c r="E5" t="str">
-        <v>marcus.bell@example.com</v>
+        <v>noah.carter@example.com</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>https://www.linkedin.com/in/noah-carter-a41b77</v>
       </c>
       <c r="G5" t="str">
-        <v>demo/photos/marcus-bell.jpg</v>
+        <v>demo/photos/noah-carter.jpg</v>
       </c>
       <c r="H5" t="str">
         <v/>
       </c>
-      <c r="I5" t="str">
-        <v/>
+      <c r="I5" s="1">
+        <v>46116</v>
       </c>
       <c r="J5" t="str">
         <v>Met</v>
       </c>
       <c r="K5" t="str">
-        <v>Consulting club</v>
+        <v/>
       </c>
       <c r="L5" t="str">
+        <v>Info session speaker</v>
+      </c>
+      <c r="M5" t="str">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Hana Kim</v>
+        <v>Mia Chen</v>
       </c>
       <c r="B6" t="str">
-        <v>Deloitte LLP</v>
+        <v>Google</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>University of Utah</v>
       </c>
       <c r="D6" t="str">
-        <v>Partner</v>
+        <v>Product Lead</v>
       </c>
       <c r="E6" t="str">
-        <v>hana.kim@example.com</v>
+        <v>mia.chen@example.com</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>https://www.linkedin.com/in/mia-chen-0c8e42</v>
       </c>
       <c r="G6" t="str">
-        <v>demo/photos/hana-kim.jpg</v>
+        <v>demo/photos/mia-chen.jpg</v>
       </c>
       <c r="H6" t="str">
         <v/>
       </c>
-      <c r="I6" t="str">
-        <v/>
+      <c r="I6" s="1">
+        <v>46192</v>
       </c>
       <c r="J6" t="str">
-        <v>To Reach Out</v>
+        <v>Met</v>
       </c>
       <c r="K6" t="str">
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Leads the strategy practice</v>
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Ethan Brooks</v>
+        <v>Marcus Bell</v>
       </c>
       <c r="B7" t="str">
-        <v>Microsoft</v>
+        <v>Deloitte</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>Stanford</v>
       </c>
       <c r="D7" t="str">
-        <v>Data Analyst</v>
+        <v>Analyst</v>
       </c>
       <c r="E7" t="str">
-        <v>ethan.brooks@example.com</v>
+        <v>marcus.bell@example.com</v>
       </c>
       <c r="F7" t="str">
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>demo/photos/ethan-brooks.jpg</v>
+        <v>demo/photos/marcus-bell.jpg</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -680,36 +699,39 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>Scheduled</v>
+        <v>Met</v>
       </c>
       <c r="K7" t="str">
-        <v>Product</v>
+        <v>Consulting club</v>
       </c>
       <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Lena Novak</v>
+        <v>Hana Kim</v>
       </c>
       <c r="B8" t="str">
-        <v>Microsoft</v>
+        <v>Deloitte LLP</v>
       </c>
       <c r="C8" t="str">
-        <v>University of Utah</v>
+        <v/>
       </c>
       <c r="D8" t="str">
-        <v>Program Manager</v>
+        <v>Partner</v>
       </c>
       <c r="E8" t="str">
-        <v>lena.novak@example.com</v>
+        <v>hana.kim@example.com</v>
       </c>
       <c r="F8" t="str">
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>demo/photos/lena-novak.jpg</v>
+        <v>demo/photos/hana-kim.jpg</v>
       </c>
       <c r="H8" t="str">
         <v/>
@@ -721,33 +743,36 @@
         <v>To Reach Out</v>
       </c>
       <c r="K8" t="str">
-        <v>Product</v>
+        <v/>
       </c>
       <c r="L8" t="str">
+        <v>Leads the strategy practice</v>
+      </c>
+      <c r="M8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Noah Carter</v>
+        <v>Ethan Brooks</v>
       </c>
       <c r="B9" t="str">
-        <v>Delta Air Lines</v>
+        <v>Microsoft</v>
       </c>
       <c r="C9" t="str">
-        <v>Stanford University</v>
+        <v/>
       </c>
       <c r="D9" t="str">
-        <v>Commercial Strategy Analyst</v>
+        <v>Data Analyst</v>
       </c>
       <c r="E9" t="str">
-        <v>noah.carter@example.com</v>
+        <v>ethan.brooks@example.com</v>
       </c>
       <c r="F9" t="str">
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>demo/photos/noah-carter.jpg</v>
+        <v>demo/photos/ethan-brooks.jpg</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -756,36 +781,39 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>Met</v>
+        <v>Scheduled</v>
       </c>
       <c r="K9" t="str">
-        <v/>
+        <v>Product</v>
       </c>
       <c r="L9" t="str">
-        <v>Info session speaker</v>
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Grace Owens</v>
+        <v>Lena Novak</v>
       </c>
       <c r="B10" t="str">
-        <v>Delta Air Lines</v>
+        <v>Microsoft</v>
       </c>
       <c r="C10" t="str">
-        <v/>
+        <v>University of Utah</v>
       </c>
       <c r="D10" t="str">
-        <v>Recruiter</v>
+        <v>Program Manager</v>
       </c>
       <c r="E10" t="str">
-        <v>grace.owens@example.com</v>
+        <v>lena.novak@example.com</v>
       </c>
       <c r="F10" t="str">
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>demo/photos/grace-owens.jpg</v>
+        <v>demo/photos/lena-novak.jpg</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -794,36 +822,39 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>Scheduled</v>
+        <v>To Reach Out</v>
       </c>
       <c r="K10" t="str">
-        <v/>
+        <v>Product</v>
       </c>
       <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Daniel Ortiz</v>
+        <v>Grace Owens</v>
       </c>
       <c r="B11" t="str">
-        <v>Goldman Sachs</v>
+        <v>Delta Air Lines</v>
       </c>
       <c r="C11" t="str">
-        <v>Stanford University</v>
+        <v/>
       </c>
       <c r="D11" t="str">
-        <v>Strategy Associate</v>
+        <v>Recruiter</v>
       </c>
       <c r="E11" t="str">
-        <v>daniel.ortiz@example.com</v>
+        <v>grace.owens@example.com</v>
       </c>
       <c r="F11" t="str">
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>demo/photos/daniel-ortiz.jpg</v>
+        <v>demo/photos/grace-owens.jpg</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -832,36 +863,39 @@
         <v/>
       </c>
       <c r="J11" t="str">
-        <v>Met</v>
+        <v>Scheduled</v>
       </c>
       <c r="K11" t="str">
         <v/>
       </c>
       <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Mia Chen</v>
+        <v>Daniel Ortiz</v>
       </c>
       <c r="B12" t="str">
-        <v>Google</v>
+        <v>Goldman Sachs</v>
       </c>
       <c r="C12" t="str">
-        <v>University of Utah</v>
+        <v>Stanford University</v>
       </c>
       <c r="D12" t="str">
-        <v>Product Lead</v>
+        <v>Strategy Associate</v>
       </c>
       <c r="E12" t="str">
-        <v>mia.chen@example.com</v>
+        <v>daniel.ortiz@example.com</v>
       </c>
       <c r="F12" t="str">
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>demo/photos/mia-chen.jpg</v>
+        <v>demo/photos/daniel-ortiz.jpg</v>
       </c>
       <c r="H12" t="str">
         <v/>
@@ -876,6 +910,9 @@
         <v/>
       </c>
       <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
         <v/>
       </c>
     </row>
@@ -916,6 +953,9 @@
       <c r="L13" t="str">
         <v/>
       </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -954,6 +994,9 @@
       <c r="L14" t="str">
         <v/>
       </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -992,6 +1035,9 @@
       <c r="L15" t="str">
         <v>Old roommate</v>
       </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1030,6 +1076,9 @@
       <c r="L16" t="str">
         <v>Jordan offered an intro</v>
       </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -1068,6 +1117,9 @@
       <c r="L17" t="str">
         <v/>
       </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -1106,6 +1158,9 @@
       <c r="L18" t="str">
         <v/>
       </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -1144,6 +1199,9 @@
       <c r="L19" t="str">
         <v/>
       </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1182,6 +1240,9 @@
       <c r="L20" t="str">
         <v/>
       </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1220,6 +1281,9 @@
       <c r="L21" t="str">
         <v/>
       </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1258,6 +1322,9 @@
       <c r="L22" t="str">
         <v/>
       </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1296,10 +1363,13 @@
       <c r="L23" t="str">
         <v>3rd-degree example</v>
       </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M23"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1447,7 +1517,7 @@
         <v>deloitte.com</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>demo/logos/deloitte.svg</v>
       </c>
     </row>
     <row r="3">
@@ -1458,7 +1528,7 @@
         <v>delta.com</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>demo/logos/delta.svg</v>
       </c>
     </row>
     <row r="4">
@@ -1469,7 +1539,7 @@
         <v>goldmansachs.com</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>demo/logos/goldman-sachs.svg</v>
       </c>
     </row>
     <row r="5">
@@ -1480,7 +1550,7 @@
         <v>qualtrics.com</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>demo/logos/qualtrics.svg</v>
       </c>
     </row>
     <row r="6">
@@ -1491,7 +1561,7 @@
         <v>microsoft.com</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>demo/logos/microsoft.svg</v>
       </c>
     </row>
     <row r="7">
@@ -1502,7 +1572,7 @@
         <v>google.com</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>demo/logos/google.svg</v>
       </c>
     </row>
     <row r="8">
@@ -1513,7 +1583,7 @@
         <v>adobe.com</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>demo/logos/adobe.svg</v>
       </c>
     </row>
     <row r="9">
@@ -1524,7 +1594,7 @@
         <v>apple.com</v>
       </c>
       <c r="C9" t="str">
-        <v/>
+        <v>demo/logos/apple.svg</v>
       </c>
     </row>
     <row r="10">
@@ -1535,7 +1605,7 @@
         <v>nike.com</v>
       </c>
       <c r="C10" t="str">
-        <v/>
+        <v>demo/logos/nike.svg</v>
       </c>
     </row>
     <row r="11">
@@ -1546,7 +1616,7 @@
         <v>stanford.edu</v>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>demo/logos/stanford.svg</v>
       </c>
     </row>
     <row r="12">
@@ -1557,7 +1627,7 @@
         <v>admissions.utah.edu</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>demo/logos/university-of-utah.svg</v>
       </c>
     </row>
   </sheetData>
@@ -1569,7 +1639,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G27"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="14.83203125"/>
     <col min="2" max="2" customWidth="1" width="16.83203125"/>
@@ -1611,7 +1681,7 @@
         <v>Lee</v>
       </c>
       <c r="C2" t="str">
-        <v>https://example.com/in/jordan-lee</v>
+        <v>https://www.linkedin.com/in/jordan-lee-3f9a21</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -1634,7 +1704,7 @@
         <v>Shah</v>
       </c>
       <c r="C3" t="str">
-        <v>https://example.com/in/priya-shah</v>
+        <v>https://www.linkedin.com/in/priya-shah-77b0c4</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -1657,7 +1727,7 @@
         <v>Alvarez</v>
       </c>
       <c r="C4" t="str">
-        <v>https://example.com/in/sofia-alvarez</v>
+        <v>https://www.linkedin.com/in/sofia-alvarez-5d2e18</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -1674,59 +1744,59 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Kai</v>
+        <v>Noah</v>
       </c>
       <c r="B5" t="str">
-        <v>Morgan</v>
+        <v>Carter</v>
       </c>
       <c r="C5" t="str">
-        <v>https://example.com/in/kai-morgan</v>
+        <v>https://www.linkedin.com/in/noah-carter-a41b77</v>
       </c>
       <c r="D5" t="str">
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Goldman Sachs</v>
+        <v>Delta Air Lines</v>
       </c>
       <c r="F5" t="str">
-        <v>Analyst</v>
+        <v>Commercial Strategy Analyst</v>
       </c>
       <c r="G5" s="1">
-        <v>46037</v>
+        <v>46116</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Elena</v>
+        <v>Mia</v>
       </c>
       <c r="B6" t="str">
-        <v>Rossi</v>
+        <v>Chen</v>
       </c>
       <c r="C6" t="str">
-        <v>https://example.com/in/elena-rossi</v>
+        <v>https://www.linkedin.com/in/mia-chen-0c8e42</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>mia.chen@example.com</v>
       </c>
       <c r="E6" t="str">
-        <v>Goldman Sachs</v>
+        <v>Google</v>
       </c>
       <c r="F6" t="str">
-        <v>Risk Associate</v>
+        <v>Product Lead</v>
       </c>
       <c r="G6" s="1">
-        <v>46145</v>
+        <v>46192</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Theo</v>
+        <v>Kai</v>
       </c>
       <c r="B7" t="str">
-        <v>Grant</v>
+        <v>Morgan</v>
       </c>
       <c r="C7" t="str">
-        <v>https://example.com/in/theo-grant</v>
+        <v>https://www.linkedin.com/in/kai-morgan-2b6f90</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -1735,38 +1805,475 @@
         <v>Goldman Sachs</v>
       </c>
       <c r="F7" t="str">
-        <v>Product Owner</v>
+        <v>Analyst</v>
       </c>
       <c r="G7" s="1">
-        <v>46182</v>
+        <v>46037</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
+        <v>Elena</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Rossi</v>
+      </c>
+      <c r="C8" t="str">
+        <v>https://www.linkedin.com/in/elena-rossi-91cd03</v>
+      </c>
+      <c r="D8" t="str">
+        <v>elena.rossi@example.com</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Goldman Sachs</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Risk Associate</v>
+      </c>
+      <c r="G8" s="1">
+        <v>46145</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Theo</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Grant</v>
+      </c>
+      <c r="C9" t="str">
+        <v>https://www.linkedin.com/in/theo-grant-e7a215</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v>Goldman Sachs</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Product Owner</v>
+      </c>
+      <c r="G9" s="1">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
         <v>Nora</v>
       </c>
-      <c r="B8" t="str">
+      <c r="B10" t="str">
         <v>Singh</v>
       </c>
-      <c r="C8" t="str">
-        <v>https://example.com/in/nora-singh</v>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
+      <c r="C10" t="str">
+        <v>https://www.linkedin.com/in/nora-singh-48fa6b</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
         <v>Adobe</v>
       </c>
-      <c r="F8" t="str">
+      <c r="F10" t="str">
         <v>Strategy Manager</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G10" s="1">
         <v>46233</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Maya</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Patel</v>
+      </c>
+      <c r="C11" t="str">
+        <v>https://www.linkedin.com/in/maya-patel-6a1d3e</v>
+      </c>
+      <c r="D11" t="str">
+        <v>maya.patel@example.com</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Apple</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Operations Program Manager</v>
+      </c>
+      <c r="G11" s="1">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Lucas</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Bennett</v>
+      </c>
+      <c r="C12" t="str">
+        <v>https://www.linkedin.com/in/lucas-bennett-c03f59</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v>Apple</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Product Marketing Manager</v>
+      </c>
+      <c r="G12" s="1">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Aisha</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Rahman</v>
+      </c>
+      <c r="C13" t="str">
+        <v>https://www.linkedin.com/in/aisha-rahman-8e47b2</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v>Nike</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Senior Analyst - Consumer Insights</v>
+      </c>
+      <c r="G13" s="1">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Diego</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Santos</v>
+      </c>
+      <c r="C14" t="str">
+        <v>https://www.linkedin.com/in/diego-santos-1f9c6d</v>
+      </c>
+      <c r="D14" t="str">
+        <v>diego.santos@example.com</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Nike</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Strategy &amp; Planning Associate</v>
+      </c>
+      <c r="G14" s="1">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Hannah</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Brooks</v>
+      </c>
+      <c r="C15" t="str">
+        <v>https://www.linkedin.com/in/hannah-brooks-5b27a0</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v>Microsoft</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Program Manager</v>
+      </c>
+      <c r="G15" s="1">
+        <v>46160</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Omar</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Haddad</v>
+      </c>
+      <c r="C16" t="str">
+        <v>https://www.linkedin.com/in/omar-haddad-3d81fe</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v>Microsoft</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Software Engineer</v>
+      </c>
+      <c r="G16" s="1">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Grace</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Liu</v>
+      </c>
+      <c r="C17" t="str">
+        <v>https://www.linkedin.com/in/grace-liu-9a0e6c</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v>Google</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Associate Product Manager</v>
+      </c>
+      <c r="G17" s="1">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Ryan</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Doyle</v>
+      </c>
+      <c r="C18" t="str">
+        <v>https://www.linkedin.com/in/ryan-doyle-4c5b12</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v>Google</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Strategy &amp; Operations Manager</v>
+      </c>
+      <c r="G18" s="1">
+        <v>46110</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Chloe</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Martin</v>
+      </c>
+      <c r="C19" t="str">
+        <v>https://www.linkedin.com/in/chloe-martin-b8d4a7</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="G19" s="1">
+        <v>46038</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Ben</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Walker</v>
+      </c>
+      <c r="C20" t="str">
+        <v>https://www.linkedin.com/in/ben-walker-0e3c95</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Senior Manager</v>
+      </c>
+      <c r="G20" s="1">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Isabel</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Cruz</v>
+      </c>
+      <c r="C21" t="str">
+        <v>https://www.linkedin.com/in/isabel-cruz-7f2a48</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v>Delta Air Lines</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Network Planning Analyst</v>
+      </c>
+      <c r="G21" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Ethan</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Park</v>
+      </c>
+      <c r="C22" t="str">
+        <v>https://www.linkedin.com/in/ethan-park-2d6e91</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v>Delta Air Lines</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Revenue Management Analyst</v>
+      </c>
+      <c r="G22" s="1">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Zara</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Ahmed</v>
+      </c>
+      <c r="C23" t="str">
+        <v>https://www.linkedin.com/in/zara-ahmed-c4b710</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v>Qualtrics</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Customer Success Manager</v>
+      </c>
+      <c r="G23" s="1">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Leo</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Fischer</v>
+      </c>
+      <c r="C24" t="str">
+        <v>https://www.linkedin.com/in/leo-fischer-6e0d2b</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v>Qualtrics</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Product Designer</v>
+      </c>
+      <c r="G24" s="1">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Emma</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Nguyen</v>
+      </c>
+      <c r="C25" t="str">
+        <v>https://www.linkedin.com/in/emma-nguyen-93a5f4</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v>Adobe</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Product Manager</v>
+      </c>
+      <c r="G25" s="1">
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Jack</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Sullivan</v>
+      </c>
+      <c r="C26" t="str">
+        <v>https://www.linkedin.com/in/jack-sullivan-1b8e07</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v>Stanford University</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Career Advisor</v>
+      </c>
+      <c r="G26" s="1">
+        <v>45991</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Olivia</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Reed</v>
+      </c>
+      <c r="C27" t="str">
+        <v>https://www.linkedin.com/in/olivia-reed-58c9d3</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v>University of Utah</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Program Coordinator</v>
+      </c>
+      <c r="G27" s="1">
+        <v>46003</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G27"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2003,7 +2510,7 @@
         <v>Priya Shah</v>
       </c>
       <c r="B7" s="1">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="C7" t="str">
         <v>10:00</v>

--- a/site/demo/demo_network.xlsx
+++ b/site/demo/demo_network.xlsx
@@ -9,9 +9,10 @@
     <sheet name="LinkedIn Pool" sheetId="4" r:id="rId4"/>
     <sheet name="Meetings" sheetId="5" r:id="rId5"/>
     <sheet name="Tasks" sheetId="6" r:id="rId6"/>
-    <sheet name="Settings" sheetId="7" r:id="rId7"/>
-    <sheet name="Layout" sheetId="8" r:id="rId8" state="hidden"/>
-    <sheet name="How to use" sheetId="9" r:id="rId9"/>
+    <sheet name="Me" sheetId="7" r:id="rId7"/>
+    <sheet name="Settings" sheetId="8" r:id="rId8"/>
+    <sheet name="Layout" sheetId="9" r:id="rId9" state="hidden"/>
+    <sheet name="How to use" sheetId="10" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
@@ -1374,6 +1375,173 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B19"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="110.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Sheet / column</v>
+      </c>
+      <c r="B1" t="str">
+        <v>What to put there</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>People</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Everyone on your map. Only Name is required.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v xml:space="preserve">  Name</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Full name, spelled the same way everywhere.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v xml:space="preserve">  Company / School</v>
+      </c>
+      <c r="B4" t="str">
+        <v>3+ direct connections at one company or school become a group bubble. 'Stanford' and 'Stanford University' count as the same.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v xml:space="preserve">  Email</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Shown in the details panel with a copy button.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v xml:space="preserve">  LinkedIn URL</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Their profile link. Double-click them on the map to open it.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v xml:space="preserve">  Photo</v>
+      </c>
+      <c r="B7" t="str">
+        <v>An image link, or use 'Add photo' in the app (it stores a small picture here). LinkedIn exports don't include photos.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v xml:space="preserve">  Connected Through</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Leave BLANK if you know them directly. Otherwise put the name of the person who connects you; they appear as a 2nd-degree connection.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v xml:space="preserve">  Connected On</v>
+      </c>
+      <c r="B9" t="str">
+        <v>The date you connected (filled in from LinkedIn).</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v xml:space="preserve">  Status</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Met / Contacted / To Reach Out / Follow Up / Referral.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v xml:space="preserve">  Tags, Notes</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Anything you want to remember. Tags are comma-separated.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Targets</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Companies you want to work at. Priority (1 = highest) and Stage (Researching / Networking / Applied / Interviewing / Offer) are optional.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Companies</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Optional. Set a company's Website (e.g. byu.edu) if its logo comes out wrong, or put an image link in Logo.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>LinkedIn Pool</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Filled by 'Import LinkedIn' from your Connections.csv. These people are NOT on the map until you add them.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Meetings</v>
+      </c>
+      <c r="B15" t="str">
+        <v>One row per meeting: Person, Date, Start, End, Type, Method, Notes, Next Step. The app fills this when you schedule or log a meeting.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Tasks</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Your to-dos: Task, Person, Company, Due, Done. Scheduling a meeting adds a 'Send thank-you' task automatically.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Your name and email, default meeting length, your Zoom link (used in invites), the invite message, and Avatar style (initials or notionists).</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Layout</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Managed by the app (saved node positions).</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Privacy</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Network Map runs entirely in your browser. This file is never uploaded anywhere.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D7"/>
@@ -2935,6 +3103,118 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B12"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="22.83203125"/>
+    <col min="2" max="2" customWidth="1" width="70.83203125"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Name</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Alex Rivera</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Photo</v>
+      </c>
+      <c r="B3" t="str">
+        <v>demo/photos/alex-rivera.jpg</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Role</v>
+      </c>
+      <c r="B4" t="str">
+        <v>MBA Candidate</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Headline</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Stanford MBA '27 · Looking for strategy &amp; product roles</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Company</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Schools</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Stanford University (2025–2027); University of Utah (2016–2020)</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Past Companies</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Delta Air Lines (2020–2022); Adobe (2022–2025)</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Email</v>
+      </c>
+      <c r="B9" t="str">
+        <v>alex.rivera@example.com</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>LinkedIn URL</v>
+      </c>
+      <c r="B10" t="str">
+        <v>https://www.linkedin.com/in/alex-rivera-demo</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Location</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Palo Alto, California</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
+        <v>What I'm looking for</v>
+      </c>
+      <c r="B12" t="str" xml:space="preserve">
+        <v xml:space="preserve">Summer 2027 internships in strategy or product at consumer-tech and airline companies.
+Happy to swap notes on case prep and product sense interviews.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B9"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="26.83203125"/>
@@ -3020,7 +3300,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C1"/>
   <cols>
@@ -3045,171 +3325,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
-  <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="110.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Sheet / column</v>
-      </c>
-      <c r="B1" t="str">
-        <v>What to put there</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>People</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Everyone on your map. Only Name is required.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v xml:space="preserve">  Name</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Full name, spelled the same way everywhere.</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v xml:space="preserve">  Company / School</v>
-      </c>
-      <c r="B4" t="str">
-        <v>3+ direct connections at one company or school become a group bubble. 'Stanford' and 'Stanford University' count as the same.</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v xml:space="preserve">  Email</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Shown in the details panel with a copy button.</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v xml:space="preserve">  LinkedIn URL</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Their profile link. Double-click them on the map to open it.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v xml:space="preserve">  Photo</v>
-      </c>
-      <c r="B7" t="str">
-        <v>An image link, or use 'Add photo' in the app (it stores a small picture here). LinkedIn exports don't include photos.</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v xml:space="preserve">  Connected Through</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Leave BLANK if you know them directly. Otherwise put the name of the person who connects you; they appear as a 2nd-degree connection.</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v xml:space="preserve">  Connected On</v>
-      </c>
-      <c r="B9" t="str">
-        <v>The date you connected (filled in from LinkedIn).</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v xml:space="preserve">  Status</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Met / Contacted / To Reach Out / Follow Up / Referral.</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v xml:space="preserve">  Tags, Notes</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Anything you want to remember. Tags are comma-separated.</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Targets</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Companies you want to work at. Priority (1 = highest) and Stage (Researching / Networking / Applied / Interviewing / Offer) are optional.</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Companies</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Optional. Set a company's Website (e.g. byu.edu) if its logo comes out wrong, or put an image link in Logo.</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>LinkedIn Pool</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Filled by 'Import LinkedIn' from your Connections.csv. These people are NOT on the map until you add them.</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Meetings</v>
-      </c>
-      <c r="B15" t="str">
-        <v>One row per meeting: Person, Date, Start, End, Type, Method, Notes, Next Step. The app fills this when you schedule or log a meeting.</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Tasks</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Your to-dos: Task, Person, Company, Due, Done. Scheduling a meeting adds a 'Send thank-you' task automatically.</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Settings</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Your name and email, default meeting length, your Zoom link (used in invites), the invite message, and Avatar style (initials or notionists).</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Layout</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Managed by the app (saved node positions).</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Privacy</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Network Map runs entirely in your browser. This file is never uploaded anywhere.</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B19"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/site/demo/demo_network.xlsx
+++ b/site/demo/demo_network.xlsx
@@ -9,10 +9,11 @@
     <sheet name="LinkedIn Pool" sheetId="4" r:id="rId4"/>
     <sheet name="Meetings" sheetId="5" r:id="rId5"/>
     <sheet name="Tasks" sheetId="6" r:id="rId6"/>
-    <sheet name="Me" sheetId="7" r:id="rId7"/>
-    <sheet name="Settings" sheetId="8" r:id="rId8"/>
-    <sheet name="Layout" sheetId="9" r:id="rId9" state="hidden"/>
-    <sheet name="How to use" sheetId="10" r:id="rId10"/>
+    <sheet name="Connections" sheetId="7" r:id="rId7"/>
+    <sheet name="Me" sheetId="8" r:id="rId8"/>
+    <sheet name="Settings" sheetId="9" r:id="rId9"/>
+    <sheet name="Layout" sheetId="10" r:id="rId10" state="hidden"/>
+    <sheet name="How to use" sheetId="11" r:id="rId11"/>
   </sheets>
 </workbook>
 </file>
@@ -1377,7 +1378,34 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:C1"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="36.83203125"/>
+    <col min="2" max="2" customWidth="1" width="8.83203125"/>
+    <col min="3" max="3" customWidth="1" width="8.83203125"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Node</v>
+      </c>
+      <c r="B1" t="str">
+        <v>X</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B21"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="110.83203125" customWidth="1"/>
@@ -1497,47 +1525,63 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Meetings</v>
+        <v>Connections</v>
       </c>
       <c r="B15" t="str">
-        <v>One row per meeting: Person, Date, Start, End, Type, Method, Notes, Next Step. The app fills this when you schedule or log a meeting.</v>
+        <v>Who knows whom: Person A, Person B, Type (Introduced me, Coworker, Classmate, Friend, Mentor, or anything else), Notes. 'Introduced me' means A introduced you to B; it's kept in sync with People → Connected Through.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Tasks</v>
+        <v>Me</v>
       </c>
       <c r="B16" t="str">
-        <v>Your to-dos: Task, Person, Company, Due, Done. Scheduling a meeting adds a 'Send thank-you' task automatically.</v>
+        <v>Your own profile: photo, role, schools, past companies, what you're looking for.</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Settings</v>
+        <v>Meetings</v>
       </c>
       <c r="B17" t="str">
-        <v>Your name and email, default meeting length, your Zoom link (used in invites), the invite message, and Avatar style (initials or notionists).</v>
+        <v>One row per meeting: Person, Date, Start, End, Type, Method, Notes, Next Step. The app fills this when you schedule or log a meeting.</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Layout</v>
+        <v>Tasks</v>
       </c>
       <c r="B18" t="str">
-        <v>Managed by the app (saved node positions).</v>
+        <v>Your to-dos: Task, Person, Company, Due, Done. Scheduling a meeting adds a 'Send thank-you' task automatically.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Your name and email, default meeting length, your Zoom link (used in invites), the invite message, and Avatar style (initials or notionists).</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Layout</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Managed by the app (saved node positions).</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
         <v>Privacy</v>
       </c>
-      <c r="B19" t="str">
+      <c r="B21" t="str">
         <v>Network Map runs entirely in your browser. This file is never uploaded anywhere.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3103,6 +3147,205 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D13"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="24.83203125"/>
+    <col min="2" max="2" customWidth="1" width="24.83203125"/>
+    <col min="3" max="3" customWidth="1" width="16.83203125"/>
+    <col min="4" max="4" customWidth="1" width="40.83203125"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Person A</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Person B</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Jordan Lee</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Rachel Green</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Introduced me</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Sofia Alvarez</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Tom Nguyen</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Introduced me</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Sofia Alvarez</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Isla Moore</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Introduced me</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Noah Carter</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Victor Hale</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Introduced me</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Mia Chen</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Chloe Park</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Introduced me</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Daniel Ortiz</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Ben Foster</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Introduced me</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Liam Walsh</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Zoe Adams</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Introduced me</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Zoe Adams</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Sam Rivera</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Introduced me</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Liam Walsh</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Mia Chen</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Friend</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Roommates' friend group</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Sofia Alvarez</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Daniel Ortiz</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Classmate</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Stanford, same product club</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Jordan Lee</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Owen Price</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Mentor</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Jordan mentors Owen on case interviews</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Hana Kim</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Ethan Brooks</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Coworker</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Worked together at Deloitte</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B12"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="22.83203125"/>
@@ -3213,7 +3456,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B9"/>
   <cols>
@@ -3298,31 +3541,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1"/>
-  <cols>
-    <col min="1" max="1" customWidth="1" width="36.83203125"/>
-    <col min="2" max="2" customWidth="1" width="8.83203125"/>
-    <col min="3" max="3" customWidth="1" width="8.83203125"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Node</v>
-      </c>
-      <c r="B1" t="str">
-        <v>X</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/site/demo/demo_network.xlsx
+++ b/site/demo/demo_network.xlsx
@@ -1576,7 +1576,7 @@
         <v>Privacy</v>
       </c>
       <c r="B21" t="str">
-        <v>Network Map runs entirely in your browser. This file is never uploaded anywhere.</v>
+        <v>Orbit runs entirely in your browser. This file is never uploaded anywhere.</v>
       </c>
     </row>
   </sheetData>

--- a/site/demo/demo_network.xlsx
+++ b/site/demo/demo_network.xlsx
@@ -4,17 +4,23 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="People" sheetId="1" r:id="rId1"/>
-    <sheet name="Targets" sheetId="2" r:id="rId2"/>
-    <sheet name="Companies" sheetId="3" r:id="rId3"/>
-    <sheet name="LinkedIn Pool" sheetId="4" r:id="rId4"/>
-    <sheet name="Meetings" sheetId="5" r:id="rId5"/>
-    <sheet name="Tasks" sheetId="6" r:id="rId6"/>
-    <sheet name="Connections" sheetId="7" r:id="rId7"/>
-    <sheet name="Me" sheetId="8" r:id="rId8"/>
-    <sheet name="Settings" sheetId="9" r:id="rId9"/>
-    <sheet name="Layout" sheetId="10" r:id="rId10" state="hidden"/>
-    <sheet name="How to use" sheetId="11" r:id="rId11"/>
+    <sheet name="How to use" sheetId="2" r:id="rId2"/>
+    <sheet name="Targets" sheetId="3" r:id="rId3"/>
+    <sheet name="Companies" sheetId="4" r:id="rId4"/>
+    <sheet name="LinkedIn Pool" sheetId="5" r:id="rId5"/>
+    <sheet name="Meetings" sheetId="6" r:id="rId6"/>
+    <sheet name="Tasks" sheetId="7" r:id="rId7"/>
+    <sheet name="Connections" sheetId="8" r:id="rId8"/>
+    <sheet name="Experience" sheetId="9" r:id="rId9"/>
+    <sheet name="Education" sheetId="10" r:id="rId10"/>
+    <sheet name="Me" sheetId="11" r:id="rId11"/>
+    <sheet name="Settings" sheetId="12" r:id="rId12"/>
+    <sheet name="Layout" sheetId="13" r:id="rId13" state="hidden"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">People!$A$1:$U$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'LinkedIn Pool'!$A$1:$G$27</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -46,8 +52,16 @@
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
     <numFmt numFmtId="60" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -75,9 +89,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -409,62 +429,94 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:U23"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="22.83203125"/>
-    <col min="2" max="2" customWidth="1" width="24.83203125"/>
-    <col min="3" max="3" customWidth="1" width="30.83203125"/>
-    <col min="4" max="4" customWidth="1" width="24.83203125"/>
-    <col min="5" max="5" customWidth="1" width="28.83203125"/>
-    <col min="6" max="6" customWidth="1" width="36.83203125"/>
-    <col min="7" max="7" customWidth="1" width="14.83203125"/>
-    <col min="8" max="8" customWidth="1" width="22.83203125"/>
-    <col min="9" max="9" customWidth="1" width="14.83203125"/>
-    <col min="10" max="10" customWidth="1" width="14.83203125"/>
-    <col min="11" max="11" customWidth="1" width="20.83203125"/>
-    <col min="12" max="12" customWidth="1" width="40.83203125"/>
-    <col min="13" max="13" customWidth="1" width="36.83203125"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="21.83203125" customWidth="1"/>
+    <col min="3" max="3" width="21.83203125" customWidth="1"/>
+    <col min="4" max="4" width="29.83203125" customWidth="1"/>
+    <col min="5" max="5" width="27.83203125" customWidth="1"/>
+    <col min="6" max="6" width="50.83203125" customWidth="1"/>
+    <col min="7" max="7" width="31.83203125" customWidth="1"/>
+    <col min="8" max="8" width="19.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="17.83203125" customWidth="1"/>
+    <col min="12" max="12" width="30.83203125" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" customWidth="1"/>
+    <col min="15" max="15" width="10.83203125" customWidth="1"/>
+    <col min="16" max="16" width="9.83203125" customWidth="1"/>
+    <col min="17" max="17" width="8.83203125" customWidth="1"/>
+    <col min="18" max="18" width="11.83203125" customWidth="1"/>
+    <col min="19" max="19" width="16.83203125" customWidth="1"/>
+    <col min="20" max="20" width="8.83203125" customWidth="1"/>
+    <col min="21" max="21" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" t="str" s="2">
         <v>Name</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" t="str" s="2">
         <v>Company</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" t="str" s="2">
         <v>Schools</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D1" t="str" s="2">
         <v>Role</v>
       </c>
-      <c r="E1" t="str">
+      <c r="E1" t="str" s="2">
         <v>Email</v>
       </c>
-      <c r="F1" t="str">
+      <c r="F1" t="str" s="2">
         <v>LinkedIn URL</v>
       </c>
-      <c r="G1" t="str">
+      <c r="G1" t="str" s="2">
         <v>Photo</v>
       </c>
-      <c r="H1" t="str">
+      <c r="H1" t="str" s="2">
         <v>Connected Through</v>
       </c>
-      <c r="I1" t="str">
+      <c r="I1" t="str" s="2">
         <v>Connected On</v>
       </c>
-      <c r="J1" t="str">
+      <c r="J1" t="str" s="2">
         <v>Status</v>
       </c>
-      <c r="K1" t="str">
+      <c r="K1" t="str" s="2">
         <v>Tags</v>
       </c>
-      <c r="L1" t="str">
+      <c r="L1" t="str" s="2">
         <v>Notes</v>
       </c>
-      <c r="M1" t="str">
+      <c r="M1" t="str" s="2">
         <v>Past Companies</v>
+      </c>
+      <c r="N1" t="str" s="2">
+        <v>Headline</v>
+      </c>
+      <c r="O1" t="str" s="2">
+        <v>Location</v>
+      </c>
+      <c r="P1" t="str" s="2">
+        <v>Website</v>
+      </c>
+      <c r="Q1" t="str" s="2">
+        <v>Skills</v>
+      </c>
+      <c r="R1" t="str" s="2">
+        <v>Languages</v>
+      </c>
+      <c r="S1" t="str" s="2">
+        <v>Certifications</v>
+      </c>
+      <c r="T1" t="str" s="2">
+        <v>Honors</v>
+      </c>
+      <c r="U1" t="str" s="2">
+        <v>About</v>
       </c>
     </row>
     <row r="2">
@@ -474,7 +526,7 @@
       <c r="B2" t="str">
         <v>Deloitte</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C2" t="str" s="3">
         <v>Stanford University</v>
       </c>
       <c r="D2" t="str">
@@ -501,10 +553,34 @@
       <c r="K2" t="str">
         <v>Consulting club</v>
       </c>
-      <c r="L2" t="str">
+      <c r="L2" t="str" s="3">
         <v>Case interview tips</v>
       </c>
-      <c r="M2" t="str">
+      <c r="M2" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N2" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -515,7 +591,7 @@
       <c r="B3" t="str">
         <v>Deloitte</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C3" t="str" s="3">
         <v>University of Utah</v>
       </c>
       <c r="D3" t="str">
@@ -542,10 +618,34 @@
       <c r="K3" t="str">
         <v/>
       </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
+      <c r="L3" t="str" s="3">
+        <v/>
+      </c>
+      <c r="M3" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N3" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -556,7 +656,7 @@
       <c r="B4" t="str">
         <v>Microsoft</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C4" t="str" s="3">
         <v>Stanford University</v>
       </c>
       <c r="D4" t="str">
@@ -583,10 +683,34 @@
       <c r="K4" t="str">
         <v>Product</v>
       </c>
-      <c r="L4" t="str">
+      <c r="L4" t="str" s="3">
         <v>Owns the marketplace roadmap</v>
       </c>
-      <c r="M4" t="str">
+      <c r="M4" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N4" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
+      <c r="U4" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -597,7 +721,7 @@
       <c r="B5" t="str">
         <v>Delta Air Lines</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C5" t="str" s="3">
         <v>Stanford University</v>
       </c>
       <c r="D5" t="str">
@@ -624,10 +748,34 @@
       <c r="K5" t="str">
         <v/>
       </c>
-      <c r="L5" t="str">
+      <c r="L5" t="str" s="3">
         <v>Info session speaker</v>
       </c>
-      <c r="M5" t="str">
+      <c r="M5" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N5" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
+      <c r="U5" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -638,7 +786,7 @@
       <c r="B6" t="str">
         <v>Google</v>
       </c>
-      <c r="C6" t="str">
+      <c r="C6" t="str" s="3">
         <v>University of Utah</v>
       </c>
       <c r="D6" t="str">
@@ -665,10 +813,34 @@
       <c r="K6" t="str">
         <v/>
       </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
+      <c r="L6" t="str" s="3">
+        <v/>
+      </c>
+      <c r="M6" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N6" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str">
+        <v/>
+      </c>
+      <c r="T6" t="str">
+        <v/>
+      </c>
+      <c r="U6" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -679,7 +851,7 @@
       <c r="B7" t="str">
         <v>Deloitte</v>
       </c>
-      <c r="C7" t="str">
+      <c r="C7" t="str" s="3">
         <v>Stanford</v>
       </c>
       <c r="D7" t="str">
@@ -706,10 +878,34 @@
       <c r="K7" t="str">
         <v>Consulting club</v>
       </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
+      <c r="L7" t="str" s="3">
+        <v/>
+      </c>
+      <c r="M7" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N7" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
+      <c r="T7" t="str">
+        <v/>
+      </c>
+      <c r="U7" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -720,7 +916,7 @@
       <c r="B8" t="str">
         <v>Deloitte LLP</v>
       </c>
-      <c r="C8" t="str">
+      <c r="C8" t="str" s="3">
         <v/>
       </c>
       <c r="D8" t="str">
@@ -747,10 +943,34 @@
       <c r="K8" t="str">
         <v/>
       </c>
-      <c r="L8" t="str">
+      <c r="L8" t="str" s="3">
         <v>Leads the strategy practice</v>
       </c>
-      <c r="M8" t="str">
+      <c r="M8" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N8" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <v/>
+      </c>
+      <c r="U8" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -761,7 +981,7 @@
       <c r="B9" t="str">
         <v>Microsoft</v>
       </c>
-      <c r="C9" t="str">
+      <c r="C9" t="str" s="3">
         <v/>
       </c>
       <c r="D9" t="str">
@@ -788,10 +1008,34 @@
       <c r="K9" t="str">
         <v>Product</v>
       </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
+      <c r="L9" t="str" s="3">
+        <v/>
+      </c>
+      <c r="M9" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N9" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <v/>
+      </c>
+      <c r="U9" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -802,7 +1046,7 @@
       <c r="B10" t="str">
         <v>Microsoft</v>
       </c>
-      <c r="C10" t="str">
+      <c r="C10" t="str" s="3">
         <v>University of Utah</v>
       </c>
       <c r="D10" t="str">
@@ -829,10 +1073,34 @@
       <c r="K10" t="str">
         <v>Product</v>
       </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
+      <c r="L10" t="str" s="3">
+        <v/>
+      </c>
+      <c r="M10" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N10" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <v/>
+      </c>
+      <c r="U10" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -843,7 +1111,7 @@
       <c r="B11" t="str">
         <v>Delta Air Lines</v>
       </c>
-      <c r="C11" t="str">
+      <c r="C11" t="str" s="3">
         <v/>
       </c>
       <c r="D11" t="str">
@@ -870,10 +1138,34 @@
       <c r="K11" t="str">
         <v/>
       </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
+      <c r="L11" t="str" s="3">
+        <v/>
+      </c>
+      <c r="M11" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N11" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <v/>
+      </c>
+      <c r="U11" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -884,7 +1176,7 @@
       <c r="B12" t="str">
         <v>Goldman Sachs</v>
       </c>
-      <c r="C12" t="str">
+      <c r="C12" t="str" s="3">
         <v>Stanford University</v>
       </c>
       <c r="D12" t="str">
@@ -911,10 +1203,34 @@
       <c r="K12" t="str">
         <v/>
       </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
-      <c r="M12" t="str">
+      <c r="L12" t="str" s="3">
+        <v/>
+      </c>
+      <c r="M12" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N12" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v/>
+      </c>
+      <c r="S12" t="str">
+        <v/>
+      </c>
+      <c r="T12" t="str">
+        <v/>
+      </c>
+      <c r="U12" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -925,7 +1241,7 @@
       <c r="B13" t="str">
         <v>Google</v>
       </c>
-      <c r="C13" t="str">
+      <c r="C13" t="str" s="3">
         <v>University of Utah</v>
       </c>
       <c r="D13" t="str">
@@ -952,10 +1268,34 @@
       <c r="K13" t="str">
         <v/>
       </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
-      <c r="M13" t="str">
+      <c r="L13" t="str" s="3">
+        <v/>
+      </c>
+      <c r="M13" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N13" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13" t="str">
+        <v/>
+      </c>
+      <c r="T13" t="str">
+        <v/>
+      </c>
+      <c r="U13" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -966,7 +1306,7 @@
       <c r="B14" t="str">
         <v>Adobe</v>
       </c>
-      <c r="C14" t="str">
+      <c r="C14" t="str" s="3">
         <v>University of Utah</v>
       </c>
       <c r="D14" t="str">
@@ -993,10 +1333,34 @@
       <c r="K14" t="str">
         <v/>
       </c>
-      <c r="L14" t="str">
-        <v/>
-      </c>
-      <c r="M14" t="str">
+      <c r="L14" t="str" s="3">
+        <v/>
+      </c>
+      <c r="M14" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N14" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str">
+        <v/>
+      </c>
+      <c r="T14" t="str">
+        <v/>
+      </c>
+      <c r="U14" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1007,7 +1371,7 @@
       <c r="B15" t="str">
         <v>Independent</v>
       </c>
-      <c r="C15" t="str">
+      <c r="C15" t="str" s="3">
         <v/>
       </c>
       <c r="D15" t="str">
@@ -1034,10 +1398,34 @@
       <c r="K15" t="str">
         <v/>
       </c>
-      <c r="L15" t="str">
+      <c r="L15" t="str" s="3">
         <v>Old roommate</v>
       </c>
-      <c r="M15" t="str">
+      <c r="M15" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N15" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <v/>
+      </c>
+      <c r="U15" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1048,7 +1436,7 @@
       <c r="B16" t="str">
         <v>Deloitte</v>
       </c>
-      <c r="C16" t="str">
+      <c r="C16" t="str" s="3">
         <v/>
       </c>
       <c r="D16" t="str">
@@ -1075,10 +1463,34 @@
       <c r="K16" t="str">
         <v/>
       </c>
-      <c r="L16" t="str">
+      <c r="L16" t="str" s="3">
         <v>Jordan offered an intro</v>
       </c>
-      <c r="M16" t="str">
+      <c r="M16" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N16" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str">
+        <v/>
+      </c>
+      <c r="T16" t="str">
+        <v/>
+      </c>
+      <c r="U16" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1089,7 +1501,7 @@
       <c r="B17" t="str">
         <v>Microsoft</v>
       </c>
-      <c r="C17" t="str">
+      <c r="C17" t="str" s="3">
         <v/>
       </c>
       <c r="D17" t="str">
@@ -1116,10 +1528,34 @@
       <c r="K17" t="str">
         <v>Product</v>
       </c>
-      <c r="L17" t="str">
-        <v/>
-      </c>
-      <c r="M17" t="str">
+      <c r="L17" t="str" s="3">
+        <v/>
+      </c>
+      <c r="M17" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N17" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str">
+        <v/>
+      </c>
+      <c r="T17" t="str">
+        <v/>
+      </c>
+      <c r="U17" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1130,7 +1566,7 @@
       <c r="B18" t="str">
         <v>Microsoft</v>
       </c>
-      <c r="C18" t="str">
+      <c r="C18" t="str" s="3">
         <v/>
       </c>
       <c r="D18" t="str">
@@ -1157,10 +1593,34 @@
       <c r="K18" t="str">
         <v>Product</v>
       </c>
-      <c r="L18" t="str">
-        <v/>
-      </c>
-      <c r="M18" t="str">
+      <c r="L18" t="str" s="3">
+        <v/>
+      </c>
+      <c r="M18" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N18" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v/>
+      </c>
+      <c r="S18" t="str">
+        <v/>
+      </c>
+      <c r="T18" t="str">
+        <v/>
+      </c>
+      <c r="U18" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1171,7 +1631,7 @@
       <c r="B19" t="str">
         <v>Delta Air Lines</v>
       </c>
-      <c r="C19" t="str">
+      <c r="C19" t="str" s="3">
         <v/>
       </c>
       <c r="D19" t="str">
@@ -1198,10 +1658,34 @@
       <c r="K19" t="str">
         <v/>
       </c>
-      <c r="L19" t="str">
-        <v/>
-      </c>
-      <c r="M19" t="str">
+      <c r="L19" t="str" s="3">
+        <v/>
+      </c>
+      <c r="M19" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N19" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str">
+        <v/>
+      </c>
+      <c r="T19" t="str">
+        <v/>
+      </c>
+      <c r="U19" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1212,7 +1696,7 @@
       <c r="B20" t="str">
         <v>Adobe</v>
       </c>
-      <c r="C20" t="str">
+      <c r="C20" t="str" s="3">
         <v/>
       </c>
       <c r="D20" t="str">
@@ -1239,10 +1723,34 @@
       <c r="K20" t="str">
         <v/>
       </c>
-      <c r="L20" t="str">
-        <v/>
-      </c>
-      <c r="M20" t="str">
+      <c r="L20" t="str" s="3">
+        <v/>
+      </c>
+      <c r="M20" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N20" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
+        <v/>
+      </c>
+      <c r="S20" t="str">
+        <v/>
+      </c>
+      <c r="T20" t="str">
+        <v/>
+      </c>
+      <c r="U20" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1253,7 +1761,7 @@
       <c r="B21" t="str">
         <v>Stanford University</v>
       </c>
-      <c r="C21" t="str">
+      <c r="C21" t="str" s="3">
         <v/>
       </c>
       <c r="D21" t="str">
@@ -1280,10 +1788,34 @@
       <c r="K21" t="str">
         <v/>
       </c>
-      <c r="L21" t="str">
-        <v/>
-      </c>
-      <c r="M21" t="str">
+      <c r="L21" t="str" s="3">
+        <v/>
+      </c>
+      <c r="M21" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N21" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v/>
+      </c>
+      <c r="S21" t="str">
+        <v/>
+      </c>
+      <c r="T21" t="str">
+        <v/>
+      </c>
+      <c r="U21" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1294,7 +1826,7 @@
       <c r="B22" t="str">
         <v>Qualtrics</v>
       </c>
-      <c r="C22" t="str">
+      <c r="C22" t="str" s="3">
         <v/>
       </c>
       <c r="D22" t="str">
@@ -1321,10 +1853,34 @@
       <c r="K22" t="str">
         <v/>
       </c>
-      <c r="L22" t="str">
-        <v/>
-      </c>
-      <c r="M22" t="str">
+      <c r="L22" t="str" s="3">
+        <v/>
+      </c>
+      <c r="M22" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N22" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+      <c r="R22" t="str">
+        <v/>
+      </c>
+      <c r="S22" t="str">
+        <v/>
+      </c>
+      <c r="T22" t="str">
+        <v/>
+      </c>
+      <c r="U22" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1335,7 +1891,7 @@
       <c r="B23" t="str">
         <v>Qualtrics</v>
       </c>
-      <c r="C23" t="str">
+      <c r="C23" t="str" s="3">
         <v/>
       </c>
       <c r="D23" t="str">
@@ -1362,27 +1918,311 @@
       <c r="K23" t="str">
         <v/>
       </c>
-      <c r="L23" t="str">
+      <c r="L23" t="str" s="3">
         <v>3rd-degree example</v>
       </c>
-      <c r="M23" t="str">
+      <c r="M23" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N23" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+      <c r="R23" t="str">
+        <v/>
+      </c>
+      <c r="S23" t="str">
+        <v/>
+      </c>
+      <c r="T23" t="str">
+        <v/>
+      </c>
+      <c r="U23" t="str" s="3">
         <v/>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:U23"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="J2:J1000">
+      <formula1>"To Reach Out,Contacted,Scheduled,Met,Follow Up,Referral"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="jordan.lee@example.com"/>
+    <hyperlink ref="E3" r:id="rId2" display="priya.shah@example.com"/>
+    <hyperlink ref="E4" r:id="rId3" display="sofia.alvarez@example.com"/>
+    <hyperlink ref="E5" r:id="rId4" display="noah.carter@example.com"/>
+    <hyperlink ref="E6" r:id="rId5" display="mia.chen@example.com"/>
+    <hyperlink ref="E7" r:id="rId6" display="marcus.bell@example.com"/>
+    <hyperlink ref="E8" r:id="rId7" display="hana.kim@example.com"/>
+    <hyperlink ref="E9" r:id="rId8" display="ethan.brooks@example.com"/>
+    <hyperlink ref="E10" r:id="rId9" display="lena.novak@example.com"/>
+    <hyperlink ref="E11" r:id="rId10" display="grace.owens@example.com"/>
+    <hyperlink ref="E12" r:id="rId11" display="daniel.ortiz@example.com"/>
+    <hyperlink ref="E13" r:id="rId12" display="owen.price@example.com"/>
+    <hyperlink ref="E14" r:id="rId13" display="ava.thompson@example.com"/>
+    <hyperlink ref="E15" r:id="rId14" display="liam.walsh@example.com"/>
+  </hyperlinks>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U23"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F1"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str" s="2">
+        <v>Person</v>
+      </c>
+      <c r="B1" t="str" s="2">
+        <v>School</v>
+      </c>
+      <c r="C1" t="str" s="2">
+        <v>Degree</v>
+      </c>
+      <c r="D1" t="str" s="2">
+        <v>Field</v>
+      </c>
+      <c r="E1" t="str" s="2">
+        <v>Start</v>
+      </c>
+      <c r="F1" t="str" s="2">
+        <v>End</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B12"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="60.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str" s="2">
+        <v>Field</v>
+      </c>
+      <c r="B1" t="str" s="2">
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Name</v>
+      </c>
+      <c r="B2" t="str" s="3">
+        <v>Alex Rivera</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Photo</v>
+      </c>
+      <c r="B3" t="str" s="3">
+        <v>demo/photos/alex-rivera.jpg</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Role</v>
+      </c>
+      <c r="B4" t="str" s="3">
+        <v>MBA Candidate</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Headline</v>
+      </c>
+      <c r="B5" t="str" s="3">
+        <v>Stanford MBA '27 · Looking for strategy &amp; product roles</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Company</v>
+      </c>
+      <c r="B6" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Schools</v>
+      </c>
+      <c r="B7" t="str" s="3">
+        <v>Stanford University (2025–2027); University of Utah (2016–2020)</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Past Companies</v>
+      </c>
+      <c r="B8" t="str" s="3">
+        <v>Delta Air Lines (2020–2022); Adobe (2022–2025)</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Email</v>
+      </c>
+      <c r="B9" t="str" s="3">
+        <v>alex.rivera@example.com</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>LinkedIn URL</v>
+      </c>
+      <c r="B10" t="str" s="3">
+        <v>https://www.linkedin.com/in/alex-rivera-demo</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Location</v>
+      </c>
+      <c r="B11" t="str" s="3">
+        <v>Palo Alto, California</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
+        <v>What I'm looking for</v>
+      </c>
+      <c r="B12" t="str" xml:space="preserve" s="3">
+        <v xml:space="preserve">Summer 2027 internships in strategy or product at consumer-tech and airline companies.
+Happy to swap notes on case prep and product sense interviews.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B9"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="60.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str" s="2">
+        <v>Setting</v>
+      </c>
+      <c r="B1" t="str" s="2">
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Your name</v>
+      </c>
+      <c r="B2" t="str" s="3">
+        <v>Alex Rivera</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Avatar style</v>
+      </c>
+      <c r="B3" t="str" s="3">
+        <v>notionists</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Your email</v>
+      </c>
+      <c r="B4" t="str" s="3">
+        <v>alex.rivera@example.com</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Meeting length (minutes)</v>
+      </c>
+      <c r="B5" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Zoom link</v>
+      </c>
+      <c r="B6" t="str" s="3">
+        <v>https://zoom.us/j/0000000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Check-in every (days)</v>
+      </c>
+      <c r="B7" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Invite message</v>
+      </c>
+      <c r="B8" t="str" s="3">
+        <v>Hi {first name}, looking forward to our chat on {date} at {time}. {link}</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Demo base date</v>
+      </c>
+      <c r="B9" t="str" s="3">
+        <v>2026-09-28</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C1"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="36.83203125"/>
-    <col min="2" max="2" customWidth="1" width="8.83203125"/>
-    <col min="3" max="3" customWidth="1" width="8.83203125"/>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1403,12 +2243,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B21"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="110.83203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="1" width="22.83203125"/>
+    <col min="2" max="2" customWidth="1" width="110.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1586,27 +2426,27 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D7"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="28.83203125"/>
-    <col min="2" max="2" customWidth="1" width="10.83203125"/>
-    <col min="3" max="3" customWidth="1" width="14.83203125"/>
-    <col min="4" max="4" customWidth="1" width="40.83203125"/>
+    <col min="1" max="1" width="17.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" customWidth="1"/>
+    <col min="4" max="4" width="49.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" t="str" s="2">
         <v>Company</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" t="str" s="2">
         <v>Priority</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" t="str" s="2">
         <v>Stage</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D1" t="str" s="2">
         <v>Notes</v>
       </c>
     </row>
@@ -1620,7 +2460,7 @@
       <c r="C2" t="str">
         <v>Networking</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D2" t="str" s="3">
         <v>Strategy practice</v>
       </c>
     </row>
@@ -1634,7 +2474,7 @@
       <c r="C3" t="str">
         <v>Applied</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D3" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1648,7 +2488,7 @@
       <c r="C4" t="str">
         <v>Researching</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D4" t="str" s="3">
         <v>Three pool contacts there aren't on the map yet</v>
       </c>
     </row>
@@ -1662,7 +2502,7 @@
       <c r="C5" t="str">
         <v>Researching</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D5" t="str" s="3">
         <v>Reachable only through Liam</v>
       </c>
     </row>
@@ -1676,7 +2516,7 @@
       <c r="C6" t="str">
         <v>Researching</v>
       </c>
-      <c r="D6" t="str">
+      <c r="D6" t="str" s="3">
         <v>No one yet</v>
       </c>
     </row>
@@ -1690,34 +2530,42 @@
       <c r="C7" t="str">
         <v>Researching</v>
       </c>
-      <c r="D7" t="str">
+      <c r="D7" t="str" s="3">
         <v>No one yet</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="B2:B1000">
+      <formula1>"1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="C2:C1000">
+      <formula1>"Researching,Networking,Applied,Interviewing,Offer"</formula1>
+    </dataValidation>
+  </dataValidations>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C12"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="28.83203125"/>
-    <col min="2" max="2" customWidth="1" width="30.83203125"/>
-    <col min="3" max="3" customWidth="1" width="30.83203125"/>
+    <col min="1" max="1" width="21.83203125" customWidth="1"/>
+    <col min="2" max="2" width="21.83203125" customWidth="1"/>
+    <col min="3" max="3" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" t="str" s="2">
         <v>Company</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" t="str" s="2">
         <v>Website</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" t="str" s="2">
         <v>Logo</v>
       </c>
     </row>
@@ -1849,39 +2697,39 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G27"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="14.83203125"/>
-    <col min="2" max="2" customWidth="1" width="16.83203125"/>
-    <col min="3" max="3" customWidth="1" width="40.83203125"/>
-    <col min="4" max="4" customWidth="1" width="28.83203125"/>
-    <col min="5" max="5" customWidth="1" width="28.83203125"/>
-    <col min="6" max="6" customWidth="1" width="30.83203125"/>
-    <col min="7" max="7" customWidth="1" width="14.83203125"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" customWidth="1"/>
+    <col min="3" max="3" width="50.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="21.83203125" customWidth="1"/>
+    <col min="6" max="6" width="36.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" t="str" s="2">
         <v>First Name</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" t="str" s="2">
         <v>Last Name</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" t="str" s="2">
         <v>URL</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D1" t="str" s="2">
         <v>Email Address</v>
       </c>
-      <c r="E1" t="str">
+      <c r="E1" t="str" s="2">
         <v>Company</v>
       </c>
-      <c r="F1" t="str">
+      <c r="F1" t="str" s="2">
         <v>Position</v>
       </c>
-      <c r="G1" t="str">
+      <c r="G1" t="str" s="2">
         <v>Connected On</v>
       </c>
     </row>
@@ -2484,61 +3332,90 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G27"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" tooltip="https://www.linkedin.com/in/jordan-lee-3f9a21" display="https://www.linkedin.com/in/jordan-lee-3f9a21"/>
+    <hyperlink ref="C3" r:id="rId2" tooltip="https://www.linkedin.com/in/priya-shah-77b0c4" display="https://www.linkedin.com/in/priya-shah-77b0c4"/>
+    <hyperlink ref="C4" r:id="rId3" tooltip="https://www.linkedin.com/in/sofia-alvarez-5d2e18" display="https://www.linkedin.com/in/sofia-alvarez-5d2e18"/>
+    <hyperlink ref="C5" r:id="rId4" tooltip="https://www.linkedin.com/in/noah-carter-a41b77" display="https://www.linkedin.com/in/noah-carter-a41b77"/>
+    <hyperlink ref="C6" r:id="rId5" tooltip="https://www.linkedin.com/in/mia-chen-0c8e42" display="https://www.linkedin.com/in/mia-chen-0c8e42"/>
+    <hyperlink ref="C7" r:id="rId6" tooltip="https://www.linkedin.com/in/kai-morgan-2b6f90" display="https://www.linkedin.com/in/kai-morgan-2b6f90"/>
+    <hyperlink ref="C8" r:id="rId7" tooltip="https://www.linkedin.com/in/elena-rossi-91cd03" display="https://www.linkedin.com/in/elena-rossi-91cd03"/>
+    <hyperlink ref="C9" r:id="rId8" tooltip="https://www.linkedin.com/in/theo-grant-e7a215" display="https://www.linkedin.com/in/theo-grant-e7a215"/>
+    <hyperlink ref="C10" r:id="rId9" tooltip="https://www.linkedin.com/in/nora-singh-48fa6b" display="https://www.linkedin.com/in/nora-singh-48fa6b"/>
+    <hyperlink ref="C11" r:id="rId10" tooltip="https://www.linkedin.com/in/maya-patel-6a1d3e" display="https://www.linkedin.com/in/maya-patel-6a1d3e"/>
+    <hyperlink ref="C12" r:id="rId11" tooltip="https://www.linkedin.com/in/lucas-bennett-c03f59" display="https://www.linkedin.com/in/lucas-bennett-c03f59"/>
+    <hyperlink ref="C13" r:id="rId12" tooltip="https://www.linkedin.com/in/aisha-rahman-8e47b2" display="https://www.linkedin.com/in/aisha-rahman-8e47b2"/>
+    <hyperlink ref="C14" r:id="rId13" tooltip="https://www.linkedin.com/in/diego-santos-1f9c6d" display="https://www.linkedin.com/in/diego-santos-1f9c6d"/>
+    <hyperlink ref="C15" r:id="rId14" tooltip="https://www.linkedin.com/in/hannah-brooks-5b27a0" display="https://www.linkedin.com/in/hannah-brooks-5b27a0"/>
+    <hyperlink ref="C16" r:id="rId15" tooltip="https://www.linkedin.com/in/omar-haddad-3d81fe" display="https://www.linkedin.com/in/omar-haddad-3d81fe"/>
+    <hyperlink ref="C17" r:id="rId16" tooltip="https://www.linkedin.com/in/grace-liu-9a0e6c" display="https://www.linkedin.com/in/grace-liu-9a0e6c"/>
+    <hyperlink ref="C18" r:id="rId17" tooltip="https://www.linkedin.com/in/ryan-doyle-4c5b12" display="https://www.linkedin.com/in/ryan-doyle-4c5b12"/>
+    <hyperlink ref="C19" r:id="rId18" tooltip="https://www.linkedin.com/in/chloe-martin-b8d4a7" display="https://www.linkedin.com/in/chloe-martin-b8d4a7"/>
+    <hyperlink ref="C20" r:id="rId19" tooltip="https://www.linkedin.com/in/ben-walker-0e3c95" display="https://www.linkedin.com/in/ben-walker-0e3c95"/>
+    <hyperlink ref="C21" r:id="rId20" tooltip="https://www.linkedin.com/in/isabel-cruz-7f2a48" display="https://www.linkedin.com/in/isabel-cruz-7f2a48"/>
+    <hyperlink ref="C22" r:id="rId21" tooltip="https://www.linkedin.com/in/ethan-park-2d6e91" display="https://www.linkedin.com/in/ethan-park-2d6e91"/>
+    <hyperlink ref="C23" r:id="rId22" tooltip="https://www.linkedin.com/in/zara-ahmed-c4b710" display="https://www.linkedin.com/in/zara-ahmed-c4b710"/>
+    <hyperlink ref="C24" r:id="rId23" tooltip="https://www.linkedin.com/in/leo-fischer-6e0d2b" display="https://www.linkedin.com/in/leo-fischer-6e0d2b"/>
+    <hyperlink ref="C25" r:id="rId24" tooltip="https://www.linkedin.com/in/emma-nguyen-93a5f4" display="https://www.linkedin.com/in/emma-nguyen-93a5f4"/>
+    <hyperlink ref="C26" r:id="rId25" tooltip="https://www.linkedin.com/in/jack-sullivan-1b8e07" display="https://www.linkedin.com/in/jack-sullivan-1b8e07"/>
+    <hyperlink ref="C27" r:id="rId26" tooltip="https://www.linkedin.com/in/olivia-reed-58c9d3" display="https://www.linkedin.com/in/olivia-reed-58c9d3"/>
+  </hyperlinks>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:G27"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K10"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="22.83203125"/>
-    <col min="2" max="2" customWidth="1" width="12.83203125"/>
-    <col min="3" max="3" customWidth="1" width="8.83203125"/>
-    <col min="4" max="4" customWidth="1" width="8.83203125"/>
-    <col min="5" max="5" customWidth="1" width="16.83203125"/>
-    <col min="6" max="6" customWidth="1" width="12.83203125"/>
-    <col min="7" max="7" customWidth="1" width="40.83203125"/>
-    <col min="8" max="8" customWidth="1" width="30.83203125"/>
-    <col min="9" max="9" customWidth="1" width="22.83203125"/>
-    <col min="10" max="10" customWidth="1" width="30.83203125"/>
-    <col min="11" max="11" customWidth="1" width="16.83203125"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" customWidth="1"/>
+    <col min="7" max="7" width="60.83203125" customWidth="1"/>
+    <col min="8" max="8" width="28.83203125" customWidth="1"/>
+    <col min="9" max="9" width="19.83203125" customWidth="1"/>
+    <col min="10" max="10" width="38.83203125" customWidth="1"/>
+    <col min="11" max="11" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" t="str" s="2">
         <v>Person</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" t="str" s="2">
         <v>Date</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" t="str" s="2">
         <v>Start</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D1" t="str" s="2">
         <v>End</v>
       </c>
-      <c r="E1" t="str">
+      <c r="E1" t="str" s="2">
         <v>Type</v>
       </c>
-      <c r="F1" t="str">
+      <c r="F1" t="str" s="2">
         <v>Method</v>
       </c>
-      <c r="G1" t="str">
+      <c r="G1" t="str" s="2">
         <v>Notes</v>
       </c>
-      <c r="H1" t="str">
+      <c r="H1" t="str" s="2">
         <v>Next Step</v>
       </c>
-      <c r="I1" t="str">
+      <c r="I1" t="str" s="2">
         <v>Calendar Event ID</v>
       </c>
-      <c r="J1" t="str">
+      <c r="J1" t="str" s="2">
         <v>Link</v>
       </c>
-      <c r="K1" t="str">
+      <c r="K1" t="str" s="2">
         <v>ID</v>
       </c>
     </row>
@@ -2561,10 +3438,10 @@
       <c r="F2" t="str">
         <v>In Person</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="3">
         <v>Caught up; he offered to introduce me to Zoe at Qualtrics.</v>
       </c>
-      <c r="H2" t="str">
+      <c r="H2" t="str" s="3">
         <v>Ask Liam for the Zoe intro</v>
       </c>
       <c r="I2" t="str">
@@ -2596,10 +3473,10 @@
       <c r="F3" t="str">
         <v>In Person</v>
       </c>
-      <c r="G3" t="str">
+      <c r="G3" t="str" s="3">
         <v>Marketplace roadmap, how PMs at Microsoft pick problems.</v>
       </c>
-      <c r="H3" t="str">
+      <c r="H3" t="str" s="3">
         <v>Send thank-you</v>
       </c>
       <c r="I3" t="str">
@@ -2631,10 +3508,10 @@
       <c r="F4" t="str">
         <v>Zoom</v>
       </c>
-      <c r="G4" t="str">
+      <c r="G4" t="str" s="3">
         <v>Walked through case interview prep and the strategy practice.</v>
       </c>
-      <c r="H4" t="str">
+      <c r="H4" t="str" s="3">
         <v>Send resume for review</v>
       </c>
       <c r="I4" t="str">
@@ -2666,10 +3543,10 @@
       <c r="F5" t="str">
         <v>Phone</v>
       </c>
-      <c r="G5" t="str">
+      <c r="G5" t="str" s="3">
         <v>Delta's commercial strategy team; APM-style rotation.</v>
       </c>
-      <c r="H5" t="str">
+      <c r="H5" t="str" s="3">
         <v>Apply to the fall rotation</v>
       </c>
       <c r="I5" t="str">
@@ -2701,10 +3578,10 @@
       <c r="F6" t="str">
         <v>Zoom</v>
       </c>
-      <c r="G6" t="str">
+      <c r="G6" t="str" s="3">
         <v>Goldman strategy group; offered to connect me with Ben.</v>
       </c>
-      <c r="H6" t="str">
+      <c r="H6" t="str" s="3">
         <v>Send thank-you</v>
       </c>
       <c r="I6" t="str">
@@ -2736,10 +3613,10 @@
       <c r="F7" t="str">
         <v>Zoom</v>
       </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
+      <c r="G7" t="str" s="3">
+        <v/>
+      </c>
+      <c r="H7" t="str" s="3">
         <v/>
       </c>
       <c r="I7" t="str">
@@ -2771,10 +3648,10 @@
       <c r="F8" t="str">
         <v>Teams</v>
       </c>
-      <c r="G8" t="str">
+      <c r="G8" t="str" s="3">
         <v>Recruiter screen for the Delta internship.</v>
       </c>
-      <c r="H8" t="str">
+      <c r="H8" t="str" s="3">
         <v/>
       </c>
       <c r="I8" t="str">
@@ -2806,10 +3683,10 @@
       <c r="F9" t="str">
         <v>Google Meet</v>
       </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
+      <c r="G9" t="str" s="3">
+        <v/>
+      </c>
+      <c r="H9" t="str" s="3">
         <v/>
       </c>
       <c r="I9" t="str">
@@ -2841,10 +3718,10 @@
       <c r="F10" t="str">
         <v>Zoom</v>
       </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
+      <c r="G10" t="str" s="3">
+        <v/>
+      </c>
+      <c r="H10" t="str" s="3">
         <v/>
       </c>
       <c r="I10" t="str">
@@ -2858,54 +3735,62 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="E2:E1000">
+      <formula1>"Coffee Chat,Informational,Networking Event,Class/Club,Interview,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="F2:F1000">
+      <formula1>"Zoom,Google Meet,Teams,Phone,In Person,Email,LinkedIn"</formula1>
+    </dataValidation>
+  </dataValidations>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:K10"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H10"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40.83203125"/>
-    <col min="2" max="2" customWidth="1" width="22.83203125"/>
-    <col min="3" max="3" customWidth="1" width="20.83203125"/>
-    <col min="4" max="4" customWidth="1" width="12.83203125"/>
-    <col min="5" max="5" customWidth="1" width="8.83203125"/>
-    <col min="6" max="6" customWidth="1" width="12.83203125"/>
-    <col min="7" max="7" customWidth="1" width="20.83203125"/>
-    <col min="8" max="8" customWidth="1" width="16.83203125"/>
+    <col min="1" max="1" width="53.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="8.83203125" customWidth="1"/>
+    <col min="8" max="8" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" t="str" s="2">
         <v>Task</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" t="str" s="2">
         <v>Person</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" t="str" s="2">
         <v>Company</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D1" t="str" s="2">
         <v>Due</v>
       </c>
-      <c r="E1" t="str">
+      <c r="E1" t="str" s="2">
         <v>Done</v>
       </c>
-      <c r="F1" t="str">
+      <c r="F1" t="str" s="2">
         <v>Created</v>
       </c>
-      <c r="G1" t="str">
+      <c r="G1" t="str" s="2">
         <v>Source</v>
       </c>
-      <c r="H1" t="str">
+      <c r="H1" t="str" s="2">
         <v>ID</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2" t="str" s="3">
         <v>Send thank-you to Daniel Ortiz within 24 hrs</v>
       </c>
       <c r="B2" t="str">
@@ -2931,7 +3816,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3" t="str" s="3">
         <v>Follow up with Hana Kim about the strategy practice</v>
       </c>
       <c r="B3" t="str">
@@ -2957,7 +3842,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
+      <c r="A4" t="str" s="3">
         <v>Send resume to Jordan for review</v>
       </c>
       <c r="B4" t="str">
@@ -2983,7 +3868,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
+      <c r="A5" t="str" s="3">
         <v>Prepare questions for coffee chat with Priya</v>
       </c>
       <c r="B5" t="str">
@@ -3009,7 +3894,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
+      <c r="A6" t="str" s="3">
         <v>Ask Liam for the intro to Zoe Adams</v>
       </c>
       <c r="B6" t="str">
@@ -3035,7 +3920,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
+      <c r="A7" t="str" s="3">
         <v>Research Apple strategy &amp; operations roles</v>
       </c>
       <c r="B7" t="str">
@@ -3061,7 +3946,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
+      <c r="A8" t="str" s="3">
         <v>Update resume with fall projects</v>
       </c>
       <c r="B8" t="str">
@@ -3087,7 +3972,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
+      <c r="A9" t="str" s="3">
         <v>Send thank-you to Noah Carter within 24 hrs</v>
       </c>
       <c r="B9" t="str">
@@ -3113,7 +3998,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
+      <c r="A10" t="str" s="3">
         <v>Send thank-you to Sofia Alvarez within 24 hrs</v>
       </c>
       <c r="B10" t="str">
@@ -3139,33 +4024,38 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="E2:E1000">
+      <formula1>"Yes"</formula1>
+    </dataValidation>
+  </dataValidations>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:H10"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D13"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="24.83203125"/>
-    <col min="2" max="2" customWidth="1" width="24.83203125"/>
-    <col min="3" max="3" customWidth="1" width="16.83203125"/>
-    <col min="4" max="4" customWidth="1" width="40.83203125"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" t="str" s="2">
         <v>Person A</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" t="str" s="2">
         <v>Person B</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" t="str" s="2">
         <v>Type</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D1" t="str" s="2">
         <v>Notes</v>
       </c>
     </row>
@@ -3179,7 +4069,7 @@
       <c r="C2" t="str">
         <v>Introduced me</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D2" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -3193,7 +4083,7 @@
       <c r="C3" t="str">
         <v>Introduced me</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D3" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -3207,7 +4097,7 @@
       <c r="C4" t="str">
         <v>Introduced me</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D4" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -3221,7 +4111,7 @@
       <c r="C5" t="str">
         <v>Introduced me</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D5" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -3235,7 +4125,7 @@
       <c r="C6" t="str">
         <v>Introduced me</v>
       </c>
-      <c r="D6" t="str">
+      <c r="D6" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -3249,7 +4139,7 @@
       <c r="C7" t="str">
         <v>Introduced me</v>
       </c>
-      <c r="D7" t="str">
+      <c r="D7" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -3263,7 +4153,7 @@
       <c r="C8" t="str">
         <v>Introduced me</v>
       </c>
-      <c r="D8" t="str">
+      <c r="D8" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -3277,7 +4167,7 @@
       <c r="C9" t="str">
         <v>Introduced me</v>
       </c>
-      <c r="D9" t="str">
+      <c r="D9" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -3291,7 +4181,7 @@
       <c r="C10" t="str">
         <v>Friend</v>
       </c>
-      <c r="D10" t="str">
+      <c r="D10" t="str" s="3">
         <v>Roommates' friend group</v>
       </c>
     </row>
@@ -3305,7 +4195,7 @@
       <c r="C11" t="str">
         <v>Classmate</v>
       </c>
-      <c r="D11" t="str">
+      <c r="D11" t="str" s="3">
         <v>Stanford, same product club</v>
       </c>
     </row>
@@ -3319,7 +4209,7 @@
       <c r="C12" t="str">
         <v>Mentor</v>
       </c>
-      <c r="D12" t="str">
+      <c r="D12" t="str" s="3">
         <v>Jordan mentors Owen on case interviews</v>
       </c>
     </row>
@@ -3333,212 +4223,61 @@
       <c r="C13" t="str">
         <v>Coworker</v>
       </c>
-      <c r="D13" t="str">
+      <c r="D13" t="str" s="3">
         <v>Worked together at Deloitte</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="C2:C1000">
+      <formula1>"Introduced me,Coworker,Classmate,Friend,Mentor,Other"</formula1>
+    </dataValidation>
+  </dataValidations>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:D13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:G1"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="22.83203125"/>
-    <col min="2" max="2" customWidth="1" width="70.83203125"/>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Field</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Value</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Alex Rivera</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Photo</v>
-      </c>
-      <c r="B3" t="str">
-        <v>demo/photos/alex-rivera.jpg</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Role</v>
-      </c>
-      <c r="B4" t="str">
-        <v>MBA Candidate</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Headline</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Stanford MBA '27 · Looking for strategy &amp; product roles</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
+      <c r="A1" t="str" s="2">
+        <v>Person</v>
+      </c>
+      <c r="B1" t="str" s="2">
         <v>Company</v>
       </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Schools</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Stanford University (2025–2027); University of Utah (2016–2020)</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Past Companies</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Delta Air Lines (2020–2022); Adobe (2022–2025)</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Email</v>
-      </c>
-      <c r="B9" t="str">
-        <v>alex.rivera@example.com</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>LinkedIn URL</v>
-      </c>
-      <c r="B10" t="str">
-        <v>https://www.linkedin.com/in/alex-rivera-demo</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
+      <c r="C1" t="str" s="2">
+        <v>Title</v>
+      </c>
+      <c r="D1" t="str" s="2">
+        <v>Start</v>
+      </c>
+      <c r="E1" t="str" s="2">
+        <v>End</v>
+      </c>
+      <c r="F1" t="str" s="2">
         <v>Location</v>
       </c>
-      <c r="B11" t="str">
-        <v>Palo Alto, California</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str">
-        <v>What I'm looking for</v>
-      </c>
-      <c r="B12" t="str" xml:space="preserve">
-        <v xml:space="preserve">Summer 2027 internships in strategy or product at consumer-tech and airline companies.
-Happy to swap notes on case prep and product sense interviews.</v>
+      <c r="G1" t="str" s="2">
+        <v>Description</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
-  <cols>
-    <col min="1" max="1" customWidth="1" width="26.83203125"/>
-    <col min="2" max="2" customWidth="1" width="60.83203125"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Setting</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Value</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Your name</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Alex Rivera</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Avatar style</v>
-      </c>
-      <c r="B3" t="str">
-        <v>notionists</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Your email</v>
-      </c>
-      <c r="B4" t="str">
-        <v>alex.rivera@example.com</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Meeting length (minutes)</v>
-      </c>
-      <c r="B5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Zoom link</v>
-      </c>
-      <c r="B6" t="str">
-        <v>https://zoom.us/j/0000000000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Check-in every (days)</v>
-      </c>
-      <c r="B7">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Invite message</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Hi {first name}, looking forward to our chat on {date} at {time}. {link}</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Demo base date</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-09-28</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/site/demo/demo_network.xlsx
+++ b/site/demo/demo_network.xlsx
@@ -2131,7 +2131,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -2203,15 +2203,23 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
+        <v>Group size (people)</v>
+      </c>
+      <c r="B9" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
         <v>Demo base date</v>
       </c>
-      <c r="B9" t="str" s="3">
+      <c r="B10" t="str" s="3">
         <v>2026-09-28</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3369,7 +3377,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:Q10"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -3382,6 +3390,12 @@
     <col min="9" max="9" width="19.83203125" customWidth="1"/>
     <col min="10" max="10" width="38.83203125" customWidth="1"/>
     <col min="11" max="11" width="9.83203125" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" customWidth="1"/>
+    <col min="13" max="13" width="8.83203125" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" customWidth="1"/>
+    <col min="15" max="15" width="13.83203125" customWidth="1"/>
+    <col min="16" max="16" width="16.83203125" customWidth="1"/>
+    <col min="17" max="17" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3418,6 +3432,24 @@
       <c r="K1" t="str" s="2">
         <v>ID</v>
       </c>
+      <c r="L1" t="str" s="2">
+        <v>Title</v>
+      </c>
+      <c r="M1" t="str" s="2">
+        <v>Guests</v>
+      </c>
+      <c r="N1" t="str" s="2">
+        <v>Location</v>
+      </c>
+      <c r="O1" t="str" s="2">
+        <v>Description</v>
+      </c>
+      <c r="P1" t="str" s="2">
+        <v>Reminder (min)</v>
+      </c>
+      <c r="Q1" t="str" s="2">
+        <v>Time Zone</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -3453,6 +3485,24 @@
       <c r="K2" t="str">
         <v>demo-m1</v>
       </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str" s="3">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -3488,6 +3538,24 @@
       <c r="K3" t="str">
         <v>demo-m2</v>
       </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str" s="3">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -3523,6 +3591,24 @@
       <c r="K4" t="str">
         <v>demo-m3</v>
       </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str" s="3">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -3558,6 +3644,24 @@
       <c r="K5" t="str">
         <v>demo-m4</v>
       </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str" s="3">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -3593,6 +3697,24 @@
       <c r="K6" t="str">
         <v>demo-m5</v>
       </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str" s="3">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -3628,6 +3750,24 @@
       <c r="K7" t="str">
         <v>demo-m6</v>
       </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str" s="3">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -3663,6 +3803,24 @@
       <c r="K8" t="str">
         <v>demo-m7</v>
       </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str" s="3">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -3698,6 +3856,24 @@
       <c r="K9" t="str">
         <v>demo-m8</v>
       </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str" s="3">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -3732,6 +3908,24 @@
       </c>
       <c r="K10" t="str">
         <v>demo-m9</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str" s="3">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3744,7 +3938,7 @@
     </dataValidation>
   </dataValidations>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q10"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/site/demo/demo_network.xlsx
+++ b/site/demo/demo_network.xlsx
@@ -443,15 +443,15 @@
     <col min="10" max="10" width="14.83203125" customWidth="1"/>
     <col min="11" max="11" width="17.83203125" customWidth="1"/>
     <col min="12" max="12" width="30.83203125" customWidth="1"/>
-    <col min="13" max="13" width="16.83203125" customWidth="1"/>
-    <col min="14" max="14" width="10.83203125" customWidth="1"/>
-    <col min="15" max="15" width="10.83203125" customWidth="1"/>
+    <col min="13" max="13" width="29.83203125" customWidth="1"/>
+    <col min="14" max="14" width="53.83203125" customWidth="1"/>
+    <col min="15" max="15" width="27.83203125" customWidth="1"/>
     <col min="16" max="16" width="9.83203125" customWidth="1"/>
-    <col min="17" max="17" width="8.83203125" customWidth="1"/>
-    <col min="18" max="18" width="11.83203125" customWidth="1"/>
-    <col min="19" max="19" width="16.83203125" customWidth="1"/>
+    <col min="17" max="17" width="52.83203125" customWidth="1"/>
+    <col min="18" max="18" width="31.83203125" customWidth="1"/>
+    <col min="19" max="19" width="31.83203125" customWidth="1"/>
     <col min="20" max="20" width="8.83203125" customWidth="1"/>
-    <col min="21" max="21" width="8.83203125" customWidth="1"/>
+    <col min="21" max="21" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -557,25 +557,25 @@
         <v>Case interview tips</v>
       </c>
       <c r="M2" t="str" s="3">
-        <v/>
+        <v>Delta Air Lines (2019–2019)</v>
       </c>
       <c r="N2" t="str" s="3">
-        <v/>
+        <v>Senior Consultant, Strategy &amp; Analytics at Deloitte</v>
       </c>
       <c r="O2" t="str">
-        <v/>
+        <v>San Francisco, California</v>
       </c>
       <c r="P2" t="str">
         <v/>
       </c>
       <c r="Q2" t="str">
-        <v/>
+        <v>Market Sizing; Financial Modeling; Case Interviews</v>
       </c>
       <c r="R2" t="str">
         <v/>
       </c>
       <c r="S2" t="str">
-        <v/>
+        <v>Certified Scrum Product Owner</v>
       </c>
       <c r="T2" t="str">
         <v/>
@@ -687,22 +687,22 @@
         <v>Owns the marketplace roadmap</v>
       </c>
       <c r="M4" t="str" s="3">
-        <v/>
+        <v>Deloitte (2018–2021)</v>
       </c>
       <c r="N4" t="str" s="3">
-        <v/>
+        <v>Product Manager at Microsoft · Marketplace</v>
       </c>
       <c r="O4" t="str">
-        <v/>
+        <v>Seattle, Washington</v>
       </c>
       <c r="P4" t="str">
         <v/>
       </c>
       <c r="Q4" t="str">
-        <v/>
+        <v>Product Strategy; SQL; Experimentation</v>
       </c>
       <c r="R4" t="str">
-        <v/>
+        <v>Spanish (Native or Bilingual)</v>
       </c>
       <c r="S4" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v/>
       </c>
       <c r="U4" t="str" s="3">
-        <v/>
+        <v>PM for the Microsoft marketplace. Former Deloitte consultant; Stanford GSB.</v>
       </c>
     </row>
     <row r="5">
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="N5" t="str" s="3">
-        <v/>
+        <v>Commercial Strategy Analyst at Delta Air Lines</v>
       </c>
       <c r="O5" t="str">
-        <v/>
+        <v>Atlanta, Georgia</v>
       </c>
       <c r="P5" t="str">
         <v/>
       </c>
       <c r="Q5" t="str">
-        <v/>
+        <v>Network Planning; Forecasting; Python</v>
       </c>
       <c r="R5" t="str">
         <v/>
@@ -1980,12 +1980,12 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F5"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="8.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="21.83203125" customWidth="1"/>
+    <col min="3" max="3" width="41.83203125" customWidth="1"/>
+    <col min="4" max="4" width="34.83203125" customWidth="1"/>
     <col min="5" max="5" width="8.83203125" customWidth="1"/>
     <col min="6" max="6" width="8.83203125" customWidth="1"/>
   </cols>
@@ -2010,9 +2010,89 @@
         <v>End</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Sofia Alvarez</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Stanford University</v>
+      </c>
+      <c r="C2" t="str" s="3">
+        <v>Master of Business Administration - MBA</v>
+      </c>
+      <c r="D2" t="str" s="3">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v>2021</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Sofia Alvarez</v>
+      </c>
+      <c r="B3" t="str">
+        <v>University of Utah</v>
+      </c>
+      <c r="C3" t="str" s="3">
+        <v>Bachelor of Science - BS</v>
+      </c>
+      <c r="D3" t="str" s="3">
+        <v>Information Systems</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2014</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Jordan Lee</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Stanford University</v>
+      </c>
+      <c r="C4" t="str" s="3">
+        <v>Bachelor of Arts - BA</v>
+      </c>
+      <c r="D4" t="str" s="3">
+        <v>Economics</v>
+      </c>
+      <c r="E4" t="str">
+        <v>2016</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Noah Carter</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Stanford University</v>
+      </c>
+      <c r="C5" t="str" s="3">
+        <v>Master of Science - MS</v>
+      </c>
+      <c r="D5" t="str" s="3">
+        <v>Management Science &amp; Engineering</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2019</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2021</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4435,15 +4515,15 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G9"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="9.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="17.83203125" customWidth="1"/>
+    <col min="3" max="3" width="41.83203125" customWidth="1"/>
+    <col min="4" max="4" width="9.83203125" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" customWidth="1"/>
+    <col min="6" max="6" width="27.83203125" customWidth="1"/>
+    <col min="7" max="7" width="49.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4469,9 +4549,193 @@
         <v>Description</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Sofia Alvarez</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Microsoft</v>
+      </c>
+      <c r="C2" t="str" s="3">
+        <v>Product Manager</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2023-07</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Present</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Redmond, Washington</v>
+      </c>
+      <c r="G2" t="str" s="3">
+        <v>Owns the marketplace roadmap and pricing tests.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Sofia Alvarez</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Microsoft</v>
+      </c>
+      <c r="C3" t="str" s="3">
+        <v>Product Manager Intern</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2022-06</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2022-09</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Redmond, Washington</v>
+      </c>
+      <c r="G3" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Sofia Alvarez</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="C4" t="str" s="3">
+        <v>Business Technology Analyst</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2018-08</v>
+      </c>
+      <c r="E4" t="str">
+        <v>2021-06</v>
+      </c>
+      <c r="F4" t="str">
+        <v>San Francisco Bay Area</v>
+      </c>
+      <c r="G4" t="str" s="3">
+        <v>Tech strategy for retail and travel clients.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Jordan Lee</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="C5" t="str" s="3">
+        <v>Strategy &amp; Analytics: Senior Consultant</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2022-01</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Present</v>
+      </c>
+      <c r="F5" t="str">
+        <v>San Francisco, California</v>
+      </c>
+      <c r="G5" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Jordan Lee</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="C6" t="str" s="3">
+        <v>Strategy &amp; Analytics: Consultant</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2020-08</v>
+      </c>
+      <c r="E6" t="str">
+        <v>2021-12</v>
+      </c>
+      <c r="F6" t="str">
+        <v>San Francisco, California</v>
+      </c>
+      <c r="G6" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Jordan Lee</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Delta Air Lines</v>
+      </c>
+      <c r="C7" t="str" s="3">
+        <v>Revenue Management Intern</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2019-06</v>
+      </c>
+      <c r="E7" t="str">
+        <v>2019-08</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Atlanta, Georgia</v>
+      </c>
+      <c r="G7" t="str" s="3">
+        <v>Pricing analysis for transatlantic routes.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Noah Carter</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Delta Air Lines</v>
+      </c>
+      <c r="C8" t="str" s="3">
+        <v>Commercial Strategy Analyst</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2023-02</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Present</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Atlanta, Georgia</v>
+      </c>
+      <c r="G8" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Noah Carter</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Delta Air Lines</v>
+      </c>
+      <c r="C9" t="str" s="3">
+        <v>Network Planning Analyst</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2021-07</v>
+      </c>
+      <c r="E9" t="str">
+        <v>2023-01</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Atlanta, Georgia</v>
+      </c>
+      <c r="G9" t="str" s="3">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/site/demo/demo_network.xlsx
+++ b/site/demo/demo_network.xlsx
@@ -434,7 +434,7 @@
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="21.83203125" customWidth="1"/>
     <col min="3" max="3" width="21.83203125" customWidth="1"/>
-    <col min="4" max="4" width="29.83203125" customWidth="1"/>
+    <col min="4" max="4" width="27.83203125" customWidth="1"/>
     <col min="5" max="5" width="27.83203125" customWidth="1"/>
     <col min="6" max="6" width="50.83203125" customWidth="1"/>
     <col min="7" max="7" width="31.83203125" customWidth="1"/>
@@ -557,7 +557,7 @@
         <v>Case interview tips</v>
       </c>
       <c r="M2" t="str" s="3">
-        <v>Delta Air Lines (2019–2019)</v>
+        <v>Adobe (2019–2019)</v>
       </c>
       <c r="N2" t="str" s="3">
         <v>Senior Consultant, Strategy &amp; Analytics at Deloitte</v>
@@ -592,7 +592,7 @@
         <v>Deloitte</v>
       </c>
       <c r="C3" t="str" s="3">
-        <v>University of Utah</v>
+        <v>Stanford University</v>
       </c>
       <c r="D3" t="str">
         <v>Manager</v>
@@ -719,13 +719,13 @@
         <v>Noah Carter</v>
       </c>
       <c r="B5" t="str">
-        <v>Delta Air Lines</v>
+        <v>Microsoft</v>
       </c>
       <c r="C5" t="str" s="3">
         <v>Stanford University</v>
       </c>
       <c r="D5" t="str">
-        <v>Commercial Strategy Analyst</v>
+        <v>Business Strategy Analyst</v>
       </c>
       <c r="E5" t="str">
         <v>noah.carter@example.com</v>
@@ -752,19 +752,19 @@
         <v>Info session speaker</v>
       </c>
       <c r="M5" t="str" s="3">
-        <v/>
+        <v>Delta Air Lines (2021–2023)</v>
       </c>
       <c r="N5" t="str" s="3">
-        <v>Commercial Strategy Analyst at Delta Air Lines</v>
+        <v>Business Strategy Analyst at Microsoft</v>
       </c>
       <c r="O5" t="str">
-        <v>Atlanta, Georgia</v>
+        <v>Seattle, Washington</v>
       </c>
       <c r="P5" t="str">
         <v/>
       </c>
       <c r="Q5" t="str">
-        <v>Network Planning; Forecasting; Python</v>
+        <v>Forecasting; Customer Research; Python</v>
       </c>
       <c r="R5" t="str">
         <v/>
@@ -784,10 +784,10 @@
         <v>Mia Chen</v>
       </c>
       <c r="B6" t="str">
-        <v>Google</v>
+        <v>Microsoft</v>
       </c>
       <c r="C6" t="str" s="3">
-        <v>University of Utah</v>
+        <v>Stanford University</v>
       </c>
       <c r="D6" t="str">
         <v>Product Lead</v>
@@ -1047,7 +1047,7 @@
         <v>Microsoft</v>
       </c>
       <c r="C10" t="str" s="3">
-        <v>University of Utah</v>
+        <v/>
       </c>
       <c r="D10" t="str">
         <v>Program Manager</v>
@@ -1109,13 +1109,13 @@
         <v>Grace Owens</v>
       </c>
       <c r="B11" t="str">
-        <v>Delta Air Lines</v>
+        <v>Deloitte</v>
       </c>
       <c r="C11" t="str" s="3">
         <v/>
       </c>
       <c r="D11" t="str">
-        <v>Recruiter</v>
+        <v>Campus Recruiter</v>
       </c>
       <c r="E11" t="str">
         <v>grace.owens@example.com</v>
@@ -1174,7 +1174,7 @@
         <v>Daniel Ortiz</v>
       </c>
       <c r="B12" t="str">
-        <v>Goldman Sachs</v>
+        <v>Deloitte</v>
       </c>
       <c r="C12" t="str" s="3">
         <v>Stanford University</v>
@@ -1239,10 +1239,10 @@
         <v>Owen Price</v>
       </c>
       <c r="B13" t="str">
-        <v>Google</v>
+        <v>Microsoft</v>
       </c>
       <c r="C13" t="str" s="3">
-        <v>University of Utah</v>
+        <v/>
       </c>
       <c r="D13" t="str">
         <v>Associate Product Manager</v>
@@ -1304,10 +1304,10 @@
         <v>Ava Thompson</v>
       </c>
       <c r="B14" t="str">
-        <v>Adobe</v>
+        <v>Microsoft</v>
       </c>
       <c r="C14" t="str" s="3">
-        <v>University of Utah</v>
+        <v/>
       </c>
       <c r="D14" t="str">
         <v>Operations Lead</v>
@@ -1629,13 +1629,13 @@
         <v>Victor Hale</v>
       </c>
       <c r="B19" t="str">
-        <v>Delta Air Lines</v>
+        <v>Microsoft</v>
       </c>
       <c r="C19" t="str" s="3">
         <v/>
       </c>
       <c r="D19" t="str">
-        <v>VP Network Planning</v>
+        <v>VP of Strategy</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1694,7 +1694,7 @@
         <v>Chloe Park</v>
       </c>
       <c r="B20" t="str">
-        <v>Adobe</v>
+        <v>Microsoft</v>
       </c>
       <c r="C20" t="str" s="3">
         <v/>
@@ -1824,7 +1824,7 @@
         <v>Zoe Adams</v>
       </c>
       <c r="B22" t="str">
-        <v>Qualtrics</v>
+        <v>Microsoft</v>
       </c>
       <c r="C22" t="str" s="3">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>Sam Rivera</v>
       </c>
       <c r="B23" t="str">
-        <v>Qualtrics</v>
+        <v>Microsoft</v>
       </c>
       <c r="C23" t="str" s="3">
         <v/>
@@ -1983,7 +1983,7 @@
   <dimension ref="A1:F5"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="21.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
     <col min="3" max="3" width="41.83203125" customWidth="1"/>
     <col min="4" max="4" width="34.83203125" customWidth="1"/>
     <col min="5" max="5" width="8.83203125" customWidth="1"/>
@@ -2035,7 +2035,7 @@
         <v>Sofia Alvarez</v>
       </c>
       <c r="B3" t="str">
-        <v>University of Utah</v>
+        <v>University of Washington</v>
       </c>
       <c r="C3" t="str" s="3">
         <v>Bachelor of Science - BS</v>
@@ -2158,7 +2158,7 @@
         <v>Schools</v>
       </c>
       <c r="B7" t="str" s="3">
-        <v>Stanford University (2025–2027); University of Utah (2016–2020)</v>
+        <v>Stanford University (2025–2027); University of Washington (2016–2020)</v>
       </c>
     </row>
     <row r="8">
@@ -2516,12 +2516,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D4"/>
   <cols>
-    <col min="1" max="1" width="17.83203125" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" customWidth="1"/>
-    <col min="4" max="4" width="49.83203125" customWidth="1"/>
+    <col min="4" max="4" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2554,72 +2554,30 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Delta Air Lines</v>
+        <v>Google</v>
       </c>
       <c r="B3" t="str">
         <v>1</v>
       </c>
       <c r="C3" t="str">
-        <v>Applied</v>
+        <v>Researching</v>
       </c>
       <c r="D3" t="str" s="3">
-        <v/>
+        <v>No one on the map yet: two people there are in your LinkedIn pool</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Goldman Sachs</v>
+        <v>Microsoft</v>
       </c>
       <c r="B4" t="str">
         <v>2</v>
       </c>
       <c r="C4" t="str">
-        <v>Researching</v>
+        <v>Networking</v>
       </c>
       <c r="D4" t="str" s="3">
-        <v>Three pool contacts there aren't on the map yet</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Qualtrics</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Researching</v>
-      </c>
-      <c r="D5" t="str" s="3">
-        <v>Reachable only through Liam</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="B6" t="str">
-        <v>3</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Researching</v>
-      </c>
-      <c r="D6" t="str" s="3">
-        <v>No one yet</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Nike</v>
-      </c>
-      <c r="B7" t="str">
-        <v>3</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Researching</v>
-      </c>
-      <c r="D7" t="str" s="3">
-        <v>No one yet</v>
+        <v>Product roles; Sofia is the warmest way in</v>
       </c>
     </row>
   </sheetData>
@@ -2632,7 +2590,7 @@
     </dataValidation>
   </dataValidations>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3551,7 +3509,7 @@
         <v>In Person</v>
       </c>
       <c r="G2" t="str" s="3">
-        <v>Caught up; he offered to introduce me to Zoe at Qualtrics.</v>
+        <v>Caught up; he offered to introduce me to Zoe on Microsoft's strategy team.</v>
       </c>
       <c r="H2" t="str" s="3">
         <v>Ask Liam for the Zoe intro</v>
@@ -3710,7 +3668,7 @@
         <v>Phone</v>
       </c>
       <c r="G5" t="str" s="3">
-        <v>Delta's commercial strategy team; APM-style rotation.</v>
+        <v>Microsoft's business strategy team; APM-style rotation.</v>
       </c>
       <c r="H5" t="str" s="3">
         <v>Apply to the fall rotation</v>
@@ -3763,7 +3721,7 @@
         <v>Zoom</v>
       </c>
       <c r="G6" t="str" s="3">
-        <v>Goldman strategy group; offered to connect me with Ben.</v>
+        <v>Deloitte strategy group; offered to connect me with Ben.</v>
       </c>
       <c r="H6" t="str" s="3">
         <v>Send thank-you</v>
@@ -3869,7 +3827,7 @@
         <v>Teams</v>
       </c>
       <c r="G8" t="str" s="3">
-        <v>Recruiter screen for the Delta internship.</v>
+        <v>Recruiter screen for the Deloitte internship.</v>
       </c>
       <c r="H8" t="str" s="3">
         <v/>
@@ -4029,7 +3987,7 @@
   <cols>
     <col min="1" max="1" width="53.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
     <col min="5" max="5" width="8.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
@@ -4071,7 +4029,7 @@
         <v>Daniel Ortiz</v>
       </c>
       <c r="C2" t="str">
-        <v>Goldman Sachs</v>
+        <v>Deloitte</v>
       </c>
       <c r="D2" s="1">
         <v>46292</v>
@@ -4175,7 +4133,7 @@
         <v>Liam Walsh</v>
       </c>
       <c r="C6" t="str">
-        <v>Qualtrics</v>
+        <v>Microsoft</v>
       </c>
       <c r="D6" s="1">
         <v>46296</v>
@@ -4195,13 +4153,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str" s="3">
-        <v>Research Apple strategy &amp; operations roles</v>
+        <v>Research Google strategy &amp; operations roles</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>Apple</v>
+        <v>Google</v>
       </c>
       <c r="D7" s="1">
         <v>46302</v>
@@ -4253,7 +4211,7 @@
         <v>Noah Carter</v>
       </c>
       <c r="C9" t="str">
-        <v>Delta Air Lines</v>
+        <v>Microsoft</v>
       </c>
       <c r="D9" s="1">
         <v>46289</v>
@@ -4669,10 +4627,10 @@
         <v>Jordan Lee</v>
       </c>
       <c r="B7" t="str">
-        <v>Delta Air Lines</v>
+        <v>Adobe</v>
       </c>
       <c r="C7" t="str" s="3">
-        <v>Revenue Management Intern</v>
+        <v>Business Strategy Intern</v>
       </c>
       <c r="D7" t="str">
         <v>2019-06</v>
@@ -4681,10 +4639,10 @@
         <v>2019-08</v>
       </c>
       <c r="F7" t="str">
-        <v>Atlanta, Georgia</v>
+        <v>San Jose, California</v>
       </c>
       <c r="G7" t="str" s="3">
-        <v>Pricing analysis for transatlantic routes.</v>
+        <v>Market sizing for a new creative-tools bundle.</v>
       </c>
     </row>
     <row r="8">
@@ -4692,10 +4650,10 @@
         <v>Noah Carter</v>
       </c>
       <c r="B8" t="str">
-        <v>Delta Air Lines</v>
+        <v>Microsoft</v>
       </c>
       <c r="C8" t="str" s="3">
-        <v>Commercial Strategy Analyst</v>
+        <v>Business Strategy Analyst</v>
       </c>
       <c r="D8" t="str">
         <v>2023-02</v>
@@ -4704,7 +4662,7 @@
         <v>Present</v>
       </c>
       <c r="F8" t="str">
-        <v>Atlanta, Georgia</v>
+        <v>Redmond, Washington</v>
       </c>
       <c r="G8" t="str" s="3">
         <v/>
@@ -4718,7 +4676,7 @@
         <v>Delta Air Lines</v>
       </c>
       <c r="C9" t="str" s="3">
-        <v>Network Planning Analyst</v>
+        <v>Loyalty Program Analyst</v>
       </c>
       <c r="D9" t="str">
         <v>2021-07</v>
@@ -4727,7 +4685,7 @@
         <v>2023-01</v>
       </c>
       <c r="F9" t="str">
-        <v>Atlanta, Georgia</v>
+        <v>Seattle, Washington</v>
       </c>
       <c r="G9" t="str" s="3">
         <v/>

--- a/site/demo/demo_network.xlsx
+++ b/site/demo/demo_network.xlsx
@@ -2211,7 +2211,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -2291,15 +2291,23 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>Group by</v>
+      </c>
+      <c r="B10" t="str" s="3">
+        <v>company, school</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
         <v>Demo base date</v>
       </c>
-      <c r="B10" t="str" s="3">
+      <c r="B11" t="str" s="3">
         <v>2026-09-28</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/site/demo/demo_network.xlsx
+++ b/site/demo/demo_network.xlsx
@@ -3999,7 +3999,7 @@
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
     <col min="5" max="5" width="8.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
     <col min="8" max="8" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4049,7 +4049,7 @@
         <v>46289</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>thanks:demo-m5</v>
       </c>
       <c r="H2" t="str">
         <v>demo-t1</v>
@@ -4127,7 +4127,7 @@
         <v>46290</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>prep:demo-m6</v>
       </c>
       <c r="H5" t="str">
         <v>demo-t4</v>
@@ -4231,7 +4231,7 @@
         <v>46286</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>thanks:demo-m4</v>
       </c>
       <c r="H9" t="str">
         <v>demo-t8</v>
@@ -4257,7 +4257,7 @@
         <v>46271</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>thanks:demo-m2</v>
       </c>
       <c r="H10" t="str">
         <v>demo-t9</v>

--- a/site/demo/demo_network.xlsx
+++ b/site/demo/demo_network.xlsx
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">People!$A$1:$U$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'LinkedIn Pool'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'LinkedIn Pool'!$A$1:$M$27</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -2099,7 +2099,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B18"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -2202,9 +2202,57 @@
 Happy to swap notes on case prep and product sense interviews.</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>About</v>
+      </c>
+      <c r="B13" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Industry</v>
+      </c>
+      <c r="B14" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Websites</v>
+      </c>
+      <c r="B15" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Skills</v>
+      </c>
+      <c r="B16" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Certifications</v>
+      </c>
+      <c r="B17" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Volunteering</v>
+      </c>
+      <c r="B18" t="str" s="3">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B18"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2753,7 +2801,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:M27"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -2762,6 +2810,12 @@
     <col min="5" max="5" width="21.83203125" customWidth="1"/>
     <col min="6" max="6" width="36.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="15.83203125" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2786,6 +2840,24 @@
       <c r="G1" t="str" s="2">
         <v>Connected On</v>
       </c>
+      <c r="H1" t="str" s="2">
+        <v>Reached Out</v>
+      </c>
+      <c r="I1" t="str" s="2">
+        <v>Invited On</v>
+      </c>
+      <c r="J1" t="str" s="2">
+        <v>Invite Note</v>
+      </c>
+      <c r="K1" t="str" s="2">
+        <v>LinkedIn Note</v>
+      </c>
+      <c r="L1" t="str" s="2">
+        <v>Messages</v>
+      </c>
+      <c r="M1" t="str" s="2">
+        <v>Last Contacted</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -2809,6 +2881,24 @@
       <c r="G2" s="1">
         <v>46093</v>
       </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -2832,6 +2922,24 @@
       <c r="G3" s="1">
         <v>46055</v>
       </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -2855,6 +2963,24 @@
       <c r="G4" s="1">
         <v>46255</v>
       </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -2878,6 +3004,24 @@
       <c r="G5" s="1">
         <v>46116</v>
       </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -2901,6 +3045,24 @@
       <c r="G6" s="1">
         <v>46192</v>
       </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -2924,6 +3086,24 @@
       <c r="G7" s="1">
         <v>46037</v>
       </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -2947,6 +3127,24 @@
       <c r="G8" s="1">
         <v>46145</v>
       </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -2970,6 +3168,24 @@
       <c r="G9" s="1">
         <v>46182</v>
       </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -2993,6 +3209,24 @@
       <c r="G10" s="1">
         <v>46233</v>
       </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -3016,6 +3250,24 @@
       <c r="G11" s="1">
         <v>46276</v>
       </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -3039,6 +3291,24 @@
       <c r="G12" s="1">
         <v>46261</v>
       </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -3062,6 +3332,24 @@
       <c r="G13" s="1">
         <v>46217</v>
       </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -3085,6 +3373,24 @@
       <c r="G14" s="1">
         <v>46267</v>
       </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -3108,6 +3414,24 @@
       <c r="G15" s="1">
         <v>46160</v>
       </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -3131,6 +3455,24 @@
       <c r="G16" s="1">
         <v>46075</v>
       </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -3154,6 +3496,24 @@
       <c r="G17" s="1">
         <v>46210</v>
       </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -3177,6 +3537,24 @@
       <c r="G18" s="1">
         <v>46110</v>
       </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -3200,6 +3578,24 @@
       <c r="G19" s="1">
         <v>46038</v>
       </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -3223,6 +3619,24 @@
       <c r="G20" s="1">
         <v>45955</v>
       </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -3246,6 +3660,24 @@
       <c r="G21" s="1">
         <v>46247</v>
       </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -3269,6 +3701,24 @@
       <c r="G22" s="1">
         <v>46147</v>
       </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -3292,6 +3742,24 @@
       <c r="G23" s="1">
         <v>46193</v>
       </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -3315,6 +3783,24 @@
       <c r="G24" s="1">
         <v>46120</v>
       </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -3338,6 +3824,24 @@
       <c r="G25" s="1">
         <v>46098</v>
       </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -3361,6 +3865,24 @@
       <c r="G26" s="1">
         <v>45991</v>
       </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -3384,9 +3906,27 @@
       <c r="G27" s="1">
         <v>46003</v>
       </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G27"/>
+  <autoFilter ref="A1:M27"/>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" tooltip="https://www.linkedin.com/in/jordan-lee-3f9a21" display="https://www.linkedin.com/in/jordan-lee-3f9a21"/>
     <hyperlink ref="C3" r:id="rId2" tooltip="https://www.linkedin.com/in/priya-shah-77b0c4" display="https://www.linkedin.com/in/priya-shah-77b0c4"/>
@@ -3416,7 +3956,7 @@
     <hyperlink ref="C27" r:id="rId26" tooltip="https://www.linkedin.com/in/olivia-reed-58c9d3" display="https://www.linkedin.com/in/olivia-reed-58c9d3"/>
   </hyperlinks>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M27"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/site/demo/demo_network.xlsx
+++ b/site/demo/demo_network.xlsx
@@ -4,22 +4,22 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="People" sheetId="1" r:id="rId1"/>
-    <sheet name="How to use" sheetId="2" r:id="rId2"/>
-    <sheet name="Targets" sheetId="3" r:id="rId3"/>
-    <sheet name="Companies" sheetId="4" r:id="rId4"/>
-    <sheet name="LinkedIn Pool" sheetId="5" r:id="rId5"/>
+    <sheet name="Experience" sheetId="2" r:id="rId2"/>
+    <sheet name="Education" sheetId="3" r:id="rId3"/>
+    <sheet name="Connections" sheetId="4" r:id="rId4"/>
+    <sheet name="Targets" sheetId="5" r:id="rId5"/>
     <sheet name="Meetings" sheetId="6" r:id="rId6"/>
     <sheet name="Tasks" sheetId="7" r:id="rId7"/>
-    <sheet name="Connections" sheetId="8" r:id="rId8"/>
-    <sheet name="Experience" sheetId="9" r:id="rId9"/>
-    <sheet name="Education" sheetId="10" r:id="rId10"/>
+    <sheet name="How to use" sheetId="8" r:id="rId8"/>
+    <sheet name="Companies" sheetId="9" r:id="rId9"/>
+    <sheet name="LinkedIn Pool" sheetId="10" r:id="rId10"/>
     <sheet name="Me" sheetId="11" r:id="rId11"/>
     <sheet name="Settings" sheetId="12" r:id="rId12"/>
     <sheet name="Layout" sheetId="13" r:id="rId13" state="hidden"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">People!$A$1:$U$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'LinkedIn Pool'!$A$1:$M$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">People!$A$1:$AE$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9">'LinkedIn Pool'!$A$1:$M$27</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -429,29 +429,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U23"/>
+  <dimension ref="A1:AE23"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="21.83203125" customWidth="1"/>
-    <col min="3" max="3" width="21.83203125" customWidth="1"/>
-    <col min="4" max="4" width="27.83203125" customWidth="1"/>
-    <col min="5" max="5" width="27.83203125" customWidth="1"/>
-    <col min="6" max="6" width="50.83203125" customWidth="1"/>
-    <col min="7" max="7" width="31.83203125" customWidth="1"/>
-    <col min="8" max="8" width="19.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="27.83203125" customWidth="1"/>
+    <col min="4" max="4" width="60.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
     <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="17.83203125" customWidth="1"/>
-    <col min="12" max="12" width="30.83203125" customWidth="1"/>
-    <col min="13" max="13" width="29.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="11.83203125" customWidth="1"/>
+    <col min="13" max="13" width="36.83203125" customWidth="1"/>
     <col min="14" max="14" width="53.83203125" customWidth="1"/>
-    <col min="15" max="15" width="27.83203125" customWidth="1"/>
-    <col min="16" max="16" width="9.83203125" customWidth="1"/>
-    <col min="17" max="17" width="52.83203125" customWidth="1"/>
-    <col min="18" max="18" width="31.83203125" customWidth="1"/>
-    <col min="19" max="19" width="31.83203125" customWidth="1"/>
-    <col min="20" max="20" width="8.83203125" customWidth="1"/>
-    <col min="21" max="21" width="60.83203125" customWidth="1"/>
+    <col min="15" max="15" width="19.83203125" customWidth="1"/>
+    <col min="16" max="16" width="27.83203125" customWidth="1"/>
+    <col min="17" max="17" width="31.83203125" customWidth="1"/>
+    <col min="18" max="18" width="29.83203125" customWidth="1"/>
+    <col min="19" max="19" width="21.83203125" customWidth="1"/>
+    <col min="20" max="20" width="17.83203125" customWidth="1"/>
+    <col min="21" max="21" width="14.83203125" customWidth="1"/>
+    <col min="22" max="22" width="19.83203125" customWidth="1"/>
+    <col min="23" max="23" width="30.83203125" customWidth="1"/>
+    <col min="24" max="24" width="53.83203125" customWidth="1"/>
+    <col min="25" max="25" width="27.83203125" customWidth="1"/>
+    <col min="26" max="26" width="9.83203125" customWidth="1"/>
+    <col min="27" max="27" width="52.83203125" customWidth="1"/>
+    <col min="28" max="28" width="31.83203125" customWidth="1"/>
+    <col min="29" max="29" width="31.83203125" customWidth="1"/>
+    <col min="30" max="30" width="8.83203125" customWidth="1"/>
+    <col min="31" max="31" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,60 +472,90 @@
         <v>Company</v>
       </c>
       <c r="C1" t="str" s="2">
+        <v>Role / Background</v>
+      </c>
+      <c r="D1" t="str" s="2">
+        <v>How We're Connected</v>
+      </c>
+      <c r="E1" t="str" s="2">
+        <v>LinkedIn</v>
+      </c>
+      <c r="F1" t="str" s="2">
+        <v>Meeting Type</v>
+      </c>
+      <c r="G1" t="str" s="2">
+        <v>Method</v>
+      </c>
+      <c r="H1" t="str" s="2">
+        <v>Status</v>
+      </c>
+      <c r="I1" t="str" s="2">
+        <v>Date Reached Out</v>
+      </c>
+      <c r="J1" t="str" s="2">
+        <v>Meeting Date</v>
+      </c>
+      <c r="K1" t="str" s="2">
+        <v>Follow-Up Date</v>
+      </c>
+      <c r="L1" t="str" s="2">
+        <v>Referral?</v>
+      </c>
+      <c r="M1" t="str" s="2">
+        <v>Relevant Opportunities</v>
+      </c>
+      <c r="N1" t="str" s="2">
+        <v>Next Steps</v>
+      </c>
+      <c r="O1" t="str" s="2">
+        <v>Relationship Plan</v>
+      </c>
+      <c r="P1" t="str" s="2">
+        <v>Email</v>
+      </c>
+      <c r="Q1" t="str" s="2">
+        <v>Photo</v>
+      </c>
+      <c r="R1" t="str" s="2">
+        <v>Past Companies</v>
+      </c>
+      <c r="S1" t="str" s="2">
         <v>Schools</v>
       </c>
-      <c r="D1" t="str" s="2">
-        <v>Role</v>
-      </c>
-      <c r="E1" t="str" s="2">
-        <v>Email</v>
-      </c>
-      <c r="F1" t="str" s="2">
-        <v>LinkedIn URL</v>
-      </c>
-      <c r="G1" t="str" s="2">
-        <v>Photo</v>
-      </c>
-      <c r="H1" t="str" s="2">
+      <c r="T1" t="str" s="2">
+        <v>Tags</v>
+      </c>
+      <c r="U1" t="str" s="2">
+        <v>Connected On</v>
+      </c>
+      <c r="V1" t="str" s="2">
         <v>Connected Through</v>
       </c>
-      <c r="I1" t="str" s="2">
-        <v>Connected On</v>
-      </c>
-      <c r="J1" t="str" s="2">
-        <v>Status</v>
-      </c>
-      <c r="K1" t="str" s="2">
-        <v>Tags</v>
-      </c>
-      <c r="L1" t="str" s="2">
+      <c r="W1" t="str" s="2">
         <v>Notes</v>
       </c>
-      <c r="M1" t="str" s="2">
-        <v>Past Companies</v>
-      </c>
-      <c r="N1" t="str" s="2">
+      <c r="X1" t="str" s="2">
         <v>Headline</v>
       </c>
-      <c r="O1" t="str" s="2">
+      <c r="Y1" t="str" s="2">
         <v>Location</v>
       </c>
-      <c r="P1" t="str" s="2">
+      <c r="Z1" t="str" s="2">
         <v>Website</v>
       </c>
-      <c r="Q1" t="str" s="2">
+      <c r="AA1" t="str" s="2">
         <v>Skills</v>
       </c>
-      <c r="R1" t="str" s="2">
+      <c r="AB1" t="str" s="2">
         <v>Languages</v>
       </c>
-      <c r="S1" t="str" s="2">
+      <c r="AC1" t="str" s="2">
         <v>Certifications</v>
       </c>
-      <c r="T1" t="str" s="2">
+      <c r="AD1" t="str" s="2">
         <v>Honors</v>
       </c>
-      <c r="U1" t="str" s="2">
+      <c r="AE1" t="str" s="2">
         <v>About</v>
       </c>
     </row>
@@ -527,60 +567,90 @@
         <v>Deloitte</v>
       </c>
       <c r="C2" t="str" s="3">
+        <v>Senior Consultant</v>
+      </c>
+      <c r="D2" t="str" s="3">
+        <v>Stanford University; Introduced you to Rachel Green; Mentor: Owen Price</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Profile</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Informational</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Zoom</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Met</v>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" s="1">
+        <v>46281</v>
+      </c>
+      <c r="K2" s="1">
+        <v>46293</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M2" t="str" s="3">
+        <v>Deloitte strategy summer associate</v>
+      </c>
+      <c r="N2" t="str" s="3">
+        <v>Send resume to Jordan for review</v>
+      </c>
+      <c r="O2" t="str">
+        <v>Follow Up Later</v>
+      </c>
+      <c r="P2" t="str">
+        <v>jordan.lee@example.com</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>demo/photos/jordan-lee.jpg</v>
+      </c>
+      <c r="R2" t="str" s="3">
+        <v>Adobe (2019–2019)</v>
+      </c>
+      <c r="S2" t="str" s="3">
         <v>Stanford University</v>
       </c>
-      <c r="D2" t="str">
-        <v>Senior Consultant</v>
-      </c>
-      <c r="E2" t="str">
-        <v>jordan.lee@example.com</v>
-      </c>
-      <c r="F2" t="str">
-        <v>https://www.linkedin.com/in/jordan-lee-3f9a21</v>
-      </c>
-      <c r="G2" t="str">
-        <v>demo/photos/jordan-lee.jpg</v>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" s="1">
+      <c r="T2" t="str">
+        <v>Consulting club</v>
+      </c>
+      <c r="U2" s="1">
         <v>46093</v>
       </c>
-      <c r="J2" t="str">
-        <v>Met</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Consulting club</v>
-      </c>
-      <c r="L2" t="str" s="3">
+      <c r="V2" t="str">
+        <v/>
+      </c>
+      <c r="W2" t="str" s="3">
         <v>Case interview tips</v>
       </c>
-      <c r="M2" t="str" s="3">
-        <v>Adobe (2019–2019)</v>
-      </c>
-      <c r="N2" t="str" s="3">
+      <c r="X2" t="str" s="3">
         <v>Senior Consultant, Strategy &amp; Analytics at Deloitte</v>
       </c>
-      <c r="O2" t="str">
+      <c r="Y2" t="str">
         <v>San Francisco, California</v>
       </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
         <v>Market Sizing; Financial Modeling; Case Interviews</v>
       </c>
-      <c r="R2" t="str">
-        <v/>
-      </c>
-      <c r="S2" t="str">
+      <c r="AB2" t="str">
+        <v/>
+      </c>
+      <c r="AC2" t="str">
         <v>Certified Scrum Product Owner</v>
       </c>
-      <c r="T2" t="str">
-        <v/>
-      </c>
-      <c r="U2" t="str" s="3">
+      <c r="AD2" t="str">
+        <v/>
+      </c>
+      <c r="AE2" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -592,60 +662,90 @@
         <v>Deloitte</v>
       </c>
       <c r="C3" t="str" s="3">
+        <v>Manager</v>
+      </c>
+      <c r="D3" t="str" s="3">
         <v>Stanford University</v>
       </c>
-      <c r="D3" t="str">
-        <v>Manager</v>
-      </c>
       <c r="E3" t="str">
+        <v>Profile</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Coffee Chat</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Zoom</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Scheduled</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" s="1">
+        <v>46294</v>
+      </c>
+      <c r="K3" s="1">
+        <v>46294</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N3" t="str" s="3">
+        <v>Prepare questions for coffee chat with Priya</v>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
         <v>priya.shah@example.com</v>
       </c>
-      <c r="F3" t="str">
-        <v>https://www.linkedin.com/in/priya-shah-77b0c4</v>
-      </c>
-      <c r="G3" t="str">
+      <c r="Q3" t="str">
         <v>demo/photos/priya-shah.jpg</v>
       </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" s="1">
+      <c r="R3" t="str" s="3">
+        <v/>
+      </c>
+      <c r="S3" t="str" s="3">
+        <v>Stanford University</v>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" s="1">
         <v>46055</v>
       </c>
-      <c r="J3" t="str">
-        <v>Scheduled</v>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str" s="3">
-        <v/>
-      </c>
-      <c r="M3" t="str" s="3">
-        <v/>
-      </c>
-      <c r="N3" t="str" s="3">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v/>
-      </c>
-      <c r="Q3" t="str">
-        <v/>
-      </c>
-      <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
-        <v/>
-      </c>
-      <c r="U3" t="str" s="3">
+      <c r="V3" t="str">
+        <v/>
+      </c>
+      <c r="W3" t="str" s="3">
+        <v/>
+      </c>
+      <c r="X3" t="str" s="3">
+        <v/>
+      </c>
+      <c r="Y3" t="str">
+        <v/>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v/>
+      </c>
+      <c r="AB3" t="str">
+        <v/>
+      </c>
+      <c r="AC3" t="str">
+        <v/>
+      </c>
+      <c r="AD3" t="str">
+        <v/>
+      </c>
+      <c r="AE3" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -657,60 +757,90 @@
         <v>Microsoft</v>
       </c>
       <c r="C4" t="str" s="3">
+        <v>Product Manager</v>
+      </c>
+      <c r="D4" t="str" s="3">
+        <v>Stanford University; Introduced you to Tom Nguyen; Introduced you to Isla Moore; Classmate: Daniel Ortiz</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Profile</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Coffee Chat</v>
+      </c>
+      <c r="G4" t="str">
+        <v>In Person</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Met</v>
+      </c>
+      <c r="I4" s="1">
+        <v>46244</v>
+      </c>
+      <c r="J4" s="1">
+        <v>46273</v>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>No</v>
+      </c>
+      <c r="M4" t="str" s="3">
+        <v>Microsoft PM internship</v>
+      </c>
+      <c r="N4" t="str" s="3">
+        <v>Send thank-you</v>
+      </c>
+      <c r="O4" t="str">
+        <v>Keep In Contact</v>
+      </c>
+      <c r="P4" t="str">
+        <v>sofia.alvarez@example.com</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>demo/photos/sofia-alvarez.jpg</v>
+      </c>
+      <c r="R4" t="str" s="3">
+        <v>Deloitte (2018–2021)</v>
+      </c>
+      <c r="S4" t="str" s="3">
         <v>Stanford University</v>
       </c>
-      <c r="D4" t="str">
-        <v>Product Manager</v>
-      </c>
-      <c r="E4" t="str">
-        <v>sofia.alvarez@example.com</v>
-      </c>
-      <c r="F4" t="str">
-        <v>https://www.linkedin.com/in/sofia-alvarez-5d2e18</v>
-      </c>
-      <c r="G4" t="str">
-        <v>demo/photos/sofia-alvarez.jpg</v>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" s="1">
+      <c r="T4" t="str">
+        <v>Product</v>
+      </c>
+      <c r="U4" s="1">
         <v>46255</v>
       </c>
-      <c r="J4" t="str">
-        <v>Met</v>
-      </c>
-      <c r="K4" t="str">
-        <v>Product</v>
-      </c>
-      <c r="L4" t="str" s="3">
+      <c r="V4" t="str">
+        <v/>
+      </c>
+      <c r="W4" t="str" s="3">
         <v>Owns the marketplace roadmap</v>
       </c>
-      <c r="M4" t="str" s="3">
-        <v>Deloitte (2018–2021)</v>
-      </c>
-      <c r="N4" t="str" s="3">
+      <c r="X4" t="str" s="3">
         <v>Product Manager at Microsoft · Marketplace</v>
       </c>
-      <c r="O4" t="str">
+      <c r="Y4" t="str">
         <v>Seattle, Washington</v>
       </c>
-      <c r="P4" t="str">
-        <v/>
-      </c>
-      <c r="Q4" t="str">
+      <c r="Z4" t="str">
+        <v/>
+      </c>
+      <c r="AA4" t="str">
         <v>Product Strategy; SQL; Experimentation</v>
       </c>
-      <c r="R4" t="str">
+      <c r="AB4" t="str">
         <v>Spanish (Native or Bilingual)</v>
       </c>
-      <c r="S4" t="str">
-        <v/>
-      </c>
-      <c r="T4" t="str">
-        <v/>
-      </c>
-      <c r="U4" t="str" s="3">
+      <c r="AC4" t="str">
+        <v/>
+      </c>
+      <c r="AD4" t="str">
+        <v/>
+      </c>
+      <c r="AE4" t="str" s="3">
         <v>PM for the Microsoft marketplace. Former Deloitte consultant; Stanford GSB.</v>
       </c>
     </row>
@@ -722,60 +852,90 @@
         <v>Microsoft</v>
       </c>
       <c r="C5" t="str" s="3">
+        <v>Business Strategy Analyst</v>
+      </c>
+      <c r="D5" t="str" s="3">
+        <v>Stanford University; Introduced you to Victor Hale</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Profile</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Informational</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Phone</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Met</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" s="1">
+        <v>46288</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N5" t="str" s="3">
+        <v>Apply to the fall rotation</v>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v>noah.carter@example.com</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>demo/photos/noah-carter.jpg</v>
+      </c>
+      <c r="R5" t="str" s="3">
+        <v>Delta Air Lines (2021–2023)</v>
+      </c>
+      <c r="S5" t="str" s="3">
         <v>Stanford University</v>
       </c>
-      <c r="D5" t="str">
-        <v>Business Strategy Analyst</v>
-      </c>
-      <c r="E5" t="str">
-        <v>noah.carter@example.com</v>
-      </c>
-      <c r="F5" t="str">
-        <v>https://www.linkedin.com/in/noah-carter-a41b77</v>
-      </c>
-      <c r="G5" t="str">
-        <v>demo/photos/noah-carter.jpg</v>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" s="1">
+      <c r="T5" t="str">
+        <v/>
+      </c>
+      <c r="U5" s="1">
         <v>46116</v>
       </c>
-      <c r="J5" t="str">
-        <v>Met</v>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str" s="3">
+      <c r="V5" t="str">
+        <v/>
+      </c>
+      <c r="W5" t="str" s="3">
         <v>Info session speaker</v>
       </c>
-      <c r="M5" t="str" s="3">
-        <v>Delta Air Lines (2021–2023)</v>
-      </c>
-      <c r="N5" t="str" s="3">
+      <c r="X5" t="str" s="3">
         <v>Business Strategy Analyst at Microsoft</v>
       </c>
-      <c r="O5" t="str">
+      <c r="Y5" t="str">
         <v>Seattle, Washington</v>
       </c>
-      <c r="P5" t="str">
-        <v/>
-      </c>
-      <c r="Q5" t="str">
+      <c r="Z5" t="str">
+        <v/>
+      </c>
+      <c r="AA5" t="str">
         <v>Forecasting; Customer Research; Python</v>
       </c>
-      <c r="R5" t="str">
-        <v/>
-      </c>
-      <c r="S5" t="str">
-        <v/>
-      </c>
-      <c r="T5" t="str">
-        <v/>
-      </c>
-      <c r="U5" t="str" s="3">
+      <c r="AB5" t="str">
+        <v/>
+      </c>
+      <c r="AC5" t="str">
+        <v/>
+      </c>
+      <c r="AD5" t="str">
+        <v/>
+      </c>
+      <c r="AE5" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -787,60 +947,90 @@
         <v>Microsoft</v>
       </c>
       <c r="C6" t="str" s="3">
+        <v>Product Lead</v>
+      </c>
+      <c r="D6" t="str" s="3">
+        <v>Stanford University; Introduced you to Chloe Park; Friend: Liam Walsh</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Profile</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Coffee Chat</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Google Meet</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Met</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" s="1">
+        <v>46305</v>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N6" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v>mia.chen@example.com</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>demo/photos/mia-chen.jpg</v>
+      </c>
+      <c r="R6" t="str" s="3">
+        <v/>
+      </c>
+      <c r="S6" t="str" s="3">
         <v>Stanford University</v>
       </c>
-      <c r="D6" t="str">
-        <v>Product Lead</v>
-      </c>
-      <c r="E6" t="str">
-        <v>mia.chen@example.com</v>
-      </c>
-      <c r="F6" t="str">
-        <v>https://www.linkedin.com/in/mia-chen-0c8e42</v>
-      </c>
-      <c r="G6" t="str">
-        <v>demo/photos/mia-chen.jpg</v>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" s="1">
+      <c r="T6" t="str">
+        <v/>
+      </c>
+      <c r="U6" s="1">
         <v>46192</v>
       </c>
-      <c r="J6" t="str">
-        <v>Met</v>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str" s="3">
-        <v/>
-      </c>
-      <c r="M6" t="str" s="3">
-        <v/>
-      </c>
-      <c r="N6" t="str" s="3">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6" t="str">
-        <v/>
-      </c>
-      <c r="Q6" t="str">
-        <v/>
-      </c>
-      <c r="R6" t="str">
-        <v/>
-      </c>
-      <c r="S6" t="str">
-        <v/>
-      </c>
-      <c r="T6" t="str">
-        <v/>
-      </c>
-      <c r="U6" t="str" s="3">
+      <c r="V6" t="str">
+        <v/>
+      </c>
+      <c r="W6" t="str" s="3">
+        <v/>
+      </c>
+      <c r="X6" t="str" s="3">
+        <v/>
+      </c>
+      <c r="Y6" t="str">
+        <v/>
+      </c>
+      <c r="Z6" t="str">
+        <v/>
+      </c>
+      <c r="AA6" t="str">
+        <v/>
+      </c>
+      <c r="AB6" t="str">
+        <v/>
+      </c>
+      <c r="AC6" t="str">
+        <v/>
+      </c>
+      <c r="AD6" t="str">
+        <v/>
+      </c>
+      <c r="AE6" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -852,60 +1042,90 @@
         <v>Deloitte</v>
       </c>
       <c r="C7" t="str" s="3">
+        <v>Analyst</v>
+      </c>
+      <c r="D7" t="str" s="3">
         <v>Stanford</v>
       </c>
-      <c r="D7" t="str">
-        <v>Analyst</v>
-      </c>
       <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>Met</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N7" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
         <v>marcus.bell@example.com</v>
       </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
+      <c r="Q7" t="str">
         <v>demo/photos/marcus-bell.jpg</v>
       </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v/>
-      </c>
-      <c r="J7" t="str">
-        <v>Met</v>
-      </c>
-      <c r="K7" t="str">
+      <c r="R7" t="str" s="3">
+        <v/>
+      </c>
+      <c r="S7" t="str" s="3">
+        <v>Stanford</v>
+      </c>
+      <c r="T7" t="str">
         <v>Consulting club</v>
       </c>
-      <c r="L7" t="str" s="3">
-        <v/>
-      </c>
-      <c r="M7" t="str" s="3">
-        <v/>
-      </c>
-      <c r="N7" t="str" s="3">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v/>
-      </c>
-      <c r="Q7" t="str">
-        <v/>
-      </c>
-      <c r="R7" t="str">
-        <v/>
-      </c>
-      <c r="S7" t="str">
-        <v/>
-      </c>
-      <c r="T7" t="str">
-        <v/>
-      </c>
-      <c r="U7" t="str" s="3">
+      <c r="U7" t="str">
+        <v/>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str" s="3">
+        <v/>
+      </c>
+      <c r="X7" t="str" s="3">
+        <v/>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
+      </c>
+      <c r="Z7" t="str">
+        <v/>
+      </c>
+      <c r="AA7" t="str">
+        <v/>
+      </c>
+      <c r="AB7" t="str">
+        <v/>
+      </c>
+      <c r="AC7" t="str">
+        <v/>
+      </c>
+      <c r="AD7" t="str">
+        <v/>
+      </c>
+      <c r="AE7" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -917,60 +1137,90 @@
         <v>Deloitte LLP</v>
       </c>
       <c r="C8" t="str" s="3">
-        <v/>
-      </c>
-      <c r="D8" t="str">
         <v>Partner</v>
       </c>
+      <c r="D8" t="str" s="3">
+        <v>Coworker: Ethan Brooks</v>
+      </c>
       <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>To Reach Out</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" s="1">
+        <v>46290</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N8" t="str" s="3">
+        <v>Follow up with Hana Kim about the strategy practice</v>
+      </c>
+      <c r="O8" t="str">
+        <v>One-Time</v>
+      </c>
+      <c r="P8" t="str">
         <v>hana.kim@example.com</v>
       </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
+      <c r="Q8" t="str">
         <v>demo/photos/hana-kim.jpg</v>
       </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v/>
-      </c>
-      <c r="J8" t="str">
-        <v>To Reach Out</v>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str" s="3">
+      <c r="R8" t="str" s="3">
+        <v/>
+      </c>
+      <c r="S8" t="str" s="3">
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <v/>
+      </c>
+      <c r="U8" t="str">
+        <v/>
+      </c>
+      <c r="V8" t="str">
+        <v/>
+      </c>
+      <c r="W8" t="str" s="3">
         <v>Leads the strategy practice</v>
       </c>
-      <c r="M8" t="str" s="3">
-        <v/>
-      </c>
-      <c r="N8" t="str" s="3">
-        <v/>
-      </c>
-      <c r="O8" t="str">
-        <v/>
-      </c>
-      <c r="P8" t="str">
-        <v/>
-      </c>
-      <c r="Q8" t="str">
-        <v/>
-      </c>
-      <c r="R8" t="str">
-        <v/>
-      </c>
-      <c r="S8" t="str">
-        <v/>
-      </c>
-      <c r="T8" t="str">
-        <v/>
-      </c>
-      <c r="U8" t="str" s="3">
+      <c r="X8" t="str" s="3">
+        <v/>
+      </c>
+      <c r="Y8" t="str">
+        <v/>
+      </c>
+      <c r="Z8" t="str">
+        <v/>
+      </c>
+      <c r="AA8" t="str">
+        <v/>
+      </c>
+      <c r="AB8" t="str">
+        <v/>
+      </c>
+      <c r="AC8" t="str">
+        <v/>
+      </c>
+      <c r="AD8" t="str">
+        <v/>
+      </c>
+      <c r="AE8" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -982,60 +1232,90 @@
         <v>Microsoft</v>
       </c>
       <c r="C9" t="str" s="3">
-        <v/>
-      </c>
-      <c r="D9" t="str">
         <v>Data Analyst</v>
       </c>
+      <c r="D9" t="str" s="3">
+        <v>Coworker: Hana Kim</v>
+      </c>
       <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>Informational</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Zoom</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Scheduled</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" s="1">
+        <v>46318</v>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N9" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
         <v>ethan.brooks@example.com</v>
       </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
+      <c r="Q9" t="str">
         <v>demo/photos/ethan-brooks.jpg</v>
       </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
-      <c r="J9" t="str">
-        <v>Scheduled</v>
-      </c>
-      <c r="K9" t="str">
+      <c r="R9" t="str" s="3">
+        <v/>
+      </c>
+      <c r="S9" t="str" s="3">
+        <v/>
+      </c>
+      <c r="T9" t="str">
         <v>Product</v>
       </c>
-      <c r="L9" t="str" s="3">
-        <v/>
-      </c>
-      <c r="M9" t="str" s="3">
-        <v/>
-      </c>
-      <c r="N9" t="str" s="3">
-        <v/>
-      </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-      <c r="P9" t="str">
-        <v/>
-      </c>
-      <c r="Q9" t="str">
-        <v/>
-      </c>
-      <c r="R9" t="str">
-        <v/>
-      </c>
-      <c r="S9" t="str">
-        <v/>
-      </c>
-      <c r="T9" t="str">
-        <v/>
-      </c>
-      <c r="U9" t="str" s="3">
+      <c r="U9" t="str">
+        <v/>
+      </c>
+      <c r="V9" t="str">
+        <v/>
+      </c>
+      <c r="W9" t="str" s="3">
+        <v/>
+      </c>
+      <c r="X9" t="str" s="3">
+        <v/>
+      </c>
+      <c r="Y9" t="str">
+        <v/>
+      </c>
+      <c r="Z9" t="str">
+        <v/>
+      </c>
+      <c r="AA9" t="str">
+        <v/>
+      </c>
+      <c r="AB9" t="str">
+        <v/>
+      </c>
+      <c r="AC9" t="str">
+        <v/>
+      </c>
+      <c r="AD9" t="str">
+        <v/>
+      </c>
+      <c r="AE9" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1047,60 +1327,90 @@
         <v>Microsoft</v>
       </c>
       <c r="C10" t="str" s="3">
-        <v/>
-      </c>
-      <c r="D10" t="str">
         <v>Program Manager</v>
       </c>
+      <c r="D10" t="str" s="3">
+        <v/>
+      </c>
       <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v>To Reach Out</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N10" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
         <v>lena.novak@example.com</v>
       </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
+      <c r="Q10" t="str">
         <v>demo/photos/lena-novak.jpg</v>
       </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v/>
-      </c>
-      <c r="J10" t="str">
-        <v>To Reach Out</v>
-      </c>
-      <c r="K10" t="str">
+      <c r="R10" t="str" s="3">
+        <v/>
+      </c>
+      <c r="S10" t="str" s="3">
+        <v/>
+      </c>
+      <c r="T10" t="str">
         <v>Product</v>
       </c>
-      <c r="L10" t="str" s="3">
-        <v/>
-      </c>
-      <c r="M10" t="str" s="3">
-        <v/>
-      </c>
-      <c r="N10" t="str" s="3">
-        <v/>
-      </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
-      <c r="P10" t="str">
-        <v/>
-      </c>
-      <c r="Q10" t="str">
-        <v/>
-      </c>
-      <c r="R10" t="str">
-        <v/>
-      </c>
-      <c r="S10" t="str">
-        <v/>
-      </c>
-      <c r="T10" t="str">
-        <v/>
-      </c>
-      <c r="U10" t="str" s="3">
+      <c r="U10" t="str">
+        <v/>
+      </c>
+      <c r="V10" t="str">
+        <v/>
+      </c>
+      <c r="W10" t="str" s="3">
+        <v/>
+      </c>
+      <c r="X10" t="str" s="3">
+        <v/>
+      </c>
+      <c r="Y10" t="str">
+        <v/>
+      </c>
+      <c r="Z10" t="str">
+        <v/>
+      </c>
+      <c r="AA10" t="str">
+        <v/>
+      </c>
+      <c r="AB10" t="str">
+        <v/>
+      </c>
+      <c r="AC10" t="str">
+        <v/>
+      </c>
+      <c r="AD10" t="str">
+        <v/>
+      </c>
+      <c r="AE10" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1112,60 +1422,90 @@
         <v>Deloitte</v>
       </c>
       <c r="C11" t="str" s="3">
-        <v/>
-      </c>
-      <c r="D11" t="str">
         <v>Campus Recruiter</v>
       </c>
+      <c r="D11" t="str" s="3">
+        <v/>
+      </c>
       <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>Interview</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Teams</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Scheduled</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" s="1">
+        <v>46299</v>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N11" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
         <v>grace.owens@example.com</v>
       </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
+      <c r="Q11" t="str">
         <v>demo/photos/grace-owens.jpg</v>
       </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v/>
-      </c>
-      <c r="J11" t="str">
-        <v>Scheduled</v>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str" s="3">
-        <v/>
-      </c>
-      <c r="M11" t="str" s="3">
-        <v/>
-      </c>
-      <c r="N11" t="str" s="3">
-        <v/>
-      </c>
-      <c r="O11" t="str">
-        <v/>
-      </c>
-      <c r="P11" t="str">
-        <v/>
-      </c>
-      <c r="Q11" t="str">
-        <v/>
-      </c>
-      <c r="R11" t="str">
-        <v/>
-      </c>
-      <c r="S11" t="str">
+      <c r="R11" t="str" s="3">
+        <v/>
+      </c>
+      <c r="S11" t="str" s="3">
         <v/>
       </c>
       <c r="T11" t="str">
         <v/>
       </c>
-      <c r="U11" t="str" s="3">
+      <c r="U11" t="str">
+        <v/>
+      </c>
+      <c r="V11" t="str">
+        <v/>
+      </c>
+      <c r="W11" t="str" s="3">
+        <v/>
+      </c>
+      <c r="X11" t="str" s="3">
+        <v/>
+      </c>
+      <c r="Y11" t="str">
+        <v/>
+      </c>
+      <c r="Z11" t="str">
+        <v/>
+      </c>
+      <c r="AA11" t="str">
+        <v/>
+      </c>
+      <c r="AB11" t="str">
+        <v/>
+      </c>
+      <c r="AC11" t="str">
+        <v/>
+      </c>
+      <c r="AD11" t="str">
+        <v/>
+      </c>
+      <c r="AE11" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1177,60 +1517,90 @@
         <v>Deloitte</v>
       </c>
       <c r="C12" t="str" s="3">
+        <v>Strategy Associate</v>
+      </c>
+      <c r="D12" t="str" s="3">
+        <v>Stanford University; Introduced you to Ben Foster; Classmate: Sofia Alvarez</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>Coffee Chat</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Zoom</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Met</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" s="1">
+        <v>46291</v>
+      </c>
+      <c r="K12" s="1">
+        <v>46292</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N12" t="str" s="3">
+        <v>Send thank-you to Daniel Ortiz within 24 hrs</v>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v>daniel.ortiz@example.com</v>
+      </c>
+      <c r="Q12" t="str">
+        <v>demo/photos/daniel-ortiz.jpg</v>
+      </c>
+      <c r="R12" t="str" s="3">
+        <v/>
+      </c>
+      <c r="S12" t="str" s="3">
         <v>Stanford University</v>
       </c>
-      <c r="D12" t="str">
-        <v>Strategy Associate</v>
-      </c>
-      <c r="E12" t="str">
-        <v>daniel.ortiz@example.com</v>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v>demo/photos/daniel-ortiz.jpg</v>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v/>
-      </c>
-      <c r="J12" t="str">
-        <v>Met</v>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str" s="3">
-        <v/>
-      </c>
-      <c r="M12" t="str" s="3">
-        <v/>
-      </c>
-      <c r="N12" t="str" s="3">
-        <v/>
-      </c>
-      <c r="O12" t="str">
-        <v/>
-      </c>
-      <c r="P12" t="str">
-        <v/>
-      </c>
-      <c r="Q12" t="str">
-        <v/>
-      </c>
-      <c r="R12" t="str">
-        <v/>
-      </c>
-      <c r="S12" t="str">
-        <v/>
-      </c>
       <c r="T12" t="str">
         <v/>
       </c>
-      <c r="U12" t="str" s="3">
+      <c r="U12" t="str">
+        <v/>
+      </c>
+      <c r="V12" t="str">
+        <v/>
+      </c>
+      <c r="W12" t="str" s="3">
+        <v/>
+      </c>
+      <c r="X12" t="str" s="3">
+        <v/>
+      </c>
+      <c r="Y12" t="str">
+        <v/>
+      </c>
+      <c r="Z12" t="str">
+        <v/>
+      </c>
+      <c r="AA12" t="str">
+        <v/>
+      </c>
+      <c r="AB12" t="str">
+        <v/>
+      </c>
+      <c r="AC12" t="str">
+        <v/>
+      </c>
+      <c r="AD12" t="str">
+        <v/>
+      </c>
+      <c r="AE12" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1242,60 +1612,90 @@
         <v>Microsoft</v>
       </c>
       <c r="C13" t="str" s="3">
-        <v/>
-      </c>
-      <c r="D13" t="str">
         <v>Associate Product Manager</v>
       </c>
+      <c r="D13" t="str" s="3">
+        <v>Mentor: Jordan Lee</v>
+      </c>
       <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v>To Reach Out</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N13" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
         <v>owen.price@example.com</v>
       </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
+      <c r="Q13" t="str">
         <v>demo/photos/owen-price.jpg</v>
       </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v/>
-      </c>
-      <c r="J13" t="str">
-        <v>To Reach Out</v>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str" s="3">
-        <v/>
-      </c>
-      <c r="M13" t="str" s="3">
-        <v/>
-      </c>
-      <c r="N13" t="str" s="3">
-        <v/>
-      </c>
-      <c r="O13" t="str">
-        <v/>
-      </c>
-      <c r="P13" t="str">
-        <v/>
-      </c>
-      <c r="Q13" t="str">
-        <v/>
-      </c>
-      <c r="R13" t="str">
-        <v/>
-      </c>
-      <c r="S13" t="str">
+      <c r="R13" t="str" s="3">
+        <v/>
+      </c>
+      <c r="S13" t="str" s="3">
         <v/>
       </c>
       <c r="T13" t="str">
         <v/>
       </c>
-      <c r="U13" t="str" s="3">
+      <c r="U13" t="str">
+        <v/>
+      </c>
+      <c r="V13" t="str">
+        <v/>
+      </c>
+      <c r="W13" t="str" s="3">
+        <v/>
+      </c>
+      <c r="X13" t="str" s="3">
+        <v/>
+      </c>
+      <c r="Y13" t="str">
+        <v/>
+      </c>
+      <c r="Z13" t="str">
+        <v/>
+      </c>
+      <c r="AA13" t="str">
+        <v/>
+      </c>
+      <c r="AB13" t="str">
+        <v/>
+      </c>
+      <c r="AC13" t="str">
+        <v/>
+      </c>
+      <c r="AD13" t="str">
+        <v/>
+      </c>
+      <c r="AE13" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1307,60 +1707,90 @@
         <v>Microsoft</v>
       </c>
       <c r="C14" t="str" s="3">
-        <v/>
-      </c>
-      <c r="D14" t="str">
         <v>Operations Lead</v>
       </c>
+      <c r="D14" t="str" s="3">
+        <v/>
+      </c>
       <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v>Met</v>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N14" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
         <v>ava.thompson@example.com</v>
       </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
+      <c r="Q14" t="str">
         <v>demo/photos/ava-thompson.jpg</v>
       </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v/>
-      </c>
-      <c r="J14" t="str">
-        <v>Met</v>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str" s="3">
-        <v/>
-      </c>
-      <c r="M14" t="str" s="3">
-        <v/>
-      </c>
-      <c r="N14" t="str" s="3">
-        <v/>
-      </c>
-      <c r="O14" t="str">
-        <v/>
-      </c>
-      <c r="P14" t="str">
-        <v/>
-      </c>
-      <c r="Q14" t="str">
-        <v/>
-      </c>
-      <c r="R14" t="str">
-        <v/>
-      </c>
-      <c r="S14" t="str">
+      <c r="R14" t="str" s="3">
+        <v/>
+      </c>
+      <c r="S14" t="str" s="3">
         <v/>
       </c>
       <c r="T14" t="str">
         <v/>
       </c>
-      <c r="U14" t="str" s="3">
+      <c r="U14" t="str">
+        <v/>
+      </c>
+      <c r="V14" t="str">
+        <v/>
+      </c>
+      <c r="W14" t="str" s="3">
+        <v/>
+      </c>
+      <c r="X14" t="str" s="3">
+        <v/>
+      </c>
+      <c r="Y14" t="str">
+        <v/>
+      </c>
+      <c r="Z14" t="str">
+        <v/>
+      </c>
+      <c r="AA14" t="str">
+        <v/>
+      </c>
+      <c r="AB14" t="str">
+        <v/>
+      </c>
+      <c r="AC14" t="str">
+        <v/>
+      </c>
+      <c r="AD14" t="str">
+        <v/>
+      </c>
+      <c r="AE14" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1372,60 +1802,90 @@
         <v>Independent</v>
       </c>
       <c r="C15" t="str" s="3">
-        <v/>
-      </c>
-      <c r="D15" t="str">
         <v>Founder</v>
       </c>
+      <c r="D15" t="str" s="3">
+        <v>Introduced you to Zoe Adams; Friend: Mia Chen</v>
+      </c>
       <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>Coffee Chat</v>
+      </c>
+      <c r="G15" t="str">
+        <v>In Person</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Met</v>
+      </c>
+      <c r="I15" s="1">
+        <v>46174</v>
+      </c>
+      <c r="J15" s="1">
+        <v>46263</v>
+      </c>
+      <c r="K15" s="1">
+        <v>46296</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N15" t="str" s="3">
+        <v>Ask Liam for the intro to Zoe Adams</v>
+      </c>
+      <c r="O15" t="str">
+        <v>Keep In Contact</v>
+      </c>
+      <c r="P15" t="str">
         <v>liam.walsh@example.com</v>
       </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
+      <c r="Q15" t="str">
         <v>demo/photos/liam-walsh.jpg</v>
       </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15" t="str">
-        <v>Met</v>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str" s="3">
+      <c r="R15" t="str" s="3">
+        <v/>
+      </c>
+      <c r="S15" t="str" s="3">
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <v/>
+      </c>
+      <c r="U15" t="str">
+        <v/>
+      </c>
+      <c r="V15" t="str">
+        <v/>
+      </c>
+      <c r="W15" t="str" s="3">
         <v>Old roommate</v>
       </c>
-      <c r="M15" t="str" s="3">
-        <v/>
-      </c>
-      <c r="N15" t="str" s="3">
-        <v/>
-      </c>
-      <c r="O15" t="str">
-        <v/>
-      </c>
-      <c r="P15" t="str">
-        <v/>
-      </c>
-      <c r="Q15" t="str">
-        <v/>
-      </c>
-      <c r="R15" t="str">
-        <v/>
-      </c>
-      <c r="S15" t="str">
-        <v/>
-      </c>
-      <c r="T15" t="str">
-        <v/>
-      </c>
-      <c r="U15" t="str" s="3">
+      <c r="X15" t="str" s="3">
+        <v/>
+      </c>
+      <c r="Y15" t="str">
+        <v/>
+      </c>
+      <c r="Z15" t="str">
+        <v/>
+      </c>
+      <c r="AA15" t="str">
+        <v/>
+      </c>
+      <c r="AB15" t="str">
+        <v/>
+      </c>
+      <c r="AC15" t="str">
+        <v/>
+      </c>
+      <c r="AD15" t="str">
+        <v/>
+      </c>
+      <c r="AE15" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1437,11 +1897,11 @@
         <v>Deloitte</v>
       </c>
       <c r="C16" t="str" s="3">
-        <v/>
-      </c>
-      <c r="D16" t="str">
         <v>Principal</v>
       </c>
+      <c r="D16" t="str" s="3">
+        <v>Introduced by Jordan Lee</v>
+      </c>
       <c r="E16" t="str">
         <v/>
       </c>
@@ -1449,48 +1909,78 @@
         <v/>
       </c>
       <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v>To Reach Out</v>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N16" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
         <v>demo/photos/rachel-green.jpg</v>
       </c>
-      <c r="H16" t="str">
+      <c r="R16" t="str" s="3">
+        <v/>
+      </c>
+      <c r="S16" t="str" s="3">
+        <v/>
+      </c>
+      <c r="T16" t="str">
+        <v/>
+      </c>
+      <c r="U16" t="str">
+        <v/>
+      </c>
+      <c r="V16" t="str">
         <v>Jordan Lee</v>
       </c>
-      <c r="I16" t="str">
-        <v/>
-      </c>
-      <c r="J16" t="str">
-        <v>To Reach Out</v>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str" s="3">
+      <c r="W16" t="str" s="3">
         <v>Jordan offered an intro</v>
       </c>
-      <c r="M16" t="str" s="3">
-        <v/>
-      </c>
-      <c r="N16" t="str" s="3">
-        <v/>
-      </c>
-      <c r="O16" t="str">
-        <v/>
-      </c>
-      <c r="P16" t="str">
-        <v/>
-      </c>
-      <c r="Q16" t="str">
-        <v/>
-      </c>
-      <c r="R16" t="str">
-        <v/>
-      </c>
-      <c r="S16" t="str">
-        <v/>
-      </c>
-      <c r="T16" t="str">
-        <v/>
-      </c>
-      <c r="U16" t="str" s="3">
+      <c r="X16" t="str" s="3">
+        <v/>
+      </c>
+      <c r="Y16" t="str">
+        <v/>
+      </c>
+      <c r="Z16" t="str">
+        <v/>
+      </c>
+      <c r="AA16" t="str">
+        <v/>
+      </c>
+      <c r="AB16" t="str">
+        <v/>
+      </c>
+      <c r="AC16" t="str">
+        <v/>
+      </c>
+      <c r="AD16" t="str">
+        <v/>
+      </c>
+      <c r="AE16" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1502,11 +1992,11 @@
         <v>Microsoft</v>
       </c>
       <c r="C17" t="str" s="3">
-        <v/>
-      </c>
-      <c r="D17" t="str">
         <v>Director of Product</v>
       </c>
+      <c r="D17" t="str" s="3">
+        <v>Introduced by Sofia Alvarez</v>
+      </c>
       <c r="E17" t="str">
         <v/>
       </c>
@@ -1514,48 +2004,78 @@
         <v/>
       </c>
       <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v>To Reach Out</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N17" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
         <v>demo/photos/tom-nguyen.jpg</v>
       </c>
-      <c r="H17" t="str">
+      <c r="R17" t="str" s="3">
+        <v/>
+      </c>
+      <c r="S17" t="str" s="3">
+        <v/>
+      </c>
+      <c r="T17" t="str">
+        <v>Product</v>
+      </c>
+      <c r="U17" t="str">
+        <v/>
+      </c>
+      <c r="V17" t="str">
         <v>Sofia Alvarez</v>
       </c>
-      <c r="I17" t="str">
-        <v/>
-      </c>
-      <c r="J17" t="str">
-        <v>To Reach Out</v>
-      </c>
-      <c r="K17" t="str">
-        <v>Product</v>
-      </c>
-      <c r="L17" t="str" s="3">
-        <v/>
-      </c>
-      <c r="M17" t="str" s="3">
-        <v/>
-      </c>
-      <c r="N17" t="str" s="3">
-        <v/>
-      </c>
-      <c r="O17" t="str">
-        <v/>
-      </c>
-      <c r="P17" t="str">
-        <v/>
-      </c>
-      <c r="Q17" t="str">
-        <v/>
-      </c>
-      <c r="R17" t="str">
-        <v/>
-      </c>
-      <c r="S17" t="str">
-        <v/>
-      </c>
-      <c r="T17" t="str">
-        <v/>
-      </c>
-      <c r="U17" t="str" s="3">
+      <c r="W17" t="str" s="3">
+        <v/>
+      </c>
+      <c r="X17" t="str" s="3">
+        <v/>
+      </c>
+      <c r="Y17" t="str">
+        <v/>
+      </c>
+      <c r="Z17" t="str">
+        <v/>
+      </c>
+      <c r="AA17" t="str">
+        <v/>
+      </c>
+      <c r="AB17" t="str">
+        <v/>
+      </c>
+      <c r="AC17" t="str">
+        <v/>
+      </c>
+      <c r="AD17" t="str">
+        <v/>
+      </c>
+      <c r="AE17" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1567,11 +2087,11 @@
         <v>Microsoft</v>
       </c>
       <c r="C18" t="str" s="3">
-        <v/>
-      </c>
-      <c r="D18" t="str">
         <v>UX Researcher</v>
       </c>
+      <c r="D18" t="str" s="3">
+        <v>Introduced by Sofia Alvarez</v>
+      </c>
       <c r="E18" t="str">
         <v/>
       </c>
@@ -1579,48 +2099,78 @@
         <v/>
       </c>
       <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N18" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
         <v>demo/photos/isla-moore.jpg</v>
       </c>
-      <c r="H18" t="str">
+      <c r="R18" t="str" s="3">
+        <v/>
+      </c>
+      <c r="S18" t="str" s="3">
+        <v/>
+      </c>
+      <c r="T18" t="str">
+        <v>Product</v>
+      </c>
+      <c r="U18" t="str">
+        <v/>
+      </c>
+      <c r="V18" t="str">
         <v>Sofia Alvarez</v>
       </c>
-      <c r="I18" t="str">
-        <v/>
-      </c>
-      <c r="J18" t="str">
-        <v/>
-      </c>
-      <c r="K18" t="str">
-        <v>Product</v>
-      </c>
-      <c r="L18" t="str" s="3">
-        <v/>
-      </c>
-      <c r="M18" t="str" s="3">
-        <v/>
-      </c>
-      <c r="N18" t="str" s="3">
-        <v/>
-      </c>
-      <c r="O18" t="str">
-        <v/>
-      </c>
-      <c r="P18" t="str">
-        <v/>
-      </c>
-      <c r="Q18" t="str">
-        <v/>
-      </c>
-      <c r="R18" t="str">
-        <v/>
-      </c>
-      <c r="S18" t="str">
-        <v/>
-      </c>
-      <c r="T18" t="str">
-        <v/>
-      </c>
-      <c r="U18" t="str" s="3">
+      <c r="W18" t="str" s="3">
+        <v/>
+      </c>
+      <c r="X18" t="str" s="3">
+        <v/>
+      </c>
+      <c r="Y18" t="str">
+        <v/>
+      </c>
+      <c r="Z18" t="str">
+        <v/>
+      </c>
+      <c r="AA18" t="str">
+        <v/>
+      </c>
+      <c r="AB18" t="str">
+        <v/>
+      </c>
+      <c r="AC18" t="str">
+        <v/>
+      </c>
+      <c r="AD18" t="str">
+        <v/>
+      </c>
+      <c r="AE18" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1632,11 +2182,11 @@
         <v>Microsoft</v>
       </c>
       <c r="C19" t="str" s="3">
-        <v/>
-      </c>
-      <c r="D19" t="str">
         <v>VP of Strategy</v>
       </c>
+      <c r="D19" t="str" s="3">
+        <v>Introduced by Noah Carter</v>
+      </c>
       <c r="E19" t="str">
         <v/>
       </c>
@@ -1644,48 +2194,78 @@
         <v/>
       </c>
       <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N19" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
         <v>demo/photos/victor-hale.jpg</v>
       </c>
-      <c r="H19" t="str">
+      <c r="R19" t="str" s="3">
+        <v/>
+      </c>
+      <c r="S19" t="str" s="3">
+        <v/>
+      </c>
+      <c r="T19" t="str">
+        <v/>
+      </c>
+      <c r="U19" t="str">
+        <v/>
+      </c>
+      <c r="V19" t="str">
         <v>Noah Carter</v>
       </c>
-      <c r="I19" t="str">
-        <v/>
-      </c>
-      <c r="J19" t="str">
-        <v/>
-      </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
-      <c r="L19" t="str" s="3">
-        <v/>
-      </c>
-      <c r="M19" t="str" s="3">
-        <v/>
-      </c>
-      <c r="N19" t="str" s="3">
-        <v/>
-      </c>
-      <c r="O19" t="str">
-        <v/>
-      </c>
-      <c r="P19" t="str">
-        <v/>
-      </c>
-      <c r="Q19" t="str">
-        <v/>
-      </c>
-      <c r="R19" t="str">
-        <v/>
-      </c>
-      <c r="S19" t="str">
-        <v/>
-      </c>
-      <c r="T19" t="str">
-        <v/>
-      </c>
-      <c r="U19" t="str" s="3">
+      <c r="W19" t="str" s="3">
+        <v/>
+      </c>
+      <c r="X19" t="str" s="3">
+        <v/>
+      </c>
+      <c r="Y19" t="str">
+        <v/>
+      </c>
+      <c r="Z19" t="str">
+        <v/>
+      </c>
+      <c r="AA19" t="str">
+        <v/>
+      </c>
+      <c r="AB19" t="str">
+        <v/>
+      </c>
+      <c r="AC19" t="str">
+        <v/>
+      </c>
+      <c r="AD19" t="str">
+        <v/>
+      </c>
+      <c r="AE19" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1697,11 +2277,11 @@
         <v>Microsoft</v>
       </c>
       <c r="C20" t="str" s="3">
-        <v/>
-      </c>
-      <c r="D20" t="str">
         <v>Design Manager</v>
       </c>
+      <c r="D20" t="str" s="3">
+        <v>Introduced by Mia Chen</v>
+      </c>
       <c r="E20" t="str">
         <v/>
       </c>
@@ -1709,48 +2289,78 @@
         <v/>
       </c>
       <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N20" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
         <v>demo/photos/chloe-park.jpg</v>
       </c>
-      <c r="H20" t="str">
+      <c r="R20" t="str" s="3">
+        <v/>
+      </c>
+      <c r="S20" t="str" s="3">
+        <v/>
+      </c>
+      <c r="T20" t="str">
+        <v/>
+      </c>
+      <c r="U20" t="str">
+        <v/>
+      </c>
+      <c r="V20" t="str">
         <v>Mia Chen</v>
       </c>
-      <c r="I20" t="str">
-        <v/>
-      </c>
-      <c r="J20" t="str">
-        <v/>
-      </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-      <c r="L20" t="str" s="3">
-        <v/>
-      </c>
-      <c r="M20" t="str" s="3">
-        <v/>
-      </c>
-      <c r="N20" t="str" s="3">
-        <v/>
-      </c>
-      <c r="O20" t="str">
-        <v/>
-      </c>
-      <c r="P20" t="str">
-        <v/>
-      </c>
-      <c r="Q20" t="str">
-        <v/>
-      </c>
-      <c r="R20" t="str">
-        <v/>
-      </c>
-      <c r="S20" t="str">
-        <v/>
-      </c>
-      <c r="T20" t="str">
-        <v/>
-      </c>
-      <c r="U20" t="str" s="3">
+      <c r="W20" t="str" s="3">
+        <v/>
+      </c>
+      <c r="X20" t="str" s="3">
+        <v/>
+      </c>
+      <c r="Y20" t="str">
+        <v/>
+      </c>
+      <c r="Z20" t="str">
+        <v/>
+      </c>
+      <c r="AA20" t="str">
+        <v/>
+      </c>
+      <c r="AB20" t="str">
+        <v/>
+      </c>
+      <c r="AC20" t="str">
+        <v/>
+      </c>
+      <c r="AD20" t="str">
+        <v/>
+      </c>
+      <c r="AE20" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1762,11 +2372,11 @@
         <v>Stanford University</v>
       </c>
       <c r="C21" t="str" s="3">
-        <v/>
-      </c>
-      <c r="D21" t="str">
         <v>Career Coach</v>
       </c>
+      <c r="D21" t="str" s="3">
+        <v>Introduced by Daniel Ortiz</v>
+      </c>
       <c r="E21" t="str">
         <v/>
       </c>
@@ -1774,48 +2384,78 @@
         <v/>
       </c>
       <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N21" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
         <v>demo/photos/ben-foster.jpg</v>
       </c>
-      <c r="H21" t="str">
+      <c r="R21" t="str" s="3">
+        <v/>
+      </c>
+      <c r="S21" t="str" s="3">
+        <v/>
+      </c>
+      <c r="T21" t="str">
+        <v/>
+      </c>
+      <c r="U21" t="str">
+        <v/>
+      </c>
+      <c r="V21" t="str">
         <v>Daniel Ortiz</v>
       </c>
-      <c r="I21" t="str">
-        <v/>
-      </c>
-      <c r="J21" t="str">
-        <v/>
-      </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21" t="str" s="3">
-        <v/>
-      </c>
-      <c r="M21" t="str" s="3">
-        <v/>
-      </c>
-      <c r="N21" t="str" s="3">
-        <v/>
-      </c>
-      <c r="O21" t="str">
-        <v/>
-      </c>
-      <c r="P21" t="str">
-        <v/>
-      </c>
-      <c r="Q21" t="str">
-        <v/>
-      </c>
-      <c r="R21" t="str">
-        <v/>
-      </c>
-      <c r="S21" t="str">
-        <v/>
-      </c>
-      <c r="T21" t="str">
-        <v/>
-      </c>
-      <c r="U21" t="str" s="3">
+      <c r="W21" t="str" s="3">
+        <v/>
+      </c>
+      <c r="X21" t="str" s="3">
+        <v/>
+      </c>
+      <c r="Y21" t="str">
+        <v/>
+      </c>
+      <c r="Z21" t="str">
+        <v/>
+      </c>
+      <c r="AA21" t="str">
+        <v/>
+      </c>
+      <c r="AB21" t="str">
+        <v/>
+      </c>
+      <c r="AC21" t="str">
+        <v/>
+      </c>
+      <c r="AD21" t="str">
+        <v/>
+      </c>
+      <c r="AE21" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1827,11 +2467,11 @@
         <v>Microsoft</v>
       </c>
       <c r="C22" t="str" s="3">
-        <v/>
-      </c>
-      <c r="D22" t="str">
         <v>Director of Strategy</v>
       </c>
+      <c r="D22" t="str" s="3">
+        <v>Introduced by Liam Walsh; Introduced you to Sam Rivera</v>
+      </c>
       <c r="E22" t="str">
         <v/>
       </c>
@@ -1839,48 +2479,78 @@
         <v/>
       </c>
       <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N22" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
         <v>demo/photos/zoe-adams.jpg</v>
       </c>
-      <c r="H22" t="str">
+      <c r="R22" t="str" s="3">
+        <v/>
+      </c>
+      <c r="S22" t="str" s="3">
+        <v/>
+      </c>
+      <c r="T22" t="str">
+        <v/>
+      </c>
+      <c r="U22" t="str">
+        <v/>
+      </c>
+      <c r="V22" t="str">
         <v>Liam Walsh</v>
       </c>
-      <c r="I22" t="str">
-        <v/>
-      </c>
-      <c r="J22" t="str">
-        <v/>
-      </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22" t="str" s="3">
-        <v/>
-      </c>
-      <c r="M22" t="str" s="3">
-        <v/>
-      </c>
-      <c r="N22" t="str" s="3">
-        <v/>
-      </c>
-      <c r="O22" t="str">
-        <v/>
-      </c>
-      <c r="P22" t="str">
-        <v/>
-      </c>
-      <c r="Q22" t="str">
-        <v/>
-      </c>
-      <c r="R22" t="str">
-        <v/>
-      </c>
-      <c r="S22" t="str">
-        <v/>
-      </c>
-      <c r="T22" t="str">
-        <v/>
-      </c>
-      <c r="U22" t="str" s="3">
+      <c r="W22" t="str" s="3">
+        <v/>
+      </c>
+      <c r="X22" t="str" s="3">
+        <v/>
+      </c>
+      <c r="Y22" t="str">
+        <v/>
+      </c>
+      <c r="Z22" t="str">
+        <v/>
+      </c>
+      <c r="AA22" t="str">
+        <v/>
+      </c>
+      <c r="AB22" t="str">
+        <v/>
+      </c>
+      <c r="AC22" t="str">
+        <v/>
+      </c>
+      <c r="AD22" t="str">
+        <v/>
+      </c>
+      <c r="AE22" t="str" s="3">
         <v/>
       </c>
     </row>
@@ -1892,11 +2562,11 @@
         <v>Microsoft</v>
       </c>
       <c r="C23" t="str" s="3">
-        <v/>
-      </c>
-      <c r="D23" t="str">
         <v>Head of Growth</v>
       </c>
+      <c r="D23" t="str" s="3">
+        <v>Introduced by Zoe Adams</v>
+      </c>
       <c r="E23" t="str">
         <v/>
       </c>
@@ -1904,902 +2574,128 @@
         <v/>
       </c>
       <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str" s="3">
+        <v/>
+      </c>
+      <c r="N23" t="str" s="3">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
         <v>demo/photos/sam-rivera.jpg</v>
       </c>
-      <c r="H23" t="str">
+      <c r="R23" t="str" s="3">
+        <v/>
+      </c>
+      <c r="S23" t="str" s="3">
+        <v/>
+      </c>
+      <c r="T23" t="str">
+        <v/>
+      </c>
+      <c r="U23" t="str">
+        <v/>
+      </c>
+      <c r="V23" t="str">
         <v>Zoe Adams</v>
       </c>
-      <c r="I23" t="str">
-        <v/>
-      </c>
-      <c r="J23" t="str">
-        <v/>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23" t="str" s="3">
+      <c r="W23" t="str" s="3">
         <v>3rd-degree example</v>
       </c>
-      <c r="M23" t="str" s="3">
-        <v/>
-      </c>
-      <c r="N23" t="str" s="3">
-        <v/>
-      </c>
-      <c r="O23" t="str">
-        <v/>
-      </c>
-      <c r="P23" t="str">
-        <v/>
-      </c>
-      <c r="Q23" t="str">
-        <v/>
-      </c>
-      <c r="R23" t="str">
-        <v/>
-      </c>
-      <c r="S23" t="str">
-        <v/>
-      </c>
-      <c r="T23" t="str">
-        <v/>
-      </c>
-      <c r="U23" t="str" s="3">
+      <c r="X23" t="str" s="3">
+        <v/>
+      </c>
+      <c r="Y23" t="str">
+        <v/>
+      </c>
+      <c r="Z23" t="str">
+        <v/>
+      </c>
+      <c r="AA23" t="str">
+        <v/>
+      </c>
+      <c r="AB23" t="str">
+        <v/>
+      </c>
+      <c r="AC23" t="str">
+        <v/>
+      </c>
+      <c r="AD23" t="str">
+        <v/>
+      </c>
+      <c r="AE23" t="str" s="3">
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U23"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="J2:J1000">
+  <autoFilter ref="A1:AE23"/>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="H2:H1000">
       <formula1>"To Reach Out,Contacted,Scheduled,Met,Follow Up,Referral"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="F2:F1000">
+      <formula1>"Coffee Chat,Informational,Networking Event,Class/Club,Interview,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="G2:G1000">
+      <formula1>"Zoom,Google Meet,Teams,Phone,In Person,Email,LinkedIn"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="L2:L1000">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="O2:O1000">
+      <formula1>"Keep In Contact,Follow Up Later,One-Time"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" display="jordan.lee@example.com"/>
-    <hyperlink ref="E3" r:id="rId2" display="priya.shah@example.com"/>
-    <hyperlink ref="E4" r:id="rId3" display="sofia.alvarez@example.com"/>
-    <hyperlink ref="E5" r:id="rId4" display="noah.carter@example.com"/>
-    <hyperlink ref="E6" r:id="rId5" display="mia.chen@example.com"/>
-    <hyperlink ref="E7" r:id="rId6" display="marcus.bell@example.com"/>
-    <hyperlink ref="E8" r:id="rId7" display="hana.kim@example.com"/>
-    <hyperlink ref="E9" r:id="rId8" display="ethan.brooks@example.com"/>
-    <hyperlink ref="E10" r:id="rId9" display="lena.novak@example.com"/>
-    <hyperlink ref="E11" r:id="rId10" display="grace.owens@example.com"/>
-    <hyperlink ref="E12" r:id="rId11" display="daniel.ortiz@example.com"/>
-    <hyperlink ref="E13" r:id="rId12" display="owen.price@example.com"/>
-    <hyperlink ref="E14" r:id="rId13" display="ava.thompson@example.com"/>
-    <hyperlink ref="E15" r:id="rId14" display="liam.walsh@example.com"/>
+    <hyperlink ref="E2" r:id="rId1" tooltip="https://www.linkedin.com/in/jordan-lee-3f9a21" display="Profile"/>
+    <hyperlink ref="P2" r:id="rId2" display="jordan.lee@example.com"/>
+    <hyperlink ref="E3" r:id="rId3" tooltip="https://www.linkedin.com/in/priya-shah-77b0c4" display="Profile"/>
+    <hyperlink ref="P3" r:id="rId4" display="priya.shah@example.com"/>
+    <hyperlink ref="E4" r:id="rId5" tooltip="https://www.linkedin.com/in/sofia-alvarez-5d2e18" display="Profile"/>
+    <hyperlink ref="P4" r:id="rId6" display="sofia.alvarez@example.com"/>
+    <hyperlink ref="E5" r:id="rId7" tooltip="https://www.linkedin.com/in/noah-carter-a41b77" display="Profile"/>
+    <hyperlink ref="P5" r:id="rId8" display="noah.carter@example.com"/>
+    <hyperlink ref="E6" r:id="rId9" tooltip="https://www.linkedin.com/in/mia-chen-0c8e42" display="Profile"/>
+    <hyperlink ref="P6" r:id="rId10" display="mia.chen@example.com"/>
+    <hyperlink ref="P7" r:id="rId11" display="marcus.bell@example.com"/>
+    <hyperlink ref="P8" r:id="rId12" display="hana.kim@example.com"/>
+    <hyperlink ref="P9" r:id="rId13" display="ethan.brooks@example.com"/>
+    <hyperlink ref="P10" r:id="rId14" display="lena.novak@example.com"/>
+    <hyperlink ref="P11" r:id="rId15" display="grace.owens@example.com"/>
+    <hyperlink ref="P12" r:id="rId16" display="daniel.ortiz@example.com"/>
+    <hyperlink ref="P13" r:id="rId17" display="owen.price@example.com"/>
+    <hyperlink ref="P14" r:id="rId18" display="ava.thompson@example.com"/>
+    <hyperlink ref="P15" r:id="rId19" display="liam.walsh@example.com"/>
   </hyperlinks>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE23"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
-  <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="41.83203125" customWidth="1"/>
-    <col min="4" max="4" width="34.83203125" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str" s="2">
-        <v>Person</v>
-      </c>
-      <c r="B1" t="str" s="2">
-        <v>School</v>
-      </c>
-      <c r="C1" t="str" s="2">
-        <v>Degree</v>
-      </c>
-      <c r="D1" t="str" s="2">
-        <v>Field</v>
-      </c>
-      <c r="E1" t="str" s="2">
-        <v>Start</v>
-      </c>
-      <c r="F1" t="str" s="2">
-        <v>End</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Sofia Alvarez</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Stanford University</v>
-      </c>
-      <c r="C2" t="str" s="3">
-        <v>Master of Business Administration - MBA</v>
-      </c>
-      <c r="D2" t="str" s="3">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v>2021</v>
-      </c>
-      <c r="F2" t="str">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Sofia Alvarez</v>
-      </c>
-      <c r="B3" t="str">
-        <v>University of Washington</v>
-      </c>
-      <c r="C3" t="str" s="3">
-        <v>Bachelor of Science - BS</v>
-      </c>
-      <c r="D3" t="str" s="3">
-        <v>Information Systems</v>
-      </c>
-      <c r="E3" t="str">
-        <v>2014</v>
-      </c>
-      <c r="F3" t="str">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Jordan Lee</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Stanford University</v>
-      </c>
-      <c r="C4" t="str" s="3">
-        <v>Bachelor of Arts - BA</v>
-      </c>
-      <c r="D4" t="str" s="3">
-        <v>Economics</v>
-      </c>
-      <c r="E4" t="str">
-        <v>2016</v>
-      </c>
-      <c r="F4" t="str">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Noah Carter</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Stanford University</v>
-      </c>
-      <c r="C5" t="str" s="3">
-        <v>Master of Science - MS</v>
-      </c>
-      <c r="D5" t="str" s="3">
-        <v>Management Science &amp; Engineering</v>
-      </c>
-      <c r="E5" t="str">
-        <v>2019</v>
-      </c>
-      <c r="F5" t="str">
-        <v>2021</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B18"/>
-  <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="60.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str" s="2">
-        <v>Field</v>
-      </c>
-      <c r="B1" t="str" s="2">
-        <v>Value</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B2" t="str" s="3">
-        <v>Alex Rivera</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Photo</v>
-      </c>
-      <c r="B3" t="str" s="3">
-        <v>demo/photos/alex-rivera.jpg</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Role</v>
-      </c>
-      <c r="B4" t="str" s="3">
-        <v>MBA Candidate</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Headline</v>
-      </c>
-      <c r="B5" t="str" s="3">
-        <v>Stanford MBA '27 · Looking for strategy &amp; product roles</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Company</v>
-      </c>
-      <c r="B6" t="str" s="3">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Schools</v>
-      </c>
-      <c r="B7" t="str" s="3">
-        <v>Stanford University (2025–2027); University of Washington (2016–2020)</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Past Companies</v>
-      </c>
-      <c r="B8" t="str" s="3">
-        <v>Delta Air Lines (2020–2022); Adobe (2022–2025)</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Email</v>
-      </c>
-      <c r="B9" t="str" s="3">
-        <v>alex.rivera@example.com</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>LinkedIn URL</v>
-      </c>
-      <c r="B10" t="str" s="3">
-        <v>https://www.linkedin.com/in/alex-rivera-demo</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Location</v>
-      </c>
-      <c r="B11" t="str" s="3">
-        <v>Palo Alto, California</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str">
-        <v>What I'm looking for</v>
-      </c>
-      <c r="B12" t="str" xml:space="preserve" s="3">
-        <v xml:space="preserve">Summer 2027 internships in strategy or product at consumer-tech and airline companies.
-Happy to swap notes on case prep and product sense interviews.</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>About</v>
-      </c>
-      <c r="B13" t="str" s="3">
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Industry</v>
-      </c>
-      <c r="B14" t="str" s="3">
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Websites</v>
-      </c>
-      <c r="B15" t="str" s="3">
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Skills</v>
-      </c>
-      <c r="B16" t="str" s="3">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Certifications</v>
-      </c>
-      <c r="B17" t="str" s="3">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Volunteering</v>
-      </c>
-      <c r="B18" t="str" s="3">
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="60.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str" s="2">
-        <v>Setting</v>
-      </c>
-      <c r="B1" t="str" s="2">
-        <v>Value</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Your name</v>
-      </c>
-      <c r="B2" t="str" s="3">
-        <v>Alex Rivera</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Avatar style</v>
-      </c>
-      <c r="B3" t="str" s="3">
-        <v>notionists</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Your email</v>
-      </c>
-      <c r="B4" t="str" s="3">
-        <v>alex.rivera@example.com</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Meeting length (minutes)</v>
-      </c>
-      <c r="B5" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Zoom link</v>
-      </c>
-      <c r="B6" t="str" s="3">
-        <v>https://zoom.us/j/0000000000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Check-in every (days)</v>
-      </c>
-      <c r="B7" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Invite message</v>
-      </c>
-      <c r="B8" t="str" s="3">
-        <v>Hi {first name}, looking forward to our chat on {date} at {time}. {link}</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Group size (people)</v>
-      </c>
-      <c r="B9" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Group by</v>
-      </c>
-      <c r="B10" t="str" s="3">
-        <v>company, school</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Demo base date</v>
-      </c>
-      <c r="B11" t="str" s="3">
-        <v>2026-09-28</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1"/>
-  <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="8.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Node</v>
-      </c>
-      <c r="B1" t="str">
-        <v>X</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B21"/>
-  <cols>
-    <col min="1" max="1" customWidth="1" width="22.83203125"/>
-    <col min="2" max="2" customWidth="1" width="110.83203125"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Sheet / column</v>
-      </c>
-      <c r="B1" t="str">
-        <v>What to put there</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>People</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Everyone on your map. Only Name is required.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v xml:space="preserve">  Name</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Full name, spelled the same way everywhere.</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v xml:space="preserve">  Company / School</v>
-      </c>
-      <c r="B4" t="str">
-        <v>3+ direct connections at one company or school become a group bubble. 'Stanford' and 'Stanford University' count as the same.</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v xml:space="preserve">  Email</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Shown in the details panel with a copy button.</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v xml:space="preserve">  LinkedIn URL</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Their profile link. Double-click them on the map to open it.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v xml:space="preserve">  Photo</v>
-      </c>
-      <c r="B7" t="str">
-        <v>An image link, or use 'Add photo' in the app (it stores a small picture here). LinkedIn exports don't include photos.</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v xml:space="preserve">  Connected Through</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Leave BLANK if you know them directly. Otherwise put the name of the person who connects you; they appear as a 2nd-degree connection.</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v xml:space="preserve">  Connected On</v>
-      </c>
-      <c r="B9" t="str">
-        <v>The date you connected (filled in from LinkedIn).</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v xml:space="preserve">  Status</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Met / Contacted / To Reach Out / Follow Up / Referral.</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v xml:space="preserve">  Tags, Notes</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Anything you want to remember. Tags are comma-separated.</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Targets</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Companies you want to work at. Priority (1 = highest) and Stage (Researching / Networking / Applied / Interviewing / Offer) are optional.</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Companies</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Optional. Set a company's Website (e.g. byu.edu) if its logo comes out wrong, or put an image link in Logo.</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>LinkedIn Pool</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Filled by 'Import LinkedIn' from your Connections.csv. These people are NOT on the map until you add them.</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Connections</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Who knows whom: Person A, Person B, Type (Introduced me, Coworker, Classmate, Friend, Mentor, or anything else), Notes. 'Introduced me' means A introduced you to B; it's kept in sync with People → Connected Through.</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Me</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Your own profile: photo, role, schools, past companies, what you're looking for.</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Meetings</v>
-      </c>
-      <c r="B17" t="str">
-        <v>One row per meeting: Person, Date, Start, End, Type, Method, Notes, Next Step. The app fills this when you schedule or log a meeting.</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Tasks</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Your to-dos: Task, Person, Company, Due, Done. Scheduling a meeting adds a 'Send thank-you' task automatically.</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Settings</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Your name and email, default meeting length, your Zoom link (used in invites), the invite message, and Avatar style (initials or notionists).</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Layout</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Managed by the app (saved node positions).</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>Privacy</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Orbit runs entirely in your browser. This file is never uploaded anywhere.</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B21"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
-  <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="13.83203125" customWidth="1"/>
-    <col min="4" max="4" width="60.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str" s="2">
-        <v>Company</v>
-      </c>
-      <c r="B1" t="str" s="2">
-        <v>Priority</v>
-      </c>
-      <c r="C1" t="str" s="2">
-        <v>Stage</v>
-      </c>
-      <c r="D1" t="str" s="2">
-        <v>Notes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Deloitte</v>
-      </c>
-      <c r="B2" t="str">
-        <v>1</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Networking</v>
-      </c>
-      <c r="D2" t="str" s="3">
-        <v>Strategy practice</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Google</v>
-      </c>
-      <c r="B3" t="str">
-        <v>1</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Researching</v>
-      </c>
-      <c r="D3" t="str" s="3">
-        <v>No one on the map yet: two people there are in your LinkedIn pool</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Microsoft</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Networking</v>
-      </c>
-      <c r="D4" t="str" s="3">
-        <v>Product roles; Sofia is the warmest way in</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="B2:B1000">
-      <formula1>"1,2,3"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="C2:C1000">
-      <formula1>"Researching,Networking,Applied,Interviewing,Offer"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C12"/>
-  <cols>
-    <col min="1" max="1" width="21.83203125" customWidth="1"/>
-    <col min="2" max="2" width="21.83203125" customWidth="1"/>
-    <col min="3" max="3" width="35.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str" s="2">
-        <v>Company</v>
-      </c>
-      <c r="B1" t="str" s="2">
-        <v>Website</v>
-      </c>
-      <c r="C1" t="str" s="2">
-        <v>Logo</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Deloitte</v>
-      </c>
-      <c r="B2" t="str">
-        <v>deloitte.com</v>
-      </c>
-      <c r="C2" t="str">
-        <v>demo/logos/deloitte.svg</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Delta Air Lines</v>
-      </c>
-      <c r="B3" t="str">
-        <v>delta.com</v>
-      </c>
-      <c r="C3" t="str">
-        <v>demo/logos/delta.svg</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Goldman Sachs</v>
-      </c>
-      <c r="B4" t="str">
-        <v>goldmansachs.com</v>
-      </c>
-      <c r="C4" t="str">
-        <v>demo/logos/goldman-sachs.svg</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Qualtrics</v>
-      </c>
-      <c r="B5" t="str">
-        <v>qualtrics.com</v>
-      </c>
-      <c r="C5" t="str">
-        <v>demo/logos/qualtrics.svg</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Microsoft</v>
-      </c>
-      <c r="B6" t="str">
-        <v>microsoft.com</v>
-      </c>
-      <c r="C6" t="str">
-        <v>demo/logos/microsoft.svg</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Google</v>
-      </c>
-      <c r="B7" t="str">
-        <v>google.com</v>
-      </c>
-      <c r="C7" t="str">
-        <v>demo/logos/google.svg</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Adobe</v>
-      </c>
-      <c r="B8" t="str">
-        <v>adobe.com</v>
-      </c>
-      <c r="C8" t="str">
-        <v>demo/logos/adobe.svg</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="B9" t="str">
-        <v>apple.com</v>
-      </c>
-      <c r="C9" t="str">
-        <v>demo/logos/apple.svg</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Nike</v>
-      </c>
-      <c r="B10" t="str">
-        <v>nike.com</v>
-      </c>
-      <c r="C10" t="str">
-        <v>demo/logos/nike.svg</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Stanford University</v>
-      </c>
-      <c r="B11" t="str">
-        <v>stanford.edu</v>
-      </c>
-      <c r="C11" t="str">
-        <v>demo/logos/stanford.svg</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>University of Utah</v>
-      </c>
-      <c r="B12" t="str">
-        <v>admissions.utah.edu</v>
-      </c>
-      <c r="C12" t="str">
-        <v>demo/logos/university-of-utah.svg</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M27"/>
   <cols>
@@ -3961,6 +3857,927 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B18"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="60.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str" s="2">
+        <v>Field</v>
+      </c>
+      <c r="B1" t="str" s="2">
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Name</v>
+      </c>
+      <c r="B2" t="str" s="3">
+        <v>Alex Rivera</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Photo</v>
+      </c>
+      <c r="B3" t="str" s="3">
+        <v>demo/photos/alex-rivera.jpg</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Role</v>
+      </c>
+      <c r="B4" t="str" s="3">
+        <v>MBA Candidate</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Headline</v>
+      </c>
+      <c r="B5" t="str" s="3">
+        <v>Stanford MBA '27 · Looking for strategy &amp; product roles</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Company</v>
+      </c>
+      <c r="B6" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Schools</v>
+      </c>
+      <c r="B7" t="str" s="3">
+        <v>Stanford University (2025–2027); University of Washington (2016–2020)</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Past Companies</v>
+      </c>
+      <c r="B8" t="str" s="3">
+        <v>Delta Air Lines (2020–2022); Adobe (2022–2025)</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Email</v>
+      </c>
+      <c r="B9" t="str" s="3">
+        <v>alex.rivera@example.com</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>LinkedIn URL</v>
+      </c>
+      <c r="B10" t="str" s="3">
+        <v>https://www.linkedin.com/in/alex-rivera-demo</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Location</v>
+      </c>
+      <c r="B11" t="str" s="3">
+        <v>Palo Alto, California</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
+        <v>What I'm looking for</v>
+      </c>
+      <c r="B12" t="str" xml:space="preserve" s="3">
+        <v xml:space="preserve">Summer 2027 internships in strategy or product at consumer-tech and airline companies.
+Happy to swap notes on case prep and product sense interviews.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>About</v>
+      </c>
+      <c r="B13" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Industry</v>
+      </c>
+      <c r="B14" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Websites</v>
+      </c>
+      <c r="B15" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Skills</v>
+      </c>
+      <c r="B16" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Certifications</v>
+      </c>
+      <c r="B17" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Volunteering</v>
+      </c>
+      <c r="B18" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B11"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="60.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str" s="2">
+        <v>Setting</v>
+      </c>
+      <c r="B1" t="str" s="2">
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Your name</v>
+      </c>
+      <c r="B2" t="str" s="3">
+        <v>Alex Rivera</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Avatar style</v>
+      </c>
+      <c r="B3" t="str" s="3">
+        <v>notionists</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Your email</v>
+      </c>
+      <c r="B4" t="str" s="3">
+        <v>alex.rivera@example.com</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Meeting length (minutes)</v>
+      </c>
+      <c r="B5" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Zoom link</v>
+      </c>
+      <c r="B6" t="str" s="3">
+        <v>https://zoom.us/j/0000000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Check-in every (days)</v>
+      </c>
+      <c r="B7" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Invite message</v>
+      </c>
+      <c r="B8" t="str" s="3">
+        <v>Hi {first name}, looking forward to our chat on {date} at {time}. {link}</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Group size (people)</v>
+      </c>
+      <c r="B9" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Group by</v>
+      </c>
+      <c r="B10" t="str" s="3">
+        <v>company, school</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Demo base date</v>
+      </c>
+      <c r="B11" t="str" s="3">
+        <v>2026-09-28</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C1"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Node</v>
+      </c>
+      <c r="B1" t="str">
+        <v>X</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G9"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="17.83203125" customWidth="1"/>
+    <col min="3" max="3" width="41.83203125" customWidth="1"/>
+    <col min="4" max="4" width="9.83203125" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" customWidth="1"/>
+    <col min="6" max="6" width="27.83203125" customWidth="1"/>
+    <col min="7" max="7" width="49.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str" s="2">
+        <v>Person</v>
+      </c>
+      <c r="B1" t="str" s="2">
+        <v>Company</v>
+      </c>
+      <c r="C1" t="str" s="2">
+        <v>Title</v>
+      </c>
+      <c r="D1" t="str" s="2">
+        <v>Start</v>
+      </c>
+      <c r="E1" t="str" s="2">
+        <v>End</v>
+      </c>
+      <c r="F1" t="str" s="2">
+        <v>Location</v>
+      </c>
+      <c r="G1" t="str" s="2">
+        <v>Description</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Sofia Alvarez</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Microsoft</v>
+      </c>
+      <c r="C2" t="str" s="3">
+        <v>Product Manager</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2023-07</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Present</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Redmond, Washington</v>
+      </c>
+      <c r="G2" t="str" s="3">
+        <v>Owns the marketplace roadmap and pricing tests.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Sofia Alvarez</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Microsoft</v>
+      </c>
+      <c r="C3" t="str" s="3">
+        <v>Product Manager Intern</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2022-06</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2022-09</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Redmond, Washington</v>
+      </c>
+      <c r="G3" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Sofia Alvarez</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="C4" t="str" s="3">
+        <v>Business Technology Analyst</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2018-08</v>
+      </c>
+      <c r="E4" t="str">
+        <v>2021-06</v>
+      </c>
+      <c r="F4" t="str">
+        <v>San Francisco Bay Area</v>
+      </c>
+      <c r="G4" t="str" s="3">
+        <v>Tech strategy for retail and travel clients.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Jordan Lee</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="C5" t="str" s="3">
+        <v>Strategy &amp; Analytics: Senior Consultant</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2022-01</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Present</v>
+      </c>
+      <c r="F5" t="str">
+        <v>San Francisco, California</v>
+      </c>
+      <c r="G5" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Jordan Lee</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="C6" t="str" s="3">
+        <v>Strategy &amp; Analytics: Consultant</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2020-08</v>
+      </c>
+      <c r="E6" t="str">
+        <v>2021-12</v>
+      </c>
+      <c r="F6" t="str">
+        <v>San Francisco, California</v>
+      </c>
+      <c r="G6" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Jordan Lee</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Adobe</v>
+      </c>
+      <c r="C7" t="str" s="3">
+        <v>Business Strategy Intern</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2019-06</v>
+      </c>
+      <c r="E7" t="str">
+        <v>2019-08</v>
+      </c>
+      <c r="F7" t="str">
+        <v>San Jose, California</v>
+      </c>
+      <c r="G7" t="str" s="3">
+        <v>Market sizing for a new creative-tools bundle.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Noah Carter</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Microsoft</v>
+      </c>
+      <c r="C8" t="str" s="3">
+        <v>Business Strategy Analyst</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2023-02</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Present</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Redmond, Washington</v>
+      </c>
+      <c r="G8" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Noah Carter</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Delta Air Lines</v>
+      </c>
+      <c r="C9" t="str" s="3">
+        <v>Loyalty Program Analyst</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2021-07</v>
+      </c>
+      <c r="E9" t="str">
+        <v>2023-01</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Seattle, Washington</v>
+      </c>
+      <c r="G9" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F5"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="41.83203125" customWidth="1"/>
+    <col min="4" max="4" width="34.83203125" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str" s="2">
+        <v>Person</v>
+      </c>
+      <c r="B1" t="str" s="2">
+        <v>School</v>
+      </c>
+      <c r="C1" t="str" s="2">
+        <v>Degree</v>
+      </c>
+      <c r="D1" t="str" s="2">
+        <v>Field</v>
+      </c>
+      <c r="E1" t="str" s="2">
+        <v>Start</v>
+      </c>
+      <c r="F1" t="str" s="2">
+        <v>End</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Sofia Alvarez</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Stanford University</v>
+      </c>
+      <c r="C2" t="str" s="3">
+        <v>Master of Business Administration - MBA</v>
+      </c>
+      <c r="D2" t="str" s="3">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v>2021</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Sofia Alvarez</v>
+      </c>
+      <c r="B3" t="str">
+        <v>University of Washington</v>
+      </c>
+      <c r="C3" t="str" s="3">
+        <v>Bachelor of Science - BS</v>
+      </c>
+      <c r="D3" t="str" s="3">
+        <v>Information Systems</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2014</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Jordan Lee</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Stanford University</v>
+      </c>
+      <c r="C4" t="str" s="3">
+        <v>Bachelor of Arts - BA</v>
+      </c>
+      <c r="D4" t="str" s="3">
+        <v>Economics</v>
+      </c>
+      <c r="E4" t="str">
+        <v>2016</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Noah Carter</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Stanford University</v>
+      </c>
+      <c r="C5" t="str" s="3">
+        <v>Master of Science - MS</v>
+      </c>
+      <c r="D5" t="str" s="3">
+        <v>Management Science &amp; Engineering</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2019</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2021</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D13"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str" s="2">
+        <v>Person A</v>
+      </c>
+      <c r="B1" t="str" s="2">
+        <v>Person B</v>
+      </c>
+      <c r="C1" t="str" s="2">
+        <v>Type</v>
+      </c>
+      <c r="D1" t="str" s="2">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Jordan Lee</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Rachel Green</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Introduced me</v>
+      </c>
+      <c r="D2" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Sofia Alvarez</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Tom Nguyen</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Introduced me</v>
+      </c>
+      <c r="D3" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Sofia Alvarez</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Isla Moore</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Introduced me</v>
+      </c>
+      <c r="D4" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Noah Carter</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Victor Hale</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Introduced me</v>
+      </c>
+      <c r="D5" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Mia Chen</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Chloe Park</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Introduced me</v>
+      </c>
+      <c r="D6" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Daniel Ortiz</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Ben Foster</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Introduced me</v>
+      </c>
+      <c r="D7" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Liam Walsh</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Zoe Adams</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Introduced me</v>
+      </c>
+      <c r="D8" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Zoe Adams</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Sam Rivera</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Introduced me</v>
+      </c>
+      <c r="D9" t="str" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Liam Walsh</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Mia Chen</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Friend</v>
+      </c>
+      <c r="D10" t="str" s="3">
+        <v>Roommates' friend group</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Sofia Alvarez</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Daniel Ortiz</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Classmate</v>
+      </c>
+      <c r="D11" t="str" s="3">
+        <v>Stanford, same product club</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Jordan Lee</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Owen Price</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Mentor</v>
+      </c>
+      <c r="D12" t="str" s="3">
+        <v>Jordan mentors Owen on case interviews</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Hana Kim</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Ethan Brooks</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Coworker</v>
+      </c>
+      <c r="D13" t="str" s="3">
+        <v>Worked together at Deloitte</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="C2:C1000">
+      <formula1>"Introduced me,Coworker,Classmate,Friend,Mentor,Other"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D4"/>
+  <cols>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" customWidth="1"/>
+    <col min="4" max="4" width="60.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str" s="2">
+        <v>Company</v>
+      </c>
+      <c r="B1" t="str" s="2">
+        <v>Priority</v>
+      </c>
+      <c r="C1" t="str" s="2">
+        <v>Stage</v>
+      </c>
+      <c r="D1" t="str" s="2">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Deloitte</v>
+      </c>
+      <c r="B2" t="str">
+        <v>1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Networking</v>
+      </c>
+      <c r="D2" t="str" s="3">
+        <v>Strategy practice</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Google</v>
+      </c>
+      <c r="B3" t="str">
+        <v>1</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Researching</v>
+      </c>
+      <c r="D3" t="str" s="3">
+        <v>No one on the map yet: two people there are in your LinkedIn pool</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Microsoft</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Networking</v>
+      </c>
+      <c r="D4" t="str" s="3">
+        <v>Product roles; Sofia is the warmest way in</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="B2:B1000">
+      <formula1>"1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="C2:C1000">
+      <formula1>"Researching,Networking,Applied,Interviewing,Offer"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q10"/>
@@ -4817,431 +5634,339 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:B22"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="1" width="22.83203125"/>
+    <col min="2" max="2" customWidth="1" width="110.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str" s="2">
-        <v>Person A</v>
-      </c>
-      <c r="B1" t="str" s="2">
-        <v>Person B</v>
-      </c>
-      <c r="C1" t="str" s="2">
-        <v>Type</v>
-      </c>
-      <c r="D1" t="str" s="2">
-        <v>Notes</v>
+      <c r="A1" t="str">
+        <v>Sheet / column</v>
+      </c>
+      <c r="B1" t="str">
+        <v>What to put there</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Jordan Lee</v>
+        <v>People</v>
       </c>
       <c r="B2" t="str">
-        <v>Rachel Green</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Introduced me</v>
-      </c>
-      <c r="D2" t="str" s="3">
-        <v/>
+        <v>Everyone on your map, in your networking-tracker layout. Only Name is required.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Sofia Alvarez</v>
+        <v xml:space="preserve">  Name, Company, Role / Background</v>
       </c>
       <c r="B3" t="str">
-        <v>Tom Nguyen</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Introduced me</v>
-      </c>
-      <c r="D3" t="str" s="3">
-        <v/>
+        <v>Who they are. 'Stanford' and 'Stanford University' (or 'Acme' and 'Acme, Inc.') count as the same.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Sofia Alvarez</v>
+        <v xml:space="preserve">  How We're Connected</v>
       </c>
       <c r="B4" t="str">
-        <v>Isla Moore</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Introduced me</v>
-      </c>
-      <c r="D4" t="str" s="3">
-        <v/>
+        <v>Filled in by Orbit from schools and connections (plus your own notes in Connection Notes).</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Noah Carter</v>
+        <v xml:space="preserve">  LinkedIn</v>
       </c>
       <c r="B5" t="str">
-        <v>Victor Hale</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Introduced me</v>
-      </c>
-      <c r="D5" t="str" s="3">
-        <v/>
+        <v>Their profile link (shown as 'Profile'). Double-click them on the map to open it.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Mia Chen</v>
+        <v xml:space="preserve">  Meeting Type, Method, Meeting Date</v>
       </c>
       <c r="B6" t="str">
-        <v>Chloe Park</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Introduced me</v>
-      </c>
-      <c r="D6" t="str" s="3">
-        <v/>
+        <v>Filled in by Orbit from the Meetings sheet (the next meeting, or the latest one).</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Daniel Ortiz</v>
+        <v xml:space="preserve">  Status</v>
       </c>
       <c r="B7" t="str">
-        <v>Ben Foster</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Introduced me</v>
-      </c>
-      <c r="D7" t="str" s="3">
-        <v/>
+        <v>To Reach Out / Contacted / Scheduled / Met / Follow Up / Referral (a dropdown; any capitalization works).</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Liam Walsh</v>
+        <v xml:space="preserve">  Date Reached Out, Referral?, Relevant Opportunities, Relationship Plan</v>
       </c>
       <c r="B8" t="str">
-        <v>Zoe Adams</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Introduced me</v>
-      </c>
-      <c r="D8" t="str" s="3">
-        <v/>
+        <v>Yours to fill in (also editable in Orbit under Outreach). Keep In Contact adds a check-in task every 60 days.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Zoe Adams</v>
+        <v xml:space="preserve">  Follow-Up Date, Next Steps</v>
       </c>
       <c r="B9" t="str">
-        <v>Sam Rivera</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Introduced me</v>
-      </c>
-      <c r="D9" t="str" s="3">
-        <v/>
+        <v>Filled in by Orbit from your next open task.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Liam Walsh</v>
+        <v xml:space="preserve">  Email, Photo, Past Companies, Schools, Tags, Connected On, Connected Through, Notes…</v>
       </c>
       <c r="B10" t="str">
-        <v>Mia Chen</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Friend</v>
-      </c>
-      <c r="D10" t="str" s="3">
-        <v>Roommates' friend group</v>
+        <v>The rest of their details. Several schools or past companies: 'BYU (2022–2026); Lakeview High'. Connected Through = who introduced you (blank if you know them directly).</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Sofia Alvarez</v>
+        <v>Groups</v>
       </c>
       <c r="B11" t="str">
-        <v>Daniel Ortiz</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Classmate</v>
-      </c>
-      <c r="D11" t="str" s="3">
-        <v>Stanford, same product club</v>
+        <v>When enough people share a company (now or in the past) or a school, it gets its own dot: 3 by default (Legend &amp; view → Groups form at).</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Jordan Lee</v>
+        <v>Targets</v>
       </c>
       <c r="B12" t="str">
-        <v>Owen Price</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Mentor</v>
-      </c>
-      <c r="D12" t="str" s="3">
-        <v>Jordan mentors Owen on case interviews</v>
+        <v>Companies you want to work at. Priority (1 = highest) and Stage (Researching / Networking / Applied / Interviewing / Offer) are optional.</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Hana Kim</v>
+        <v>Companies</v>
       </c>
       <c r="B13" t="str">
-        <v>Ethan Brooks</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Coworker</v>
-      </c>
-      <c r="D13" t="str" s="3">
-        <v>Worked together at Deloitte</v>
+        <v>Optional: a company or school's Website (for its logo) or a Logo image link.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>LinkedIn Pool</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Your LinkedIn connections from your data export. They're NOT on the map until you add them.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Connections</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Who knows whom: Person A, Person B, Type (Introduced me, Coworker, Classmate, Friend, Mentor, or anything else), Notes.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Experience, Education</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Jobs and schools read from LinkedIn profile PDFs (a timeline in each person's details).</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Me</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Your own profile: photo, role, schools, past companies, what you're looking for.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Meetings</v>
+      </c>
+      <c r="B18" t="str">
+        <v>One row per meeting. The app fills this when you schedule or log a meeting.</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Tasks</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Your to-dos: Task, Person, Company, Due, Done. Meetings add a 'Send thank-you' task automatically.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Your name and email, meeting length, Zoom link, invite message, check-in interval, group size and group by.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Layout</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Managed by the app (where you dragged things on the map).</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Privacy</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Orbit runs entirely in your browser. This file is never uploaded anywhere.</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="0" showErrorMessage="0" errorStyle="information" sqref="C2:C1000">
-      <formula1>"Introduced me,Coworker,Classmate,Friend,Mentor,Other"</formula1>
-    </dataValidation>
-  </dataValidations>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B22"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:C12"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="17.83203125" customWidth="1"/>
-    <col min="3" max="3" width="41.83203125" customWidth="1"/>
-    <col min="4" max="4" width="9.83203125" customWidth="1"/>
-    <col min="5" max="5" width="9.83203125" customWidth="1"/>
-    <col min="6" max="6" width="27.83203125" customWidth="1"/>
-    <col min="7" max="7" width="49.83203125" customWidth="1"/>
+    <col min="1" max="1" width="21.83203125" customWidth="1"/>
+    <col min="2" max="2" width="21.83203125" customWidth="1"/>
+    <col min="3" max="3" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str" s="2">
-        <v>Person</v>
+        <v>Company</v>
       </c>
       <c r="B1" t="str" s="2">
-        <v>Company</v>
+        <v>Website</v>
       </c>
       <c r="C1" t="str" s="2">
-        <v>Title</v>
-      </c>
-      <c r="D1" t="str" s="2">
-        <v>Start</v>
-      </c>
-      <c r="E1" t="str" s="2">
-        <v>End</v>
-      </c>
-      <c r="F1" t="str" s="2">
-        <v>Location</v>
-      </c>
-      <c r="G1" t="str" s="2">
-        <v>Description</v>
+        <v>Logo</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Sofia Alvarez</v>
+        <v>Deloitte</v>
       </c>
       <c r="B2" t="str">
-        <v>Microsoft</v>
-      </c>
-      <c r="C2" t="str" s="3">
-        <v>Product Manager</v>
-      </c>
-      <c r="D2" t="str">
-        <v>2023-07</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Present</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Redmond, Washington</v>
-      </c>
-      <c r="G2" t="str" s="3">
-        <v>Owns the marketplace roadmap and pricing tests.</v>
+        <v>deloitte.com</v>
+      </c>
+      <c r="C2" t="str">
+        <v>demo/logos/deloitte.svg</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Sofia Alvarez</v>
+        <v>Delta Air Lines</v>
       </c>
       <c r="B3" t="str">
-        <v>Microsoft</v>
-      </c>
-      <c r="C3" t="str" s="3">
-        <v>Product Manager Intern</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2022-06</v>
-      </c>
-      <c r="E3" t="str">
-        <v>2022-09</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Redmond, Washington</v>
-      </c>
-      <c r="G3" t="str" s="3">
-        <v/>
+        <v>delta.com</v>
+      </c>
+      <c r="C3" t="str">
+        <v>demo/logos/delta.svg</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Sofia Alvarez</v>
+        <v>Goldman Sachs</v>
       </c>
       <c r="B4" t="str">
-        <v>Deloitte</v>
-      </c>
-      <c r="C4" t="str" s="3">
-        <v>Business Technology Analyst</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2018-08</v>
-      </c>
-      <c r="E4" t="str">
-        <v>2021-06</v>
-      </c>
-      <c r="F4" t="str">
-        <v>San Francisco Bay Area</v>
-      </c>
-      <c r="G4" t="str" s="3">
-        <v>Tech strategy for retail and travel clients.</v>
+        <v>goldmansachs.com</v>
+      </c>
+      <c r="C4" t="str">
+        <v>demo/logos/goldman-sachs.svg</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jordan Lee</v>
+        <v>Qualtrics</v>
       </c>
       <c r="B5" t="str">
-        <v>Deloitte</v>
-      </c>
-      <c r="C5" t="str" s="3">
-        <v>Strategy &amp; Analytics: Senior Consultant</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2022-01</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Present</v>
-      </c>
-      <c r="F5" t="str">
-        <v>San Francisco, California</v>
-      </c>
-      <c r="G5" t="str" s="3">
-        <v/>
+        <v>qualtrics.com</v>
+      </c>
+      <c r="C5" t="str">
+        <v>demo/logos/qualtrics.svg</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Jordan Lee</v>
+        <v>Microsoft</v>
       </c>
       <c r="B6" t="str">
-        <v>Deloitte</v>
-      </c>
-      <c r="C6" t="str" s="3">
-        <v>Strategy &amp; Analytics: Consultant</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2020-08</v>
-      </c>
-      <c r="E6" t="str">
-        <v>2021-12</v>
-      </c>
-      <c r="F6" t="str">
-        <v>San Francisco, California</v>
-      </c>
-      <c r="G6" t="str" s="3">
-        <v/>
+        <v>microsoft.com</v>
+      </c>
+      <c r="C6" t="str">
+        <v>demo/logos/microsoft.svg</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Jordan Lee</v>
+        <v>Google</v>
       </c>
       <c r="B7" t="str">
-        <v>Adobe</v>
-      </c>
-      <c r="C7" t="str" s="3">
-        <v>Business Strategy Intern</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2019-06</v>
-      </c>
-      <c r="E7" t="str">
-        <v>2019-08</v>
-      </c>
-      <c r="F7" t="str">
-        <v>San Jose, California</v>
-      </c>
-      <c r="G7" t="str" s="3">
-        <v>Market sizing for a new creative-tools bundle.</v>
+        <v>google.com</v>
+      </c>
+      <c r="C7" t="str">
+        <v>demo/logos/google.svg</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Noah Carter</v>
+        <v>Adobe</v>
       </c>
       <c r="B8" t="str">
-        <v>Microsoft</v>
-      </c>
-      <c r="C8" t="str" s="3">
-        <v>Business Strategy Analyst</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2023-02</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Present</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Redmond, Washington</v>
-      </c>
-      <c r="G8" t="str" s="3">
-        <v/>
+        <v>adobe.com</v>
+      </c>
+      <c r="C8" t="str">
+        <v>demo/logos/adobe.svg</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Noah Carter</v>
+        <v>Apple</v>
       </c>
       <c r="B9" t="str">
-        <v>Delta Air Lines</v>
-      </c>
-      <c r="C9" t="str" s="3">
-        <v>Loyalty Program Analyst</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2021-07</v>
-      </c>
-      <c r="E9" t="str">
-        <v>2023-01</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Seattle, Washington</v>
-      </c>
-      <c r="G9" t="str" s="3">
-        <v/>
+        <v>apple.com</v>
+      </c>
+      <c r="C9" t="str">
+        <v>demo/logos/apple.svg</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Nike</v>
+      </c>
+      <c r="B10" t="str">
+        <v>nike.com</v>
+      </c>
+      <c r="C10" t="str">
+        <v>demo/logos/nike.svg</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Stanford University</v>
+      </c>
+      <c r="B11" t="str">
+        <v>stanford.edu</v>
+      </c>
+      <c r="C11" t="str">
+        <v>demo/logos/stanford.svg</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>University of Utah</v>
+      </c>
+      <c r="B12" t="str">
+        <v>admissions.utah.edu</v>
+      </c>
+      <c r="C12" t="str">
+        <v>demo/logos/university-of-utah.svg</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
   </ignoredErrors>
 </worksheet>
 </file>